--- a/industries/telecom-it/telecom-model.xlsx
+++ b/industries/telecom-it/telecom-model.xlsx
@@ -10,20 +10,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drivers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PPE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WC" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IS" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segments" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equity" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CFS" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spectrum" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leases" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PPE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WC" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segments" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equity" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CFS" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -992,6 +994,2326 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>INCOME STATEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Segment-disclosed revenue + 10-line cost split + finance items + tax + attributable NI + EPS. All figures SAR billion, EPS in SAR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n"/>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mobile postpaid</t>
+        </is>
+      </c>
+      <c r="C6" s="21">
+        <f>Drivers!$C$31</f>
+        <v/>
+      </c>
+      <c r="D6" s="21">
+        <f>Drivers!$D$31</f>
+        <v/>
+      </c>
+      <c r="E6" s="21">
+        <f>Drivers!$E$31</f>
+        <v/>
+      </c>
+      <c r="F6" s="21">
+        <f>Drivers!$F$31</f>
+        <v/>
+      </c>
+      <c r="G6" s="21">
+        <f>Drivers!$G$31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mobile prepaid</t>
+        </is>
+      </c>
+      <c r="C7" s="21">
+        <f>Drivers!$C$32</f>
+        <v/>
+      </c>
+      <c r="D7" s="21">
+        <f>Drivers!$D$32</f>
+        <v/>
+      </c>
+      <c r="E7" s="21">
+        <f>Drivers!$E$32</f>
+        <v/>
+      </c>
+      <c r="F7" s="21">
+        <f>Drivers!$F$32</f>
+        <v/>
+      </c>
+      <c r="G7" s="21">
+        <f>Drivers!$G$32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fixed broadband</t>
+        </is>
+      </c>
+      <c r="C8" s="21">
+        <f>Drivers!$C$33</f>
+        <v/>
+      </c>
+      <c r="D8" s="21">
+        <f>Drivers!$D$33</f>
+        <v/>
+      </c>
+      <c r="E8" s="21">
+        <f>Drivers!$E$33</f>
+        <v/>
+      </c>
+      <c r="F8" s="21">
+        <f>Drivers!$F$33</f>
+        <v/>
+      </c>
+      <c r="G8" s="21">
+        <f>Drivers!$G$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B2B connectivity</t>
+        </is>
+      </c>
+      <c r="C9" s="21">
+        <f>Drivers!$C$34</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
+        <f>Drivers!$D$34</f>
+        <v/>
+      </c>
+      <c r="E9" s="21">
+        <f>Drivers!$E$34</f>
+        <v/>
+      </c>
+      <c r="F9" s="21">
+        <f>Drivers!$F$34</f>
+        <v/>
+      </c>
+      <c r="G9" s="21">
+        <f>Drivers!$G$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ICT / cloud</t>
+        </is>
+      </c>
+      <c r="C10" s="21">
+        <f>Drivers!$C$35</f>
+        <v/>
+      </c>
+      <c r="D10" s="21">
+        <f>Drivers!$D$35</f>
+        <v/>
+      </c>
+      <c r="E10" s="21">
+        <f>Drivers!$E$35</f>
+        <v/>
+      </c>
+      <c r="F10" s="21">
+        <f>Drivers!$F$35</f>
+        <v/>
+      </c>
+      <c r="G10" s="21">
+        <f>Drivers!$G$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Wholesale</t>
+        </is>
+      </c>
+      <c r="C11" s="21">
+        <f>Drivers!$C$36</f>
+        <v/>
+      </c>
+      <c r="D11" s="21">
+        <f>Drivers!$D$36</f>
+        <v/>
+      </c>
+      <c r="E11" s="21">
+        <f>Drivers!$E$36</f>
+        <v/>
+      </c>
+      <c r="F11" s="21">
+        <f>Drivers!$F$36</f>
+        <v/>
+      </c>
+      <c r="G11" s="21">
+        <f>Drivers!$G$36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Total service revenue</t>
+        </is>
+      </c>
+      <c r="C12" s="24">
+        <f>C6+C7+C8+C9+C10+C11</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>D6+D7+D8+D9+D10+D11</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>E6+E7+E8+E9+E10+E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="24">
+        <f>F6+F7+F8+F9+F10+F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="24">
+        <f>G6+G7+G8+G9+G10+G11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Equipment / handset revenue</t>
+        </is>
+      </c>
+      <c r="C13" s="21">
+        <f>Drivers!$C$39</f>
+        <v/>
+      </c>
+      <c r="D13" s="21">
+        <f>Drivers!$D$39</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>Drivers!$E$39</f>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>Drivers!$F$39</f>
+        <v/>
+      </c>
+      <c r="G13" s="21">
+        <f>Drivers!$G$39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="C14" s="22">
+        <f>C12+C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="22">
+        <f>D12+D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="22">
+        <f>E12+E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="22">
+        <f>F12+F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="22">
+        <f>G12+G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>OPERATING COSTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Interconnect &amp; roaming</t>
+        </is>
+      </c>
+      <c r="C17" s="21">
+        <f>-Assumptions!$B$109*C14</f>
+        <v/>
+      </c>
+      <c r="D17" s="21">
+        <f>-Assumptions!$B$109*D14</f>
+        <v/>
+      </c>
+      <c r="E17" s="21">
+        <f>-Assumptions!$B$109*E14</f>
+        <v/>
+      </c>
+      <c r="F17" s="21">
+        <f>-Assumptions!$B$109*F14</f>
+        <v/>
+      </c>
+      <c r="G17" s="21">
+        <f>-Assumptions!$B$109*G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Content / OTT licensing</t>
+        </is>
+      </c>
+      <c r="C18" s="21">
+        <f>-Assumptions!$B$110*C14</f>
+        <v/>
+      </c>
+      <c r="D18" s="21">
+        <f>-Assumptions!$B$110*D14</f>
+        <v/>
+      </c>
+      <c r="E18" s="21">
+        <f>-Assumptions!$B$110*E14</f>
+        <v/>
+      </c>
+      <c r="F18" s="21">
+        <f>-Assumptions!$B$110*F14</f>
+        <v/>
+      </c>
+      <c r="G18" s="21">
+        <f>-Assumptions!$B$110*G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Equipment COGS</t>
+        </is>
+      </c>
+      <c r="C19" s="21">
+        <f>-C13*(1-Assumptions!$B$106)</f>
+        <v/>
+      </c>
+      <c r="D19" s="21">
+        <f>-D13*(1-Assumptions!$B$106)</f>
+        <v/>
+      </c>
+      <c r="E19" s="21">
+        <f>-E13*(1-Assumptions!$B$106)</f>
+        <v/>
+      </c>
+      <c r="F19" s="21">
+        <f>-F13*(1-Assumptions!$B$106)</f>
+        <v/>
+      </c>
+      <c r="G19" s="21">
+        <f>-G13*(1-Assumptions!$B$106)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Network energy + site lease</t>
+        </is>
+      </c>
+      <c r="C20" s="21">
+        <f>-Assumptions!$B$111*C14</f>
+        <v/>
+      </c>
+      <c r="D20" s="21">
+        <f>-Assumptions!$B$111*D14</f>
+        <v/>
+      </c>
+      <c r="E20" s="21">
+        <f>-Assumptions!$B$111*E14</f>
+        <v/>
+      </c>
+      <c r="F20" s="21">
+        <f>-Assumptions!$B$111*F14</f>
+        <v/>
+      </c>
+      <c r="G20" s="21">
+        <f>-Assumptions!$B$111*G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other network opex</t>
+        </is>
+      </c>
+      <c r="C21" s="21">
+        <f>-Assumptions!$B$112*C14</f>
+        <v/>
+      </c>
+      <c r="D21" s="21">
+        <f>-Assumptions!$B$112*D14</f>
+        <v/>
+      </c>
+      <c r="E21" s="21">
+        <f>-Assumptions!$B$112*E14</f>
+        <v/>
+      </c>
+      <c r="F21" s="21">
+        <f>-Assumptions!$B$112*F14</f>
+        <v/>
+      </c>
+      <c r="G21" s="21">
+        <f>-Assumptions!$B$112*G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Employee costs</t>
+        </is>
+      </c>
+      <c r="C22" s="21">
+        <f>-Assumptions!$B$14*C14</f>
+        <v/>
+      </c>
+      <c r="D22" s="21">
+        <f>-Assumptions!$B$14*D14</f>
+        <v/>
+      </c>
+      <c r="E22" s="21">
+        <f>-Assumptions!$B$14*E14</f>
+        <v/>
+      </c>
+      <c r="F22" s="21">
+        <f>-Assumptions!$B$14*F14</f>
+        <v/>
+      </c>
+      <c r="G22" s="21">
+        <f>-Assumptions!$B$14*G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Customer acquisition (commissions, subsidies)</t>
+        </is>
+      </c>
+      <c r="C23" s="21">
+        <f>-Assumptions!$B$15*C14</f>
+        <v/>
+      </c>
+      <c r="D23" s="21">
+        <f>-Assumptions!$B$15*D14</f>
+        <v/>
+      </c>
+      <c r="E23" s="21">
+        <f>-Assumptions!$B$15*E14</f>
+        <v/>
+      </c>
+      <c r="F23" s="21">
+        <f>-Assumptions!$B$15*F14</f>
+        <v/>
+      </c>
+      <c r="G23" s="21">
+        <f>-Assumptions!$B$15*G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other commercial / marketing</t>
+        </is>
+      </c>
+      <c r="C24" s="21">
+        <f>-Assumptions!$B$113*C14</f>
+        <v/>
+      </c>
+      <c r="D24" s="21">
+        <f>-Assumptions!$B$113*D14</f>
+        <v/>
+      </c>
+      <c r="E24" s="21">
+        <f>-Assumptions!$B$113*E14</f>
+        <v/>
+      </c>
+      <c r="F24" s="21">
+        <f>-Assumptions!$B$113*F14</f>
+        <v/>
+      </c>
+      <c r="G24" s="21">
+        <f>-Assumptions!$B$113*G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  G&amp;A / overhead</t>
+        </is>
+      </c>
+      <c r="C25" s="21">
+        <f>-Assumptions!$B$114*C14</f>
+        <v/>
+      </c>
+      <c r="D25" s="21">
+        <f>-Assumptions!$B$114*D14</f>
+        <v/>
+      </c>
+      <c r="E25" s="21">
+        <f>-Assumptions!$B$114*E14</f>
+        <v/>
+      </c>
+      <c r="F25" s="21">
+        <f>-Assumptions!$B$114*F14</f>
+        <v/>
+      </c>
+      <c r="G25" s="21">
+        <f>-Assumptions!$B$114*G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FX losses (net)</t>
+        </is>
+      </c>
+      <c r="C26" s="21">
+        <f>-Assumptions!$B$115*C14</f>
+        <v/>
+      </c>
+      <c r="D26" s="21">
+        <f>-Assumptions!$B$115*D14</f>
+        <v/>
+      </c>
+      <c r="E26" s="21">
+        <f>-Assumptions!$B$115*E14</f>
+        <v/>
+      </c>
+      <c r="F26" s="21">
+        <f>-Assumptions!$B$115*F14</f>
+        <v/>
+      </c>
+      <c r="G26" s="21">
+        <f>-Assumptions!$B$115*G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Total operating costs</t>
+        </is>
+      </c>
+      <c r="C27" s="24">
+        <f>C17+C18+C19+C20+C21+C22+C23+C24+C25+C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="24">
+        <f>D17+D18+D19+D20+D21+D22+D23+D24+D25+D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="24">
+        <f>E17+E18+E19+E20+E21+E22+E23+E24+E25+E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="24">
+        <f>F17+F18+F19+F20+F21+F22+F23+F24+F25+F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="24">
+        <f>G17+G18+G19+G20+G21+G22+G23+G24+G25+G26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C28" s="22">
+        <f>C14+C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="22">
+        <f>D14+D27</f>
+        <v/>
+      </c>
+      <c r="E28" s="22">
+        <f>E14+E27</f>
+        <v/>
+      </c>
+      <c r="F28" s="22">
+        <f>F14+F27</f>
+        <v/>
+      </c>
+      <c r="G28" s="22">
+        <f>G14+G27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation (PP&amp;E + right-of-use)</t>
+        </is>
+      </c>
+      <c r="C30" s="21">
+        <f>PPE!$C$8+Leases!$C$9</f>
+        <v/>
+      </c>
+      <c r="D30" s="21">
+        <f>PPE!$D$8+Leases!$D$9</f>
+        <v/>
+      </c>
+      <c r="E30" s="21">
+        <f>PPE!$E$8+Leases!$E$9</f>
+        <v/>
+      </c>
+      <c r="F30" s="21">
+        <f>PPE!$F$8+Leases!$F$9</f>
+        <v/>
+      </c>
+      <c r="G30" s="21">
+        <f>PPE!$G$8+Leases!$G$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Amortisation (intangibles + spectrum)</t>
+        </is>
+      </c>
+      <c r="C31" s="21">
+        <f>-Assumptions!$B$118*C14+Spectrum!$C$24</f>
+        <v/>
+      </c>
+      <c r="D31" s="21">
+        <f>-Assumptions!$B$118*D14+Spectrum!$D$24</f>
+        <v/>
+      </c>
+      <c r="E31" s="21">
+        <f>-Assumptions!$B$118*E14+Spectrum!$E$24</f>
+        <v/>
+      </c>
+      <c r="F31" s="21">
+        <f>-Assumptions!$B$118*F14+Spectrum!$F$24</f>
+        <v/>
+      </c>
+      <c r="G31" s="21">
+        <f>-Assumptions!$B$118*G14+Spectrum!$G$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="C32" s="22">
+        <f>C28+C30+C31</f>
+        <v/>
+      </c>
+      <c r="D32" s="22">
+        <f>D28+D30+D31</f>
+        <v/>
+      </c>
+      <c r="E32" s="22">
+        <f>E28+E30+E31</f>
+        <v/>
+      </c>
+      <c r="F32" s="22">
+        <f>F28+F30+F31</f>
+        <v/>
+      </c>
+      <c r="G32" s="22">
+        <f>G28+G30+G31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Finance income</t>
+        </is>
+      </c>
+      <c r="C34" s="21">
+        <f>Assumptions!$B$17*C14</f>
+        <v/>
+      </c>
+      <c r="D34" s="21">
+        <f>Assumptions!$B$17*D14</f>
+        <v/>
+      </c>
+      <c r="E34" s="21">
+        <f>Assumptions!$B$17*E14</f>
+        <v/>
+      </c>
+      <c r="F34" s="21">
+        <f>Assumptions!$B$17*F14</f>
+        <v/>
+      </c>
+      <c r="G34" s="21">
+        <f>Assumptions!$B$17*G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Finance costs (interest + lease interest)</t>
+        </is>
+      </c>
+      <c r="C35" s="21">
+        <f>-Debt!$C$16-Leases!$C$14</f>
+        <v/>
+      </c>
+      <c r="D35" s="21">
+        <f>-Debt!$D$16-Leases!$D$14</f>
+        <v/>
+      </c>
+      <c r="E35" s="21">
+        <f>-Debt!$E$16-Leases!$E$14</f>
+        <v/>
+      </c>
+      <c r="F35" s="21">
+        <f>-Debt!$F$16-Leases!$F$14</f>
+        <v/>
+      </c>
+      <c r="G35" s="21">
+        <f>-Debt!$G$16-Leases!$G$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Share of associates / JVs</t>
+        </is>
+      </c>
+      <c r="C36" s="21">
+        <f>Assumptions!$B$119*(1+Assumptions!$B$120)^1</f>
+        <v/>
+      </c>
+      <c r="D36" s="21">
+        <f>Assumptions!$B$119*(1+Assumptions!$B$120)^2</f>
+        <v/>
+      </c>
+      <c r="E36" s="21">
+        <f>Assumptions!$B$119*(1+Assumptions!$B$120)^3</f>
+        <v/>
+      </c>
+      <c r="F36" s="21">
+        <f>Assumptions!$B$119*(1+Assumptions!$B$120)^4</f>
+        <v/>
+      </c>
+      <c r="G36" s="21">
+        <f>Assumptions!$B$119*(1+Assumptions!$B$120)^5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Profit before tax</t>
+        </is>
+      </c>
+      <c r="C37" s="24">
+        <f>C32+C34+C35+C36</f>
+        <v/>
+      </c>
+      <c r="D37" s="24">
+        <f>D32+D34+D35+D36</f>
+        <v/>
+      </c>
+      <c r="E37" s="24">
+        <f>E32+E34+E35+E36</f>
+        <v/>
+      </c>
+      <c r="F37" s="24">
+        <f>F32+F34+F35+F36</f>
+        <v/>
+      </c>
+      <c r="G37" s="24">
+        <f>G32+G34+G35+G36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Current tax expense</t>
+        </is>
+      </c>
+      <c r="C38" s="21">
+        <f>-Tax!$C$8</f>
+        <v/>
+      </c>
+      <c r="D38" s="21">
+        <f>-Tax!$D$8</f>
+        <v/>
+      </c>
+      <c r="E38" s="21">
+        <f>-Tax!$E$8</f>
+        <v/>
+      </c>
+      <c r="F38" s="21">
+        <f>-Tax!$F$8</f>
+        <v/>
+      </c>
+      <c r="G38" s="21">
+        <f>-Tax!$G$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax (movement)</t>
+        </is>
+      </c>
+      <c r="C39" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D39" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E39" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F39" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G39" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>NET INCOME</t>
+        </is>
+      </c>
+      <c r="C40" s="22">
+        <f>C37+C38+C39</f>
+        <v/>
+      </c>
+      <c r="D40" s="22">
+        <f>D37+D38+D39</f>
+        <v/>
+      </c>
+      <c r="E40" s="22">
+        <f>E37+E38+E39</f>
+        <v/>
+      </c>
+      <c r="F40" s="22">
+        <f>F37+F38+F39</f>
+        <v/>
+      </c>
+      <c r="G40" s="22">
+        <f>G37+G38+G39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Attributable to equity holders of the parent</t>
+        </is>
+      </c>
+      <c r="C42" s="21">
+        <f>C40*(1-Assumptions!$B$121)</f>
+        <v/>
+      </c>
+      <c r="D42" s="21">
+        <f>D40*(1-Assumptions!$B$121)</f>
+        <v/>
+      </c>
+      <c r="E42" s="21">
+        <f>E40*(1-Assumptions!$B$121)</f>
+        <v/>
+      </c>
+      <c r="F42" s="21">
+        <f>F40*(1-Assumptions!$B$121)</f>
+        <v/>
+      </c>
+      <c r="G42" s="21">
+        <f>G40*(1-Assumptions!$B$121)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Attributable to minority interest</t>
+        </is>
+      </c>
+      <c r="C43" s="21">
+        <f>C40*Assumptions!$B$121</f>
+        <v/>
+      </c>
+      <c r="D43" s="21">
+        <f>D40*Assumptions!$B$121</f>
+        <v/>
+      </c>
+      <c r="E43" s="21">
+        <f>E40*Assumptions!$B$121</f>
+        <v/>
+      </c>
+      <c r="F43" s="21">
+        <f>F40*Assumptions!$B$121</f>
+        <v/>
+      </c>
+      <c r="G43" s="21">
+        <f>G40*Assumptions!$B$121</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Basic EPS (SAR / share)</t>
+        </is>
+      </c>
+      <c r="C45" s="25">
+        <f>C42*1000/Assumptions!$B$32</f>
+        <v/>
+      </c>
+      <c r="D45" s="25">
+        <f>D42*1000/Assumptions!$B$32</f>
+        <v/>
+      </c>
+      <c r="E45" s="25">
+        <f>E42*1000/Assumptions!$B$32</f>
+        <v/>
+      </c>
+      <c r="F45" s="25">
+        <f>F42*1000/Assumptions!$B$32</f>
+        <v/>
+      </c>
+      <c r="G45" s="25">
+        <f>G42*1000/Assumptions!$B$32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>MEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C48" s="23">
+        <f>C28/C14</f>
+        <v/>
+      </c>
+      <c r="D48" s="23">
+        <f>D28/D14</f>
+        <v/>
+      </c>
+      <c r="E48" s="23">
+        <f>E28/E14</f>
+        <v/>
+      </c>
+      <c r="F48" s="23">
+        <f>F28/F14</f>
+        <v/>
+      </c>
+      <c r="G48" s="23">
+        <f>G28/G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBIT margin</t>
+        </is>
+      </c>
+      <c r="C49" s="23">
+        <f>C32/C14</f>
+        <v/>
+      </c>
+      <c r="D49" s="23">
+        <f>D32/D14</f>
+        <v/>
+      </c>
+      <c r="E49" s="23">
+        <f>E32/E14</f>
+        <v/>
+      </c>
+      <c r="F49" s="23">
+        <f>F32/F14</f>
+        <v/>
+      </c>
+      <c r="G49" s="23">
+        <f>G32/G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Net margin</t>
+        </is>
+      </c>
+      <c r="C50" s="23">
+        <f>C40/C14</f>
+        <v/>
+      </c>
+      <c r="D50" s="23">
+        <f>D40/D14</f>
+        <v/>
+      </c>
+      <c r="E50" s="23">
+        <f>E40/E14</f>
+        <v/>
+      </c>
+      <c r="F50" s="23">
+        <f>F40/F14</f>
+        <v/>
+      </c>
+      <c r="G50" s="23">
+        <f>G40/G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Effective tax rate</t>
+        </is>
+      </c>
+      <c r="C51" s="23">
+        <f>-(C38+C39)/C37</f>
+        <v/>
+      </c>
+      <c r="D51" s="23">
+        <f>-(D38+D39)/D37</f>
+        <v/>
+      </c>
+      <c r="E51" s="23">
+        <f>-(E38+E39)/E37</f>
+        <v/>
+      </c>
+      <c r="F51" s="23">
+        <f>-(F38+F39)/F37</f>
+        <v/>
+      </c>
+      <c r="G51" s="23">
+        <f>-(G38+G39)/G37</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>SEGMENT P&amp;L  (contribution margin view)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Each segment carries its own contribution margin (segment revenue × CM%). Difference vs. IS EBITDA = unallocated group overhead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n"/>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Y0 (base)</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mobile postpaid</t>
+        </is>
+      </c>
+      <c r="B7" s="21">
+        <f>Drivers!$B$31</f>
+        <v/>
+      </c>
+      <c r="C7" s="21">
+        <f>Drivers!$C$31</f>
+        <v/>
+      </c>
+      <c r="D7" s="21">
+        <f>Drivers!$D$31</f>
+        <v/>
+      </c>
+      <c r="E7" s="21">
+        <f>Drivers!$E$31</f>
+        <v/>
+      </c>
+      <c r="F7" s="21">
+        <f>Drivers!$F$31</f>
+        <v/>
+      </c>
+      <c r="G7" s="21">
+        <f>Drivers!$G$31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mobile prepaid</t>
+        </is>
+      </c>
+      <c r="B8" s="21">
+        <f>Drivers!$B$32</f>
+        <v/>
+      </c>
+      <c r="C8" s="21">
+        <f>Drivers!$C$32</f>
+        <v/>
+      </c>
+      <c r="D8" s="21">
+        <f>Drivers!$D$32</f>
+        <v/>
+      </c>
+      <c r="E8" s="21">
+        <f>Drivers!$E$32</f>
+        <v/>
+      </c>
+      <c r="F8" s="21">
+        <f>Drivers!$F$32</f>
+        <v/>
+      </c>
+      <c r="G8" s="21">
+        <f>Drivers!$G$32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fixed broadband</t>
+        </is>
+      </c>
+      <c r="B9" s="21">
+        <f>Drivers!$B$33</f>
+        <v/>
+      </c>
+      <c r="C9" s="21">
+        <f>Drivers!$C$33</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
+        <f>Drivers!$D$33</f>
+        <v/>
+      </c>
+      <c r="E9" s="21">
+        <f>Drivers!$E$33</f>
+        <v/>
+      </c>
+      <c r="F9" s="21">
+        <f>Drivers!$F$33</f>
+        <v/>
+      </c>
+      <c r="G9" s="21">
+        <f>Drivers!$G$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B2B connectivity</t>
+        </is>
+      </c>
+      <c r="B10" s="21">
+        <f>Drivers!$B$34</f>
+        <v/>
+      </c>
+      <c r="C10" s="21">
+        <f>Drivers!$C$34</f>
+        <v/>
+      </c>
+      <c r="D10" s="21">
+        <f>Drivers!$D$34</f>
+        <v/>
+      </c>
+      <c r="E10" s="21">
+        <f>Drivers!$E$34</f>
+        <v/>
+      </c>
+      <c r="F10" s="21">
+        <f>Drivers!$F$34</f>
+        <v/>
+      </c>
+      <c r="G10" s="21">
+        <f>Drivers!$G$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ICT / cloud</t>
+        </is>
+      </c>
+      <c r="B11" s="21">
+        <f>Drivers!$B$35</f>
+        <v/>
+      </c>
+      <c r="C11" s="21">
+        <f>Drivers!$C$35</f>
+        <v/>
+      </c>
+      <c r="D11" s="21">
+        <f>Drivers!$D$35</f>
+        <v/>
+      </c>
+      <c r="E11" s="21">
+        <f>Drivers!$E$35</f>
+        <v/>
+      </c>
+      <c r="F11" s="21">
+        <f>Drivers!$F$35</f>
+        <v/>
+      </c>
+      <c r="G11" s="21">
+        <f>Drivers!$G$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Wholesale</t>
+        </is>
+      </c>
+      <c r="B12" s="21">
+        <f>Drivers!$B$36</f>
+        <v/>
+      </c>
+      <c r="C12" s="21">
+        <f>Drivers!$C$36</f>
+        <v/>
+      </c>
+      <c r="D12" s="21">
+        <f>Drivers!$D$36</f>
+        <v/>
+      </c>
+      <c r="E12" s="21">
+        <f>Drivers!$E$36</f>
+        <v/>
+      </c>
+      <c r="F12" s="21">
+        <f>Drivers!$F$36</f>
+        <v/>
+      </c>
+      <c r="G12" s="21">
+        <f>Drivers!$G$36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Equipment</t>
+        </is>
+      </c>
+      <c r="B13" s="21">
+        <f>Drivers!$B$39</f>
+        <v/>
+      </c>
+      <c r="C13" s="21">
+        <f>Drivers!$C$39</f>
+        <v/>
+      </c>
+      <c r="D13" s="21">
+        <f>Drivers!$D$39</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>Drivers!$E$39</f>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>Drivers!$F$39</f>
+        <v/>
+      </c>
+      <c r="G13" s="21">
+        <f>Drivers!$G$39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total service revenue</t>
+        </is>
+      </c>
+      <c r="B14" s="24">
+        <f>B7+B8+B9+B10+B11+B12</f>
+        <v/>
+      </c>
+      <c r="C14" s="24">
+        <f>C7+C8+C9+C10+C11+C12</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>D7+D8+D9+D10+D11+D12</f>
+        <v/>
+      </c>
+      <c r="E14" s="24">
+        <f>E7+E8+E9+E10+E11+E12</f>
+        <v/>
+      </c>
+      <c r="F14" s="24">
+        <f>F7+F8+F9+F10+F11+F12</f>
+        <v/>
+      </c>
+      <c r="G14" s="24">
+        <f>G7+G8+G9+G10+G11+G12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Total revenue (incl. equipment)</t>
+        </is>
+      </c>
+      <c r="B15" s="22">
+        <f>B7+B8+B9+B10+B11+B12+B13</f>
+        <v/>
+      </c>
+      <c r="C15" s="22">
+        <f>C7+C8+C9+C10+C11+C12+C13</f>
+        <v/>
+      </c>
+      <c r="D15" s="22">
+        <f>D7+D8+D9+D10+D11+D12+D13</f>
+        <v/>
+      </c>
+      <c r="E15" s="22">
+        <f>E7+E8+E9+E10+E11+E12+E13</f>
+        <v/>
+      </c>
+      <c r="F15" s="22">
+        <f>F7+F8+F9+F10+F11+F12+F13</f>
+        <v/>
+      </c>
+      <c r="G15" s="22">
+        <f>G7+G8+G9+G10+G11+G12+G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>DIRECT COSTS  (= revenue × (1 − CM%))</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mobile postpaid</t>
+        </is>
+      </c>
+      <c r="B18" s="21">
+        <f>-B7*(1-Assumptions!$B$70)</f>
+        <v/>
+      </c>
+      <c r="C18" s="21">
+        <f>-C7*(1-Assumptions!$B$70)</f>
+        <v/>
+      </c>
+      <c r="D18" s="21">
+        <f>-D7*(1-Assumptions!$B$70)</f>
+        <v/>
+      </c>
+      <c r="E18" s="21">
+        <f>-E7*(1-Assumptions!$B$70)</f>
+        <v/>
+      </c>
+      <c r="F18" s="21">
+        <f>-F7*(1-Assumptions!$B$70)</f>
+        <v/>
+      </c>
+      <c r="G18" s="21">
+        <f>-G7*(1-Assumptions!$B$70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mobile prepaid</t>
+        </is>
+      </c>
+      <c r="B19" s="21">
+        <f>-B8*(1-Assumptions!$B$78)</f>
+        <v/>
+      </c>
+      <c r="C19" s="21">
+        <f>-C8*(1-Assumptions!$B$78)</f>
+        <v/>
+      </c>
+      <c r="D19" s="21">
+        <f>-D8*(1-Assumptions!$B$78)</f>
+        <v/>
+      </c>
+      <c r="E19" s="21">
+        <f>-E8*(1-Assumptions!$B$78)</f>
+        <v/>
+      </c>
+      <c r="F19" s="21">
+        <f>-F8*(1-Assumptions!$B$78)</f>
+        <v/>
+      </c>
+      <c r="G19" s="21">
+        <f>-G8*(1-Assumptions!$B$78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fixed broadband</t>
+        </is>
+      </c>
+      <c r="B20" s="21">
+        <f>-B9*(1-Assumptions!$B$86)</f>
+        <v/>
+      </c>
+      <c r="C20" s="21">
+        <f>-C9*(1-Assumptions!$B$86)</f>
+        <v/>
+      </c>
+      <c r="D20" s="21">
+        <f>-D9*(1-Assumptions!$B$86)</f>
+        <v/>
+      </c>
+      <c r="E20" s="21">
+        <f>-E9*(1-Assumptions!$B$86)</f>
+        <v/>
+      </c>
+      <c r="F20" s="21">
+        <f>-F9*(1-Assumptions!$B$86)</f>
+        <v/>
+      </c>
+      <c r="G20" s="21">
+        <f>-G9*(1-Assumptions!$B$86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B2B connectivity</t>
+        </is>
+      </c>
+      <c r="B21" s="21">
+        <f>-B10*(1-Assumptions!$B$91)</f>
+        <v/>
+      </c>
+      <c r="C21" s="21">
+        <f>-C10*(1-Assumptions!$B$91)</f>
+        <v/>
+      </c>
+      <c r="D21" s="21">
+        <f>-D10*(1-Assumptions!$B$91)</f>
+        <v/>
+      </c>
+      <c r="E21" s="21">
+        <f>-E10*(1-Assumptions!$B$91)</f>
+        <v/>
+      </c>
+      <c r="F21" s="21">
+        <f>-F10*(1-Assumptions!$B$91)</f>
+        <v/>
+      </c>
+      <c r="G21" s="21">
+        <f>-G10*(1-Assumptions!$B$91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ICT / cloud</t>
+        </is>
+      </c>
+      <c r="B22" s="21">
+        <f>-B11*(1-Assumptions!$B$96)</f>
+        <v/>
+      </c>
+      <c r="C22" s="21">
+        <f>-C11*(1-Assumptions!$B$96)</f>
+        <v/>
+      </c>
+      <c r="D22" s="21">
+        <f>-D11*(1-Assumptions!$B$96)</f>
+        <v/>
+      </c>
+      <c r="E22" s="21">
+        <f>-E11*(1-Assumptions!$B$96)</f>
+        <v/>
+      </c>
+      <c r="F22" s="21">
+        <f>-F11*(1-Assumptions!$B$96)</f>
+        <v/>
+      </c>
+      <c r="G22" s="21">
+        <f>-G11*(1-Assumptions!$B$96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Wholesale</t>
+        </is>
+      </c>
+      <c r="B23" s="21">
+        <f>-B12*(1-Assumptions!$B$101)</f>
+        <v/>
+      </c>
+      <c r="C23" s="21">
+        <f>-C12*(1-Assumptions!$B$101)</f>
+        <v/>
+      </c>
+      <c r="D23" s="21">
+        <f>-D12*(1-Assumptions!$B$101)</f>
+        <v/>
+      </c>
+      <c r="E23" s="21">
+        <f>-E12*(1-Assumptions!$B$101)</f>
+        <v/>
+      </c>
+      <c r="F23" s="21">
+        <f>-F12*(1-Assumptions!$B$101)</f>
+        <v/>
+      </c>
+      <c r="G23" s="21">
+        <f>-G12*(1-Assumptions!$B$101)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Equipment</t>
+        </is>
+      </c>
+      <c r="B24" s="21">
+        <f>-B13*(1-Assumptions!$B$106)</f>
+        <v/>
+      </c>
+      <c r="C24" s="21">
+        <f>-C13*(1-Assumptions!$B$106)</f>
+        <v/>
+      </c>
+      <c r="D24" s="21">
+        <f>-D13*(1-Assumptions!$B$106)</f>
+        <v/>
+      </c>
+      <c r="E24" s="21">
+        <f>-E13*(1-Assumptions!$B$106)</f>
+        <v/>
+      </c>
+      <c r="F24" s="21">
+        <f>-F13*(1-Assumptions!$B$106)</f>
+        <v/>
+      </c>
+      <c r="G24" s="21">
+        <f>-G13*(1-Assumptions!$B$106)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Total direct costs</t>
+        </is>
+      </c>
+      <c r="B25" s="24">
+        <f>B18+B19+B20+B21+B22+B23+B24</f>
+        <v/>
+      </c>
+      <c r="C25" s="24">
+        <f>C18+C19+C20+C21+C22+C23+C24</f>
+        <v/>
+      </c>
+      <c r="D25" s="24">
+        <f>D18+D19+D20+D21+D22+D23+D24</f>
+        <v/>
+      </c>
+      <c r="E25" s="24">
+        <f>E18+E19+E20+E21+E22+E23+E24</f>
+        <v/>
+      </c>
+      <c r="F25" s="24">
+        <f>F18+F19+F20+F21+F22+F23+F24</f>
+        <v/>
+      </c>
+      <c r="G25" s="24">
+        <f>G18+G19+G20+G21+G22+G23+G24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>SEGMENT CONTRIBUTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mobile postpaid</t>
+        </is>
+      </c>
+      <c r="B28" s="21">
+        <f>B7+B18</f>
+        <v/>
+      </c>
+      <c r="C28" s="21">
+        <f>C7+C18</f>
+        <v/>
+      </c>
+      <c r="D28" s="21">
+        <f>D7+D18</f>
+        <v/>
+      </c>
+      <c r="E28" s="21">
+        <f>E7+E18</f>
+        <v/>
+      </c>
+      <c r="F28" s="21">
+        <f>F7+F18</f>
+        <v/>
+      </c>
+      <c r="G28" s="21">
+        <f>G7+G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mobile prepaid</t>
+        </is>
+      </c>
+      <c r="B29" s="21">
+        <f>B8+B19</f>
+        <v/>
+      </c>
+      <c r="C29" s="21">
+        <f>C8+C19</f>
+        <v/>
+      </c>
+      <c r="D29" s="21">
+        <f>D8+D19</f>
+        <v/>
+      </c>
+      <c r="E29" s="21">
+        <f>E8+E19</f>
+        <v/>
+      </c>
+      <c r="F29" s="21">
+        <f>F8+F19</f>
+        <v/>
+      </c>
+      <c r="G29" s="21">
+        <f>G8+G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fixed broadband</t>
+        </is>
+      </c>
+      <c r="B30" s="21">
+        <f>B9+B20</f>
+        <v/>
+      </c>
+      <c r="C30" s="21">
+        <f>C9+C20</f>
+        <v/>
+      </c>
+      <c r="D30" s="21">
+        <f>D9+D20</f>
+        <v/>
+      </c>
+      <c r="E30" s="21">
+        <f>E9+E20</f>
+        <v/>
+      </c>
+      <c r="F30" s="21">
+        <f>F9+F20</f>
+        <v/>
+      </c>
+      <c r="G30" s="21">
+        <f>G9+G20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B2B connectivity</t>
+        </is>
+      </c>
+      <c r="B31" s="21">
+        <f>B10+B21</f>
+        <v/>
+      </c>
+      <c r="C31" s="21">
+        <f>C10+C21</f>
+        <v/>
+      </c>
+      <c r="D31" s="21">
+        <f>D10+D21</f>
+        <v/>
+      </c>
+      <c r="E31" s="21">
+        <f>E10+E21</f>
+        <v/>
+      </c>
+      <c r="F31" s="21">
+        <f>F10+F21</f>
+        <v/>
+      </c>
+      <c r="G31" s="21">
+        <f>G10+G21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ICT / cloud</t>
+        </is>
+      </c>
+      <c r="B32" s="21">
+        <f>B11+B22</f>
+        <v/>
+      </c>
+      <c r="C32" s="21">
+        <f>C11+C22</f>
+        <v/>
+      </c>
+      <c r="D32" s="21">
+        <f>D11+D22</f>
+        <v/>
+      </c>
+      <c r="E32" s="21">
+        <f>E11+E22</f>
+        <v/>
+      </c>
+      <c r="F32" s="21">
+        <f>F11+F22</f>
+        <v/>
+      </c>
+      <c r="G32" s="21">
+        <f>G11+G22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Wholesale</t>
+        </is>
+      </c>
+      <c r="B33" s="21">
+        <f>B12+B23</f>
+        <v/>
+      </c>
+      <c r="C33" s="21">
+        <f>C12+C23</f>
+        <v/>
+      </c>
+      <c r="D33" s="21">
+        <f>D12+D23</f>
+        <v/>
+      </c>
+      <c r="E33" s="21">
+        <f>E12+E23</f>
+        <v/>
+      </c>
+      <c r="F33" s="21">
+        <f>F12+F23</f>
+        <v/>
+      </c>
+      <c r="G33" s="21">
+        <f>G12+G23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Equipment</t>
+        </is>
+      </c>
+      <c r="B34" s="21">
+        <f>B13+B24</f>
+        <v/>
+      </c>
+      <c r="C34" s="21">
+        <f>C13+C24</f>
+        <v/>
+      </c>
+      <c r="D34" s="21">
+        <f>D13+D24</f>
+        <v/>
+      </c>
+      <c r="E34" s="21">
+        <f>E13+E24</f>
+        <v/>
+      </c>
+      <c r="F34" s="21">
+        <f>F13+F24</f>
+        <v/>
+      </c>
+      <c r="G34" s="21">
+        <f>G13+G24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>Aggregate segment contribution</t>
+        </is>
+      </c>
+      <c r="B35" s="22">
+        <f>B28+B29+B30+B31+B32+B33+B34</f>
+        <v/>
+      </c>
+      <c r="C35" s="22">
+        <f>C28+C29+C30+C31+C32+C33+C34</f>
+        <v/>
+      </c>
+      <c r="D35" s="22">
+        <f>D28+D29+D30+D31+D32+D33+D34</f>
+        <v/>
+      </c>
+      <c r="E35" s="22">
+        <f>E28+E29+E30+E31+E32+E33+E34</f>
+        <v/>
+      </c>
+      <c r="F35" s="22">
+        <f>F28+F29+F30+F31+F32+F33+F34</f>
+        <v/>
+      </c>
+      <c r="G35" s="22">
+        <f>G28+G29+G30+G31+G32+G33+G34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>CONTRIBUTION MARGIN %</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mobile postpaid</t>
+        </is>
+      </c>
+      <c r="B38" s="23">
+        <f>IF(B7=0,0,B28/B7)</f>
+        <v/>
+      </c>
+      <c r="C38" s="23">
+        <f>IF(C7=0,0,C28/C7)</f>
+        <v/>
+      </c>
+      <c r="D38" s="23">
+        <f>IF(D7=0,0,D28/D7)</f>
+        <v/>
+      </c>
+      <c r="E38" s="23">
+        <f>IF(E7=0,0,E28/E7)</f>
+        <v/>
+      </c>
+      <c r="F38" s="23">
+        <f>IF(F7=0,0,F28/F7)</f>
+        <v/>
+      </c>
+      <c r="G38" s="23">
+        <f>IF(G7=0,0,G28/G7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mobile prepaid</t>
+        </is>
+      </c>
+      <c r="B39" s="23">
+        <f>IF(B8=0,0,B29/B8)</f>
+        <v/>
+      </c>
+      <c r="C39" s="23">
+        <f>IF(C8=0,0,C29/C8)</f>
+        <v/>
+      </c>
+      <c r="D39" s="23">
+        <f>IF(D8=0,0,D29/D8)</f>
+        <v/>
+      </c>
+      <c r="E39" s="23">
+        <f>IF(E8=0,0,E29/E8)</f>
+        <v/>
+      </c>
+      <c r="F39" s="23">
+        <f>IF(F8=0,0,F29/F8)</f>
+        <v/>
+      </c>
+      <c r="G39" s="23">
+        <f>IF(G8=0,0,G29/G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fixed broadband</t>
+        </is>
+      </c>
+      <c r="B40" s="23">
+        <f>IF(B9=0,0,B30/B9)</f>
+        <v/>
+      </c>
+      <c r="C40" s="23">
+        <f>IF(C9=0,0,C30/C9)</f>
+        <v/>
+      </c>
+      <c r="D40" s="23">
+        <f>IF(D9=0,0,D30/D9)</f>
+        <v/>
+      </c>
+      <c r="E40" s="23">
+        <f>IF(E9=0,0,E30/E9)</f>
+        <v/>
+      </c>
+      <c r="F40" s="23">
+        <f>IF(F9=0,0,F30/F9)</f>
+        <v/>
+      </c>
+      <c r="G40" s="23">
+        <f>IF(G9=0,0,G30/G9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B2B connectivity</t>
+        </is>
+      </c>
+      <c r="B41" s="23">
+        <f>IF(B10=0,0,B31/B10)</f>
+        <v/>
+      </c>
+      <c r="C41" s="23">
+        <f>IF(C10=0,0,C31/C10)</f>
+        <v/>
+      </c>
+      <c r="D41" s="23">
+        <f>IF(D10=0,0,D31/D10)</f>
+        <v/>
+      </c>
+      <c r="E41" s="23">
+        <f>IF(E10=0,0,E31/E10)</f>
+        <v/>
+      </c>
+      <c r="F41" s="23">
+        <f>IF(F10=0,0,F31/F10)</f>
+        <v/>
+      </c>
+      <c r="G41" s="23">
+        <f>IF(G10=0,0,G31/G10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ICT / cloud</t>
+        </is>
+      </c>
+      <c r="B42" s="23">
+        <f>IF(B11=0,0,B32/B11)</f>
+        <v/>
+      </c>
+      <c r="C42" s="23">
+        <f>IF(C11=0,0,C32/C11)</f>
+        <v/>
+      </c>
+      <c r="D42" s="23">
+        <f>IF(D11=0,0,D32/D11)</f>
+        <v/>
+      </c>
+      <c r="E42" s="23">
+        <f>IF(E11=0,0,E32/E11)</f>
+        <v/>
+      </c>
+      <c r="F42" s="23">
+        <f>IF(F11=0,0,F32/F11)</f>
+        <v/>
+      </c>
+      <c r="G42" s="23">
+        <f>IF(G11=0,0,G32/G11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Wholesale</t>
+        </is>
+      </c>
+      <c r="B43" s="23">
+        <f>IF(B12=0,0,B33/B12)</f>
+        <v/>
+      </c>
+      <c r="C43" s="23">
+        <f>IF(C12=0,0,C33/C12)</f>
+        <v/>
+      </c>
+      <c r="D43" s="23">
+        <f>IF(D12=0,0,D33/D12)</f>
+        <v/>
+      </c>
+      <c r="E43" s="23">
+        <f>IF(E12=0,0,E33/E12)</f>
+        <v/>
+      </c>
+      <c r="F43" s="23">
+        <f>IF(F12=0,0,F33/F12)</f>
+        <v/>
+      </c>
+      <c r="G43" s="23">
+        <f>IF(G12=0,0,G33/G12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Equipment</t>
+        </is>
+      </c>
+      <c r="B44" s="23">
+        <f>IF(B13=0,0,B34/B13)</f>
+        <v/>
+      </c>
+      <c r="C44" s="23">
+        <f>IF(C13=0,0,C34/C13)</f>
+        <v/>
+      </c>
+      <c r="D44" s="23">
+        <f>IF(D13=0,0,D34/D13)</f>
+        <v/>
+      </c>
+      <c r="E44" s="23">
+        <f>IF(E13=0,0,E34/E13)</f>
+        <v/>
+      </c>
+      <c r="F44" s="23">
+        <f>IF(F13=0,0,F34/F13)</f>
+        <v/>
+      </c>
+      <c r="G44" s="23">
+        <f>IF(G13=0,0,G34/G13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Blended CM %</t>
+        </is>
+      </c>
+      <c r="B45" s="26">
+        <f>B35/B15</f>
+        <v/>
+      </c>
+      <c r="C45" s="26">
+        <f>C35/C15</f>
+        <v/>
+      </c>
+      <c r="D45" s="26">
+        <f>D35/D15</f>
+        <v/>
+      </c>
+      <c r="E45" s="26">
+        <f>E35/E15</f>
+        <v/>
+      </c>
+      <c r="F45" s="26">
+        <f>F35/F15</f>
+        <v/>
+      </c>
+      <c r="G45" s="26">
+        <f>G35/G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>RECONCILIATION TO GROUP EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Aggregate segment contribution</t>
+        </is>
+      </c>
+      <c r="C48" s="21">
+        <f>C35</f>
+        <v/>
+      </c>
+      <c r="D48" s="21">
+        <f>D35</f>
+        <v/>
+      </c>
+      <c r="E48" s="21">
+        <f>E35</f>
+        <v/>
+      </c>
+      <c r="F48" s="21">
+        <f>F35</f>
+        <v/>
+      </c>
+      <c r="G48" s="21">
+        <f>G35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>− IS EBITDA (group)</t>
+        </is>
+      </c>
+      <c r="C49" s="21">
+        <f>-IS!$C$28</f>
+        <v/>
+      </c>
+      <c r="D49" s="21">
+        <f>-IS!$D$28</f>
+        <v/>
+      </c>
+      <c r="E49" s="21">
+        <f>-IS!$E$28</f>
+        <v/>
+      </c>
+      <c r="F49" s="21">
+        <f>-IS!$F$28</f>
+        <v/>
+      </c>
+      <c r="G49" s="21">
+        <f>-IS!$G$28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18">
+        <f> Unallocated / shared overhead</f>
+        <v/>
+      </c>
+      <c r="C50" s="22">
+        <f>C48+C49</f>
+        <v/>
+      </c>
+      <c r="D50" s="22">
+        <f>D48+D49</f>
+        <v/>
+      </c>
+      <c r="E50" s="22">
+        <f>E48+E49</f>
+        <v/>
+      </c>
+      <c r="F50" s="22">
+        <f>F48+F49</f>
+        <v/>
+      </c>
+      <c r="G50" s="22">
+        <f>G48+G49</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1307,13 +3629,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1390,23 +3712,23 @@
         <v/>
       </c>
       <c r="C7" s="21">
-        <f>B7+CFS!C23</f>
+        <f>B7+CFS!C25</f>
         <v/>
       </c>
       <c r="D7" s="21">
-        <f>C7+CFS!D23</f>
+        <f>C7+CFS!D25</f>
         <v/>
       </c>
       <c r="E7" s="21">
-        <f>D7+CFS!E23</f>
+        <f>D7+CFS!E25</f>
         <v/>
       </c>
       <c r="F7" s="21">
-        <f>E7+CFS!F23</f>
+        <f>E7+CFS!F25</f>
         <v/>
       </c>
       <c r="G7" s="21">
-        <f>F7+CFS!G23</f>
+        <f>F7+CFS!G25</f>
         <v/>
       </c>
     </row>
@@ -1537,7 +3859,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>PP&amp;E</t>
+          <t>Property, plant &amp; equipment</t>
         </is>
       </c>
       <c r="B13" s="21">
@@ -1568,452 +3890,452 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Goodwill (flat)</t>
+          <t>Right-of-use assets (IFRS 16)</t>
         </is>
       </c>
       <c r="B14" s="21">
-        <f>Assumptions!$B$40</f>
+        <f>Leases!$B$10</f>
         <v/>
       </c>
       <c r="C14" s="21">
-        <f>B14</f>
+        <f>Leases!$C$10</f>
         <v/>
       </c>
       <c r="D14" s="21">
-        <f>C14</f>
+        <f>Leases!$D$10</f>
         <v/>
       </c>
       <c r="E14" s="21">
-        <f>D14</f>
+        <f>Leases!$E$10</f>
         <v/>
       </c>
       <c r="F14" s="21">
-        <f>E14</f>
+        <f>Leases!$F$10</f>
         <v/>
       </c>
       <c r="G14" s="21">
-        <f>F14</f>
+        <f>Leases!$G$10</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Intangibles (less amortisation)</t>
+          <t>Goodwill (flat)</t>
         </is>
       </c>
       <c r="B15" s="21">
-        <f>Assumptions!$B$41</f>
+        <f>Assumptions!$B$40</f>
         <v/>
       </c>
       <c r="C15" s="21">
-        <f>B15+IS!$C$31</f>
+        <f>B15</f>
         <v/>
       </c>
       <c r="D15" s="21">
-        <f>C15+IS!$D$31</f>
+        <f>C15</f>
         <v/>
       </c>
       <c r="E15" s="21">
-        <f>D15+IS!$E$31</f>
+        <f>D15</f>
         <v/>
       </c>
       <c r="F15" s="21">
-        <f>E15+IS!$F$31</f>
+        <f>E15</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>F15+IS!$G$31</f>
+        <f>F15</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Investments / associates (flat)</t>
+          <t>Spectrum licenses</t>
         </is>
       </c>
       <c r="B16" s="21">
-        <f>Assumptions!$B$42</f>
+        <f>Assumptions!$B$124+Assumptions!$B$126</f>
         <v/>
       </c>
       <c r="C16" s="21">
-        <f>B16</f>
+        <f>Spectrum!$C$23</f>
         <v/>
       </c>
       <c r="D16" s="21">
-        <f>C16</f>
+        <f>Spectrum!$D$23</f>
         <v/>
       </c>
       <c r="E16" s="21">
-        <f>D16</f>
+        <f>Spectrum!$E$23</f>
         <v/>
       </c>
       <c r="F16" s="21">
-        <f>E16</f>
+        <f>Spectrum!$F$23</f>
         <v/>
       </c>
       <c r="G16" s="21">
-        <f>F16</f>
+        <f>Spectrum!$G$23</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>Other intangibles (less amortisation)</t>
+        </is>
+      </c>
+      <c r="B17" s="21">
+        <f>Assumptions!$B$142</f>
+        <v/>
+      </c>
+      <c r="C17" s="21">
+        <f>B17-Assumptions!$B$118*IS!$C$14</f>
+        <v/>
+      </c>
+      <c r="D17" s="21">
+        <f>C17-Assumptions!$B$118*IS!$D$14</f>
+        <v/>
+      </c>
+      <c r="E17" s="21">
+        <f>D17-Assumptions!$B$118*IS!$E$14</f>
+        <v/>
+      </c>
+      <c r="F17" s="21">
+        <f>E17-Assumptions!$B$118*IS!$F$14</f>
+        <v/>
+      </c>
+      <c r="G17" s="21">
+        <f>F17-Assumptions!$B$118*IS!$G$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Investments / associates (flat)</t>
+        </is>
+      </c>
+      <c r="B18" s="21">
+        <f>Assumptions!$B$42</f>
+        <v/>
+      </c>
+      <c r="C18" s="21">
+        <f>B18</f>
+        <v/>
+      </c>
+      <c r="D18" s="21">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="21">
+        <f>D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="21">
+        <f>E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="21">
+        <f>F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
           <t>Deferred tax assets (flat)</t>
         </is>
       </c>
-      <c r="B17" s="21">
+      <c r="B19" s="21">
         <f>Assumptions!$B$43</f>
         <v/>
       </c>
-      <c r="C17" s="21">
-        <f>B17</f>
-        <v/>
-      </c>
-      <c r="D17" s="21">
-        <f>C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="21">
-        <f>D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="21">
-        <f>E17</f>
-        <v/>
-      </c>
-      <c r="G17" s="21">
-        <f>F17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="C19" s="21">
+        <f>B19</f>
+        <v/>
+      </c>
+      <c r="D19" s="21">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="21">
+        <f>D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="21">
+        <f>E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="21">
+        <f>F19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Total non-current assets</t>
         </is>
       </c>
-      <c r="B18" s="24">
-        <f>B13+B14+B15+B16+B17</f>
-        <v/>
-      </c>
-      <c r="C18" s="24">
-        <f>C13+C14+C15+C16+C17</f>
-        <v/>
-      </c>
-      <c r="D18" s="24">
-        <f>D13+D14+D15+D16+D17</f>
-        <v/>
-      </c>
-      <c r="E18" s="24">
-        <f>E13+E14+E15+E16+E17</f>
-        <v/>
-      </c>
-      <c r="F18" s="24">
-        <f>F13+F14+F15+F16+F17</f>
-        <v/>
-      </c>
-      <c r="G18" s="24">
-        <f>G13+G14+G15+G16+G17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="B20" s="24">
+        <f>B13+B14+B15+B16+B17+B18+B19</f>
+        <v/>
+      </c>
+      <c r="C20" s="24">
+        <f>C13+C14+C15+C16+C17+C18+C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="24">
+        <f>D13+D14+D15+D16+D17+D18+D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="24">
+        <f>E13+E14+E15+E16+E17+E18+E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="24">
+        <f>F13+F14+F15+F16+F17+F18+F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="24">
+        <f>G13+G14+G15+G16+G17+G18+G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B20" s="22">
-        <f>B11+B18</f>
-        <v/>
-      </c>
-      <c r="C20" s="22">
-        <f>C11+C18</f>
-        <v/>
-      </c>
-      <c r="D20" s="22">
-        <f>D11+D18</f>
-        <v/>
-      </c>
-      <c r="E20" s="22">
-        <f>E11+E18</f>
-        <v/>
-      </c>
-      <c r="F20" s="22">
-        <f>F11+F18</f>
-        <v/>
-      </c>
-      <c r="G20" s="22">
-        <f>G11+G18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="B22" s="22">
+        <f>B11+B20</f>
+        <v/>
+      </c>
+      <c r="C22" s="22">
+        <f>C11+C20</f>
+        <v/>
+      </c>
+      <c r="D22" s="22">
+        <f>D11+D20</f>
+        <v/>
+      </c>
+      <c r="E22" s="22">
+        <f>E11+E20</f>
+        <v/>
+      </c>
+      <c r="F22" s="22">
+        <f>F11+F20</f>
+        <v/>
+      </c>
+      <c r="G22" s="22">
+        <f>G11+G20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>LIABILITIES</t>
         </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Accounts payable</t>
-        </is>
-      </c>
-      <c r="B23" s="21">
-        <f>Assumptions!$B$46</f>
-        <v/>
-      </c>
-      <c r="C23" s="21">
-        <f>WC!$C$13</f>
-        <v/>
-      </c>
-      <c r="D23" s="21">
-        <f>WC!$D$13</f>
-        <v/>
-      </c>
-      <c r="E23" s="21">
-        <f>WC!$E$13</f>
-        <v/>
-      </c>
-      <c r="F23" s="21">
-        <f>WC!$F$13</f>
-        <v/>
-      </c>
-      <c r="G23" s="21">
-        <f>WC!$G$13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Other current liabilities (flat)</t>
-        </is>
-      </c>
-      <c r="B24" s="21">
-        <f>Assumptions!$B$47</f>
-        <v/>
-      </c>
-      <c r="C24" s="21">
-        <f>B24</f>
-        <v/>
-      </c>
-      <c r="D24" s="21">
-        <f>C24</f>
-        <v/>
-      </c>
-      <c r="E24" s="21">
-        <f>D24</f>
-        <v/>
-      </c>
-      <c r="F24" s="21">
-        <f>E24</f>
-        <v/>
-      </c>
-      <c r="G24" s="21">
-        <f>F24</f>
-        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>Accounts payable</t>
+        </is>
+      </c>
+      <c r="B25" s="21">
+        <f>Assumptions!$B$46</f>
+        <v/>
+      </c>
+      <c r="C25" s="21">
+        <f>WC!$C$13</f>
+        <v/>
+      </c>
+      <c r="D25" s="21">
+        <f>WC!$D$13</f>
+        <v/>
+      </c>
+      <c r="E25" s="21">
+        <f>WC!$E$13</f>
+        <v/>
+      </c>
+      <c r="F25" s="21">
+        <f>WC!$F$13</f>
+        <v/>
+      </c>
+      <c r="G25" s="21">
+        <f>WC!$G$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Other current liabilities (flat)</t>
+        </is>
+      </c>
+      <c r="B26" s="21">
+        <f>Assumptions!$B$47</f>
+        <v/>
+      </c>
+      <c r="C26" s="21">
+        <f>B26</f>
+        <v/>
+      </c>
+      <c r="D26" s="21">
+        <f>C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="21">
+        <f>D26</f>
+        <v/>
+      </c>
+      <c r="F26" s="21">
+        <f>E26</f>
+        <v/>
+      </c>
+      <c r="G26" s="21">
+        <f>F26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t>Short-term debt</t>
         </is>
       </c>
-      <c r="B25" s="21">
+      <c r="B27" s="21">
         <f>Debt!B6</f>
         <v/>
       </c>
-      <c r="C25" s="21">
+      <c r="C27" s="21">
         <f>Debt!C6</f>
         <v/>
       </c>
-      <c r="D25" s="21">
+      <c r="D27" s="21">
         <f>Debt!D6</f>
         <v/>
       </c>
-      <c r="E25" s="21">
+      <c r="E27" s="21">
         <f>Debt!E6</f>
         <v/>
       </c>
-      <c r="F25" s="21">
+      <c r="F27" s="21">
         <f>Debt!F6</f>
         <v/>
       </c>
-      <c r="G25" s="21">
+      <c r="G27" s="21">
         <f>Debt!G6</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Total current liabilities</t>
         </is>
       </c>
-      <c r="B26" s="24">
-        <f>B23+B24+B25</f>
-        <v/>
-      </c>
-      <c r="C26" s="24">
-        <f>C23+C24+C25</f>
-        <v/>
-      </c>
-      <c r="D26" s="24">
-        <f>D23+D24+D25</f>
-        <v/>
-      </c>
-      <c r="E26" s="24">
-        <f>E23+E24+E25</f>
-        <v/>
-      </c>
-      <c r="F26" s="24">
-        <f>F23+F24+F25</f>
-        <v/>
-      </c>
-      <c r="G26" s="24">
-        <f>G23+G24+G25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Long-term debt</t>
-        </is>
-      </c>
-      <c r="B28" s="21">
-        <f>Debt!B7</f>
-        <v/>
-      </c>
-      <c r="C28" s="21">
-        <f>Debt!C7</f>
-        <v/>
-      </c>
-      <c r="D28" s="21">
-        <f>Debt!D7</f>
-        <v/>
-      </c>
-      <c r="E28" s="21">
-        <f>Debt!E7</f>
-        <v/>
-      </c>
-      <c r="F28" s="21">
-        <f>Debt!F7</f>
-        <v/>
-      </c>
-      <c r="G28" s="21">
-        <f>Debt!G7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Lease liabilities</t>
-        </is>
-      </c>
-      <c r="B29" s="21">
-        <f>Debt!B8</f>
-        <v/>
-      </c>
-      <c r="C29" s="21">
-        <f>Debt!C8</f>
-        <v/>
-      </c>
-      <c r="D29" s="21">
-        <f>Debt!D8</f>
-        <v/>
-      </c>
-      <c r="E29" s="21">
-        <f>Debt!E8</f>
-        <v/>
-      </c>
-      <c r="F29" s="21">
-        <f>Debt!F8</f>
-        <v/>
-      </c>
-      <c r="G29" s="21">
-        <f>Debt!G8</f>
+      <c r="B28" s="24">
+        <f>B25+B26+B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="24">
+        <f>C25+C26+C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="24">
+        <f>D25+D26+D27</f>
+        <v/>
+      </c>
+      <c r="E28" s="24">
+        <f>E25+E26+E27</f>
+        <v/>
+      </c>
+      <c r="F28" s="24">
+        <f>F25+F26+F27</f>
+        <v/>
+      </c>
+      <c r="G28" s="24">
+        <f>G25+G26+G27</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Provisions (flat)</t>
+          <t>Long-term debt</t>
         </is>
       </c>
       <c r="B30" s="21">
-        <f>Assumptions!$B$51</f>
+        <f>Debt!B7</f>
         <v/>
       </c>
       <c r="C30" s="21">
-        <f>B30</f>
+        <f>Debt!C7</f>
         <v/>
       </c>
       <c r="D30" s="21">
-        <f>C30</f>
+        <f>Debt!D7</f>
         <v/>
       </c>
       <c r="E30" s="21">
-        <f>D30</f>
+        <f>Debt!E7</f>
         <v/>
       </c>
       <c r="F30" s="21">
-        <f>E30</f>
+        <f>Debt!F7</f>
         <v/>
       </c>
       <c r="G30" s="21">
-        <f>F30</f>
+        <f>Debt!G7</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Deferred tax liabilities (flat)</t>
+          <t>Lease liabilities</t>
         </is>
       </c>
       <c r="B31" s="21">
-        <f>Assumptions!$B$52</f>
+        <f>Debt!B8</f>
         <v/>
       </c>
       <c r="C31" s="21">
-        <f>B31</f>
+        <f>Debt!C8</f>
         <v/>
       </c>
       <c r="D31" s="21">
-        <f>C31</f>
+        <f>Debt!D8</f>
         <v/>
       </c>
       <c r="E31" s="21">
-        <f>D31</f>
+        <f>Debt!E8</f>
         <v/>
       </c>
       <c r="F31" s="21">
-        <f>E31</f>
+        <f>Debt!F8</f>
         <v/>
       </c>
       <c r="G31" s="21">
-        <f>F31</f>
+        <f>Debt!G8</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Other non-current liabilities (flat)</t>
+          <t>Provisions (flat)</t>
         </is>
       </c>
       <c r="B32" s="21">
-        <f>Assumptions!$B$53</f>
+        <f>Assumptions!$B$51</f>
         <v/>
       </c>
       <c r="C32" s="21">
@@ -2038,257 +4360,319 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax liabilities (flat)</t>
+        </is>
+      </c>
+      <c r="B33" s="21">
+        <f>Assumptions!$B$52</f>
+        <v/>
+      </c>
+      <c r="C33" s="21">
+        <f>B33</f>
+        <v/>
+      </c>
+      <c r="D33" s="21">
+        <f>C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="21">
+        <f>D33</f>
+        <v/>
+      </c>
+      <c r="F33" s="21">
+        <f>E33</f>
+        <v/>
+      </c>
+      <c r="G33" s="21">
+        <f>F33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Other non-current liabilities (flat)</t>
+        </is>
+      </c>
+      <c r="B34" s="21">
+        <f>Assumptions!$B$53</f>
+        <v/>
+      </c>
+      <c r="C34" s="21">
+        <f>B34</f>
+        <v/>
+      </c>
+      <c r="D34" s="21">
+        <f>C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="21">
+        <f>D34</f>
+        <v/>
+      </c>
+      <c r="F34" s="21">
+        <f>E34</f>
+        <v/>
+      </c>
+      <c r="G34" s="21">
+        <f>F34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Total non-current liabilities</t>
         </is>
       </c>
-      <c r="B33" s="24">
-        <f>B28+B29+B30+B31+B32</f>
-        <v/>
-      </c>
-      <c r="C33" s="24">
-        <f>C28+C29+C30+C31+C32</f>
-        <v/>
-      </c>
-      <c r="D33" s="24">
-        <f>D28+D29+D30+D31+D32</f>
-        <v/>
-      </c>
-      <c r="E33" s="24">
-        <f>E28+E29+E30+E31+E32</f>
-        <v/>
-      </c>
-      <c r="F33" s="24">
-        <f>F28+F29+F30+F31+F32</f>
-        <v/>
-      </c>
-      <c r="G33" s="24">
-        <f>G28+G29+G30+G31+G32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="B35" s="24">
+        <f>B30+B31+B32+B33+B34</f>
+        <v/>
+      </c>
+      <c r="C35" s="24">
+        <f>C30+C31+C32+C33+C34</f>
+        <v/>
+      </c>
+      <c r="D35" s="24">
+        <f>D30+D31+D32+D33+D34</f>
+        <v/>
+      </c>
+      <c r="E35" s="24">
+        <f>E30+E31+E32+E33+E34</f>
+        <v/>
+      </c>
+      <c r="F35" s="24">
+        <f>F30+F31+F32+F33+F34</f>
+        <v/>
+      </c>
+      <c r="G35" s="24">
+        <f>G30+G31+G32+G33+G34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>TOTAL LIABILITIES</t>
         </is>
       </c>
-      <c r="B35" s="22">
-        <f>B26+B33</f>
-        <v/>
-      </c>
-      <c r="C35" s="22">
-        <f>C26+C33</f>
-        <v/>
-      </c>
-      <c r="D35" s="22">
-        <f>D26+D33</f>
-        <v/>
-      </c>
-      <c r="E35" s="22">
-        <f>E26+E33</f>
-        <v/>
-      </c>
-      <c r="F35" s="22">
-        <f>F26+F33</f>
-        <v/>
-      </c>
-      <c r="G35" s="22">
-        <f>G26+G33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="B37" s="22">
+        <f>B28+B35</f>
+        <v/>
+      </c>
+      <c r="C37" s="22">
+        <f>C28+C35</f>
+        <v/>
+      </c>
+      <c r="D37" s="22">
+        <f>D28+D35</f>
+        <v/>
+      </c>
+      <c r="E37" s="22">
+        <f>E28+E35</f>
+        <v/>
+      </c>
+      <c r="F37" s="22">
+        <f>F28+F35</f>
+        <v/>
+      </c>
+      <c r="G37" s="22">
+        <f>G28+G35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Share capital</t>
-        </is>
-      </c>
-      <c r="B38" s="21">
-        <f>Equity!$B$6</f>
-        <v/>
-      </c>
-      <c r="C38" s="21">
-        <f>Equity!$C$6</f>
-        <v/>
-      </c>
-      <c r="D38" s="21">
-        <f>Equity!$D$6</f>
-        <v/>
-      </c>
-      <c r="E38" s="21">
-        <f>Equity!$E$6</f>
-        <v/>
-      </c>
-      <c r="F38" s="21">
-        <f>Equity!$F$6</f>
-        <v/>
-      </c>
-      <c r="G38" s="21">
-        <f>Equity!$G$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Retained earnings</t>
-        </is>
-      </c>
-      <c r="B39" s="21">
-        <f>Equity!$B$10</f>
-        <v/>
-      </c>
-      <c r="C39" s="21">
-        <f>Equity!$C$10</f>
-        <v/>
-      </c>
-      <c r="D39" s="21">
-        <f>Equity!$D$10</f>
-        <v/>
-      </c>
-      <c r="E39" s="21">
-        <f>Equity!$E$10</f>
-        <v/>
-      </c>
-      <c r="F39" s="21">
-        <f>Equity!$F$10</f>
-        <v/>
-      </c>
-      <c r="G39" s="21">
-        <f>Equity!$G$10</f>
-        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>OCI reserve</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="B40" s="21">
-        <f>Equity!$B$12</f>
+        <f>Equity!$B$6</f>
         <v/>
       </c>
       <c r="C40" s="21">
-        <f>Equity!$C$12</f>
+        <f>Equity!$C$6</f>
         <v/>
       </c>
       <c r="D40" s="21">
-        <f>Equity!$D$12</f>
+        <f>Equity!$D$6</f>
         <v/>
       </c>
       <c r="E40" s="21">
-        <f>Equity!$E$12</f>
+        <f>Equity!$E$6</f>
         <v/>
       </c>
       <c r="F40" s="21">
-        <f>Equity!$F$12</f>
+        <f>Equity!$F$6</f>
         <v/>
       </c>
       <c r="G40" s="21">
-        <f>Equity!$G$12</f>
+        <f>Equity!$G$6</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="B41" s="21">
+        <f>Equity!$B$10</f>
+        <v/>
+      </c>
+      <c r="C41" s="21">
+        <f>Equity!$C$10</f>
+        <v/>
+      </c>
+      <c r="D41" s="21">
+        <f>Equity!$D$10</f>
+        <v/>
+      </c>
+      <c r="E41" s="21">
+        <f>Equity!$E$10</f>
+        <v/>
+      </c>
+      <c r="F41" s="21">
+        <f>Equity!$F$10</f>
+        <v/>
+      </c>
+      <c r="G41" s="21">
+        <f>Equity!$G$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>OCI reserve</t>
+        </is>
+      </c>
+      <c r="B42" s="21">
+        <f>Equity!$B$12</f>
+        <v/>
+      </c>
+      <c r="C42" s="21">
+        <f>Equity!$C$12</f>
+        <v/>
+      </c>
+      <c r="D42" s="21">
+        <f>Equity!$D$12</f>
+        <v/>
+      </c>
+      <c r="E42" s="21">
+        <f>Equity!$E$12</f>
+        <v/>
+      </c>
+      <c r="F42" s="21">
+        <f>Equity!$F$12</f>
+        <v/>
+      </c>
+      <c r="G42" s="21">
+        <f>Equity!$G$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
           <t>Minority interest</t>
         </is>
       </c>
-      <c r="B41" s="21">
+      <c r="B43" s="21">
         <f>Equity!$B$13</f>
         <v/>
       </c>
-      <c r="C41" s="21">
+      <c r="C43" s="21">
         <f>Equity!$C$13</f>
         <v/>
       </c>
-      <c r="D41" s="21">
+      <c r="D43" s="21">
         <f>Equity!$D$13</f>
         <v/>
       </c>
-      <c r="E41" s="21">
+      <c r="E43" s="21">
         <f>Equity!$E$13</f>
         <v/>
       </c>
-      <c r="F41" s="21">
+      <c r="F43" s="21">
         <f>Equity!$F$13</f>
         <v/>
       </c>
-      <c r="G41" s="21">
+      <c r="G43" s="21">
         <f>Equity!$G$13</f>
         <v/>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>TOTAL EQUITY</t>
         </is>
       </c>
-      <c r="B42" s="22">
+      <c r="B44" s="22">
         <f>Equity!$B$15</f>
         <v/>
       </c>
-      <c r="C42" s="22">
+      <c r="C44" s="22">
         <f>Equity!$C$15</f>
         <v/>
       </c>
-      <c r="D42" s="22">
+      <c r="D44" s="22">
         <f>Equity!$D$15</f>
         <v/>
       </c>
-      <c r="E42" s="22">
+      <c r="E44" s="22">
         <f>Equity!$E$15</f>
         <v/>
       </c>
-      <c r="F42" s="22">
+      <c r="F44" s="22">
         <f>Equity!$F$15</f>
         <v/>
       </c>
-      <c r="G42" s="22">
+      <c r="G44" s="22">
         <f>Equity!$G$15</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Balance check (A − L − E)</t>
         </is>
       </c>
-      <c r="B44" s="24">
-        <f>B20-B35-B42</f>
-        <v/>
-      </c>
-      <c r="C44" s="24">
-        <f>C20-C35-C42</f>
-        <v/>
-      </c>
-      <c r="D44" s="24">
-        <f>D20-D35-D42</f>
-        <v/>
-      </c>
-      <c r="E44" s="24">
-        <f>E20-E35-E42</f>
-        <v/>
-      </c>
-      <c r="F44" s="24">
-        <f>F20-F35-F42</f>
-        <v/>
-      </c>
-      <c r="G44" s="24">
-        <f>G20-G35-G42</f>
+      <c r="B46" s="24">
+        <f>B22-B37-B44</f>
+        <v/>
+      </c>
+      <c r="C46" s="24">
+        <f>C22-C37-C44</f>
+        <v/>
+      </c>
+      <c r="D46" s="24">
+        <f>D22-D37-D44</f>
+        <v/>
+      </c>
+      <c r="E46" s="24">
+        <f>E22-E37-E44</f>
+        <v/>
+      </c>
+      <c r="F46" s="24">
+        <f>F22-F37-F44</f>
+        <v/>
+      </c>
+      <c r="G46" s="24">
+        <f>G22-G37-G44</f>
         <v/>
       </c>
     </row>
@@ -2297,13 +4681,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2509,7 +4893,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>− Capex</t>
+          <t>− Capex (PP&amp;E)</t>
         </is>
       </c>
       <c r="C14" s="21">
@@ -2536,223 +4920,277 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
+          <t>− Spectrum cash payments</t>
+        </is>
+      </c>
+      <c r="C15" s="21">
+        <f>-Spectrum!$C$25</f>
+        <v/>
+      </c>
+      <c r="D15" s="21">
+        <f>-Spectrum!$D$25</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>-Spectrum!$E$25</f>
+        <v/>
+      </c>
+      <c r="F15" s="21">
+        <f>-Spectrum!$F$25</f>
+        <v/>
+      </c>
+      <c r="G15" s="21">
+        <f>-Spectrum!$G$25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
           <t>Other investing (flat / nil)</t>
         </is>
       </c>
-      <c r="C15" s="21">
+      <c r="C16" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="D15" s="21">
+      <c r="D16" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="E15" s="21">
+      <c r="E16" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="F16" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="G15" s="21">
+      <c r="G16" s="21">
         <f>0</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Cash from investing (CFI)</t>
         </is>
       </c>
-      <c r="C16" s="22">
-        <f>C14+C15</f>
-        <v/>
-      </c>
-      <c r="D16" s="22">
-        <f>D14+D15</f>
-        <v/>
-      </c>
-      <c r="E16" s="22">
-        <f>E14+E15</f>
-        <v/>
-      </c>
-      <c r="F16" s="22">
-        <f>F14+F15</f>
-        <v/>
-      </c>
-      <c r="G16" s="22">
-        <f>G14+G15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="C17" s="22">
+        <f>C14+C15+C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="22">
+        <f>D14+D15+D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="22">
+        <f>E14+E15+E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="22">
+        <f>F14+F15+F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="22">
+        <f>G14+G15+G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>FINANCING</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>+/− Net debt issuance (flat assumption)</t>
-        </is>
-      </c>
-      <c r="C19" s="21">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D19" s="21">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E19" s="21">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F19" s="21">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G19" s="21">
-        <f>0</f>
-        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
+          <t>+/− Net debt issuance (flat assumption)</t>
+        </is>
+      </c>
+      <c r="C20" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D20" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E20" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F20" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G20" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>− Lease cash payments</t>
+        </is>
+      </c>
+      <c r="C21" s="21">
+        <f>Leases!$C$16</f>
+        <v/>
+      </c>
+      <c r="D21" s="21">
+        <f>Leases!$D$16</f>
+        <v/>
+      </c>
+      <c r="E21" s="21">
+        <f>Leases!$E$16</f>
+        <v/>
+      </c>
+      <c r="F21" s="21">
+        <f>Leases!$F$16</f>
+        <v/>
+      </c>
+      <c r="G21" s="21">
+        <f>Leases!$G$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
           <t>− Dividends paid</t>
         </is>
       </c>
-      <c r="C20" s="21">
+      <c r="C22" s="21">
         <f>Equity!$C$9</f>
         <v/>
       </c>
-      <c r="D20" s="21">
+      <c r="D22" s="21">
         <f>Equity!$D$9</f>
         <v/>
       </c>
-      <c r="E20" s="21">
+      <c r="E22" s="21">
         <f>Equity!$E$9</f>
         <v/>
       </c>
-      <c r="F20" s="21">
+      <c r="F22" s="21">
         <f>Equity!$F$9</f>
         <v/>
       </c>
-      <c r="G20" s="21">
+      <c r="G22" s="21">
         <f>Equity!$G$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>Cash from financing (CFF)</t>
-        </is>
-      </c>
-      <c r="C21" s="22">
-        <f>C19+C20</f>
-        <v/>
-      </c>
-      <c r="D21" s="22">
-        <f>D19+D20</f>
-        <v/>
-      </c>
-      <c r="E21" s="22">
-        <f>E19+E20</f>
-        <v/>
-      </c>
-      <c r="F21" s="22">
-        <f>F19+F20</f>
-        <v/>
-      </c>
-      <c r="G21" s="22">
-        <f>G19+G20</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
+          <t>Cash from financing (CFF)</t>
         </is>
       </c>
       <c r="C23" s="22">
-        <f>C11+C16+C21</f>
+        <f>C20+C21+C22</f>
         <v/>
       </c>
       <c r="D23" s="22">
-        <f>D11+D16+D21</f>
+        <f>D20+D21+D22</f>
         <v/>
       </c>
       <c r="E23" s="22">
-        <f>E11+E16+E21</f>
+        <f>E20+E21+E22</f>
         <v/>
       </c>
       <c r="F23" s="22">
-        <f>F11+F16+F21</f>
+        <f>F20+F21+F22</f>
         <v/>
       </c>
       <c r="G23" s="22">
-        <f>G11+G16+G21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Opening cash</t>
-        </is>
-      </c>
-      <c r="C24" s="21">
-        <f>Assumptions!$B$35</f>
-        <v/>
-      </c>
-      <c r="D24" s="21">
-        <f>C25</f>
-        <v/>
-      </c>
-      <c r="E24" s="21">
-        <f>D25</f>
-        <v/>
-      </c>
-      <c r="F24" s="21">
-        <f>E25</f>
-        <v/>
-      </c>
-      <c r="G24" s="21">
-        <f>F25</f>
+        <f>G20+G21+G22</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
+          <t>Net change in cash</t>
+        </is>
+      </c>
+      <c r="C25" s="22">
+        <f>C11+C17+C23</f>
+        <v/>
+      </c>
+      <c r="D25" s="22">
+        <f>D11+D17+D23</f>
+        <v/>
+      </c>
+      <c r="E25" s="22">
+        <f>E11+E17+E23</f>
+        <v/>
+      </c>
+      <c r="F25" s="22">
+        <f>F11+F17+F23</f>
+        <v/>
+      </c>
+      <c r="G25" s="22">
+        <f>G11+G17+G23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Opening cash</t>
+        </is>
+      </c>
+      <c r="C26" s="21">
+        <f>Assumptions!$B$35</f>
+        <v/>
+      </c>
+      <c r="D26" s="21">
+        <f>C27</f>
+        <v/>
+      </c>
+      <c r="E26" s="21">
+        <f>D27</f>
+        <v/>
+      </c>
+      <c r="F26" s="21">
+        <f>E27</f>
+        <v/>
+      </c>
+      <c r="G26" s="21">
+        <f>F27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
           <t>Closing cash</t>
         </is>
       </c>
-      <c r="C25" s="22">
-        <f>C24+C23</f>
-        <v/>
-      </c>
-      <c r="D25" s="22">
-        <f>D24+D23</f>
-        <v/>
-      </c>
-      <c r="E25" s="22">
-        <f>E24+E23</f>
-        <v/>
-      </c>
-      <c r="F25" s="22">
-        <f>F24+F23</f>
-        <v/>
-      </c>
-      <c r="G25" s="22">
-        <f>G24+G23</f>
+      <c r="C27" s="22">
+        <f>C26+C25</f>
+        <v/>
+      </c>
+      <c r="D27" s="22">
+        <f>D26+D25</f>
+        <v/>
+      </c>
+      <c r="E27" s="22">
+        <f>E26+E25</f>
+        <v/>
+      </c>
+      <c r="F27" s="22">
+        <f>F26+F25</f>
+        <v/>
+      </c>
+      <c r="G27" s="22">
+        <f>G26+G25</f>
         <v/>
       </c>
     </row>
@@ -2761,7 +5199,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4165,7 +6603,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4299,7 +6737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4621,13 +7059,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4792,7 +7230,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>− Capex</t>
+          <t>− Capex (PP&amp;E)</t>
         </is>
       </c>
       <c r="C10" s="21">
@@ -4819,225 +7257,252 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>− Spectrum cash payments</t>
+        </is>
+      </c>
+      <c r="C11" s="21">
+        <f>-Spectrum!$C$25</f>
+        <v/>
+      </c>
+      <c r="D11" s="21">
+        <f>-Spectrum!$D$25</f>
+        <v/>
+      </c>
+      <c r="E11" s="21">
+        <f>-Spectrum!$E$25</f>
+        <v/>
+      </c>
+      <c r="F11" s="21">
+        <f>-Spectrum!$F$25</f>
+        <v/>
+      </c>
+      <c r="G11" s="21">
+        <f>-Spectrum!$G$25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>+/− Δ working capital</t>
         </is>
       </c>
-      <c r="C11" s="21">
+      <c r="C12" s="21">
         <f>WC!$C$20</f>
         <v/>
       </c>
-      <c r="D11" s="21">
+      <c r="D12" s="21">
         <f>WC!$D$20</f>
         <v/>
       </c>
-      <c r="E11" s="21">
+      <c r="E12" s="21">
         <f>WC!$E$20</f>
         <v/>
       </c>
-      <c r="F11" s="21">
+      <c r="F12" s="21">
         <f>WC!$F$20</f>
         <v/>
       </c>
-      <c r="G11" s="21">
+      <c r="G12" s="21">
         <f>WC!$G$20</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>FCFF</t>
         </is>
       </c>
-      <c r="C12" s="22">
-        <f>C7+C8+C9+C10+C11</f>
-        <v/>
-      </c>
-      <c r="D12" s="22">
-        <f>D7+D8+D9+D10+D11</f>
-        <v/>
-      </c>
-      <c r="E12" s="22">
-        <f>E7+E8+E9+E10+E11</f>
-        <v/>
-      </c>
-      <c r="F12" s="22">
-        <f>F7+F8+F9+F10+F11</f>
-        <v/>
-      </c>
-      <c r="G12" s="22">
-        <f>G7+G8+G9+G10+G11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="C13" s="22">
+        <f>C7+C8+C9+C10+C11+C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="22">
+        <f>D7+D8+D9+D10+D11+D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="22">
+        <f>E7+E8+E9+E10+E11+E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="22">
+        <f>F7+F8+F9+F10+F11+F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="22">
+        <f>G7+G8+G9+G10+G11+G12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Discount factor (1/(1+WACC)^t)</t>
         </is>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f>1/(1+Assumptions!$B$21)^1</f>
         <v/>
       </c>
-      <c r="D14" s="29">
+      <c r="D15" s="29">
         <f>1/(1+Assumptions!$B$21)^2</f>
         <v/>
       </c>
-      <c r="E14" s="29">
+      <c r="E15" s="29">
         <f>1/(1+Assumptions!$B$21)^3</f>
         <v/>
       </c>
-      <c r="F14" s="29">
+      <c r="F15" s="29">
         <f>1/(1+Assumptions!$B$21)^4</f>
         <v/>
       </c>
-      <c r="G14" s="29">
+      <c r="G15" s="29">
         <f>1/(1+Assumptions!$B$21)^5</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="C15" s="24">
-        <f>C12*C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="24">
-        <f>D12*D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="24">
-        <f>E12*E14</f>
-        <v/>
-      </c>
-      <c r="F15" s="24">
-        <f>F12*F14</f>
-        <v/>
-      </c>
-      <c r="G15" s="24">
-        <f>G12*G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="C16" s="24">
+        <f>C13*C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="24">
+        <f>D13*D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>E13*E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="24">
+        <f>F13*F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="24">
+        <f>G13*G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Sum PV (explicit Y1-Y5)</t>
         </is>
       </c>
-      <c r="B17" s="24">
-        <f>SUM(C15:G15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="B18" s="24">
+        <f>SUM(C16:G16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B18" s="21">
-        <f>G12*(1+Assumptions!$B$22)/(Assumptions!$B$21-Assumptions!$B$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="B19" s="21">
+        <f>G13*(1+Assumptions!$B$22)/(Assumptions!$B$21-Assumptions!$B$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B19" s="24">
-        <f>B18*G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="B20" s="24">
+        <f>B19*G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B21" s="22">
-        <f>B17+B19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="B22" s="22">
+        <f>B18+B20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>− Net debt (Y0)</t>
         </is>
       </c>
-      <c r="B22" s="21">
+      <c r="B23" s="21">
         <f>-Debt!$B$14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>EQUITY VALUE</t>
-        </is>
-      </c>
-      <c r="B23" s="22">
-        <f>B21+B22</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
+          <t>EQUITY VALUE</t>
+        </is>
+      </c>
+      <c r="B24" s="22">
+        <f>B22+B23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
           <t>Per-share value (SAR)</t>
         </is>
       </c>
-      <c r="B24" s="30">
-        <f>B23*1000/Assumptions!$B$32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="B25" s="30">
+        <f>B24*1000/Assumptions!$B$32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Cross-checks</t>
         </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Implied FY+1 EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="B27" s="31">
-        <f>B21/IS!$C$28</f>
-        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Implied FY+1 EV/EBIT</t>
+          <t>Implied FY+1 EV/EBITDA</t>
         </is>
       </c>
       <c r="B28" s="31">
-        <f>B21/IS!$C$32</f>
+        <f>B22/IS!$C$28</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
+          <t>Implied FY+1 EV/EBIT</t>
+        </is>
+      </c>
+      <c r="B29" s="31">
+        <f>B22/IS!$C$32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
           <t>Implied FY+1 P/E</t>
         </is>
       </c>
-      <c r="B29" s="31">
-        <f>B23/IS!$C$40</f>
+      <c r="B30" s="31">
+        <f>B24/IS!$C$40</f>
         <v/>
       </c>
     </row>
@@ -5046,7 +7511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5120,27 +7585,27 @@
         </is>
       </c>
       <c r="B6" s="32">
-        <f>IF(ABS(BS!B44)&lt;0.01,"PASS","FAIL: "&amp;TEXT(BS!B44,"+0.00;-0.00"))</f>
+        <f>IF(ABS(BS!B46)&lt;0.01,"PASS","FAIL: "&amp;TEXT(BS!B46,"+0.00;-0.00"))</f>
         <v/>
       </c>
       <c r="C6" s="32">
-        <f>IF(ABS(BS!C44)&lt;0.01,"PASS","FAIL: "&amp;TEXT(BS!C44,"+0.00;-0.00"))</f>
+        <f>IF(ABS(BS!C46)&lt;0.01,"PASS","FAIL: "&amp;TEXT(BS!C46,"+0.00;-0.00"))</f>
         <v/>
       </c>
       <c r="D6" s="32">
-        <f>IF(ABS(BS!D44)&lt;0.01,"PASS","FAIL: "&amp;TEXT(BS!D44,"+0.00;-0.00"))</f>
+        <f>IF(ABS(BS!D46)&lt;0.01,"PASS","FAIL: "&amp;TEXT(BS!D46,"+0.00;-0.00"))</f>
         <v/>
       </c>
       <c r="E6" s="32">
-        <f>IF(ABS(BS!E44)&lt;0.01,"PASS","FAIL: "&amp;TEXT(BS!E44,"+0.00;-0.00"))</f>
+        <f>IF(ABS(BS!E46)&lt;0.01,"PASS","FAIL: "&amp;TEXT(BS!E46,"+0.00;-0.00"))</f>
         <v/>
       </c>
       <c r="F6" s="32">
-        <f>IF(ABS(BS!F44)&lt;0.01,"PASS","FAIL: "&amp;TEXT(BS!F44,"+0.00;-0.00"))</f>
+        <f>IF(ABS(BS!F46)&lt;0.01,"PASS","FAIL: "&amp;TEXT(BS!F46,"+0.00;-0.00"))</f>
         <v/>
       </c>
       <c r="G6" s="32">
-        <f>IF(ABS(BS!G44)&lt;0.01,"PASS","FAIL: "&amp;TEXT(BS!G44,"+0.00;-0.00"))</f>
+        <f>IF(ABS(BS!G46)&lt;0.01,"PASS","FAIL: "&amp;TEXT(BS!G46,"+0.00;-0.00"))</f>
         <v/>
       </c>
     </row>
@@ -5151,23 +7616,23 @@
         </is>
       </c>
       <c r="C7" s="32">
-        <f>IF(ABS(BS!C7-CFS!C25)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(BS!C7-CFS!C27)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="D7" s="32">
-        <f>IF(ABS(BS!D7-CFS!D25)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(BS!D7-CFS!D27)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="E7" s="32">
-        <f>IF(ABS(BS!E7-CFS!E25)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(BS!E7-CFS!E27)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="F7" s="32">
-        <f>IF(ABS(BS!F7-CFS!F25)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(BS!F7-CFS!F27)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="G7" s="32">
-        <f>IF(ABS(BS!G7-CFS!G25)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(BS!G7-CFS!G27)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -5178,27 +7643,27 @@
         </is>
       </c>
       <c r="B8" s="32">
-        <f>IF(ABS(Equity!B15-BS!B42)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(Equity!B15-BS!B44)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="C8" s="32">
-        <f>IF(ABS(Equity!C15-BS!C42)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(Equity!C15-BS!C44)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="D8" s="32">
-        <f>IF(ABS(Equity!D15-BS!D42)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(Equity!D15-BS!D44)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="E8" s="32">
-        <f>IF(ABS(Equity!E15-BS!E42)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(Equity!E15-BS!E44)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="F8" s="32">
-        <f>IF(ABS(Equity!F15-BS!F42)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(Equity!F15-BS!F44)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="G8" s="32">
-        <f>IF(ABS(Equity!G15-BS!G42)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(Equity!G15-BS!G44)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -5279,7 +7744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -5705,7 +8170,7 @@
         </is>
       </c>
       <c r="B39" s="9" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -6500,7 +8965,7 @@
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>Intangibles amortisation</t>
+          <t>Intangibles amortisation (ex-spectrum)</t>
         </is>
       </c>
       <c r="B118" s="10" t="n">
@@ -6508,7 +8973,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Ex-spectrum (spectrum schedule comes in Phase 2).</t>
+          <t>Other intangibles only; spectrum lives on its own schedule.</t>
         </is>
       </c>
     </row>
@@ -6549,6 +9014,222 @@
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>Vodafone Egypt 49% non-controlling interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>PHASE 2 — Spectrum licenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>Cohort 1 — pre-2020 NBV (SAR bn)</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Mostly amortised legacy 2G/3G spectrum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>Cohort 1 — remaining life (yrs)</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>Cohort 2 — 2020-2024 NBV</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>4G refarm + initial 5G allocations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>Cohort 2 — remaining life (yrs)</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>Cohort 3 — cash payment year</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Year of next major 5G mid-band auction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>Cohort 3 — cash payment (SAR bn)</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Lump-sum auction cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>Cohort 3 — amortisation life</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>PHASE 2 — Leases (IFRS 16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>Right-of-use asset Y0 (SAR bn)</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Carved out of original PPE Y0 = 80.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>Average lease term (years)</t>
+        </is>
+      </c>
+      <c r="B134" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Drives ROU depreciation rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Implicit lease rate</t>
+        </is>
+      </c>
+      <c r="B135" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Interest accretion on lease liabilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>New lease additions / year (SAR bn)</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Annual lease take-on (non-cash).</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>PHASE 2 — PP&amp;E depreciation</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>PP&amp;E annual depreciation rate</t>
+        </is>
+      </c>
+      <c r="B139" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Applied to opening NBV (blended useful-life).</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>Capex maintenance share</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Growth = 1 − maintenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>Other intangibles Y0 (SAR bn)</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Brand, software, customer lists (ex-spectrum).</t>
         </is>
       </c>
     </row>
@@ -7561,6 +10242,844 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>SPECTRUM LICENSE SCHEDULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Three cohorts. Cohort 1 &amp; 2 are on the books at Y0 and amortise from there. Cohort 3 lands as a lumpy cash payment in year c3_cash_y, then amortises over its license term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n"/>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Y0 (base)</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>COHORT 1 — Pre-2020 legacy 2G/3G</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening NBV</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="C7" s="21">
+        <f>Assumptions!$B$124</f>
+        <v/>
+      </c>
+      <c r="D7" s="21">
+        <f>C9</f>
+        <v/>
+      </c>
+      <c r="E7" s="21">
+        <f>D9</f>
+        <v/>
+      </c>
+      <c r="F7" s="21">
+        <f>E9</f>
+        <v/>
+      </c>
+      <c r="G7" s="21">
+        <f>F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Annual amortisation</t>
+        </is>
+      </c>
+      <c r="C8" s="21">
+        <f>-MIN((Assumptions!$B$124/Assumptions!$B$125),C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="21">
+        <f>-MIN((Assumptions!$B$124/Assumptions!$B$125),D7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="21">
+        <f>-MIN((Assumptions!$B$124/Assumptions!$B$125),E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="21">
+        <f>-MIN((Assumptions!$B$124/Assumptions!$B$125),F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="21">
+        <f>-MIN((Assumptions!$B$124/Assumptions!$B$125),G7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Closing NBV</t>
+        </is>
+      </c>
+      <c r="B9" s="22">
+        <f>Assumptions!$B$124</f>
+        <v/>
+      </c>
+      <c r="C9" s="22">
+        <f>C7+C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="22">
+        <f>D7+D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="22">
+        <f>E7+E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="22">
+        <f>F7+F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="22">
+        <f>G7+G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>COHORT 2 — 2020-2024 licenses (4G refarm + initial 5G)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening NBV</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="C12" s="21">
+        <f>Assumptions!$B$126</f>
+        <v/>
+      </c>
+      <c r="D12" s="21">
+        <f>C14</f>
+        <v/>
+      </c>
+      <c r="E12" s="21">
+        <f>D14</f>
+        <v/>
+      </c>
+      <c r="F12" s="21">
+        <f>E14</f>
+        <v/>
+      </c>
+      <c r="G12" s="21">
+        <f>F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Annual amortisation</t>
+        </is>
+      </c>
+      <c r="C13" s="21">
+        <f>-MIN((Assumptions!$B$126/Assumptions!$B$127),C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="21">
+        <f>-MIN((Assumptions!$B$126/Assumptions!$B$127),D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>-MIN((Assumptions!$B$126/Assumptions!$B$127),E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>-MIN((Assumptions!$B$126/Assumptions!$B$127),F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="21">
+        <f>-MIN((Assumptions!$B$126/Assumptions!$B$127),G12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Closing NBV</t>
+        </is>
+      </c>
+      <c r="B14" s="22">
+        <f>Assumptions!$B$126</f>
+        <v/>
+      </c>
+      <c r="C14" s="22">
+        <f>C12+C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="22">
+        <f>D12+D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="22">
+        <f>E12+E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="22">
+        <f>F12+F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="22">
+        <f>G12+G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>COHORT 3 — Future 5G mid-band (auction in year c3_cash_y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cash payment (auction)</t>
+        </is>
+      </c>
+      <c r="B17" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C17" s="21">
+        <f>IF(1=Assumptions!$B$128,Assumptions!$B$129,0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="21">
+        <f>IF(2=Assumptions!$B$128,Assumptions!$B$129,0)</f>
+        <v/>
+      </c>
+      <c r="E17" s="21">
+        <f>IF(3=Assumptions!$B$128,Assumptions!$B$129,0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="21">
+        <f>IF(4=Assumptions!$B$128,Assumptions!$B$129,0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="21">
+        <f>IF(5=Assumptions!$B$128,Assumptions!$B$129,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening NBV (+ current-year cash)</t>
+        </is>
+      </c>
+      <c r="B18" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C18" s="21">
+        <f>0+C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="21">
+        <f>C20+D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="21">
+        <f>D20+E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="21">
+        <f>E20+F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="21">
+        <f>F20+G17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Annual amortisation</t>
+        </is>
+      </c>
+      <c r="C19" s="21">
+        <f>IF(C18&gt;0,-MIN((Assumptions!$B$129/Assumptions!$B$130),C18),0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="21">
+        <f>IF(D18&gt;0,-MIN((Assumptions!$B$129/Assumptions!$B$130),D18),0)</f>
+        <v/>
+      </c>
+      <c r="E19" s="21">
+        <f>IF(E18&gt;0,-MIN((Assumptions!$B$129/Assumptions!$B$130),E18),0)</f>
+        <v/>
+      </c>
+      <c r="F19" s="21">
+        <f>IF(F18&gt;0,-MIN((Assumptions!$B$129/Assumptions!$B$130),F18),0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="21">
+        <f>IF(G18&gt;0,-MIN((Assumptions!$B$129/Assumptions!$B$130),G18),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Closing NBV</t>
+        </is>
+      </c>
+      <c r="B20" s="22">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C20" s="22">
+        <f>C18+C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="22">
+        <f>D18+D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="22">
+        <f>E18+E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="22">
+        <f>F18+F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="22">
+        <f>G18+G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>Total spectrum NBV (to BS)</t>
+        </is>
+      </c>
+      <c r="B23" s="22">
+        <f>B9+B14+B20</f>
+        <v/>
+      </c>
+      <c r="C23" s="22">
+        <f>C9+C14+C20</f>
+        <v/>
+      </c>
+      <c r="D23" s="22">
+        <f>D9+D14+D20</f>
+        <v/>
+      </c>
+      <c r="E23" s="22">
+        <f>E9+E14+E20</f>
+        <v/>
+      </c>
+      <c r="F23" s="22">
+        <f>F9+F14+F20</f>
+        <v/>
+      </c>
+      <c r="G23" s="22">
+        <f>G9+G14+G20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Total amortisation (to IS)</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="C24" s="24">
+        <f>C8+C13+C19</f>
+        <v/>
+      </c>
+      <c r="D24" s="24">
+        <f>D8+D13+D19</f>
+        <v/>
+      </c>
+      <c r="E24" s="24">
+        <f>E8+E13+E19</f>
+        <v/>
+      </c>
+      <c r="F24" s="24">
+        <f>F8+F13+F19</f>
+        <v/>
+      </c>
+      <c r="G24" s="24">
+        <f>G8+G13+G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Total cash payments (to CFS)</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="C25" s="21">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="D25" s="21">
+        <f>D17</f>
+        <v/>
+      </c>
+      <c r="E25" s="21">
+        <f>E17</f>
+        <v/>
+      </c>
+      <c r="F25" s="21">
+        <f>F17</f>
+        <v/>
+      </c>
+      <c r="G25" s="21">
+        <f>G17</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>IFRS 16 LEASE SCHEDULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Right-of-use asset and lease liability rollforward. Additions are non-cash; cash payments hit CFS financing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n"/>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Y0 (base)</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>RIGHT-OF-USE ASSET</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening ROU</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="C7" s="21">
+        <f>Assumptions!$B$133</f>
+        <v/>
+      </c>
+      <c r="D7" s="21">
+        <f>C10</f>
+        <v/>
+      </c>
+      <c r="E7" s="21">
+        <f>D10</f>
+        <v/>
+      </c>
+      <c r="F7" s="21">
+        <f>E10</f>
+        <v/>
+      </c>
+      <c r="G7" s="21">
+        <f>F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + New lease additions</t>
+        </is>
+      </c>
+      <c r="C8" s="21">
+        <f>Assumptions!$B$136</f>
+        <v/>
+      </c>
+      <c r="D8" s="21">
+        <f>Assumptions!$B$136</f>
+        <v/>
+      </c>
+      <c r="E8" s="21">
+        <f>Assumptions!$B$136</f>
+        <v/>
+      </c>
+      <c r="F8" s="21">
+        <f>Assumptions!$B$136</f>
+        <v/>
+      </c>
+      <c r="G8" s="21">
+        <f>Assumptions!$B$136</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − ROU depreciation</t>
+        </is>
+      </c>
+      <c r="C9" s="21">
+        <f>-(C7+C8)/Assumptions!$B$134</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
+        <f>-(D7+D8)/Assumptions!$B$134</f>
+        <v/>
+      </c>
+      <c r="E9" s="21">
+        <f>-(E7+E8)/Assumptions!$B$134</f>
+        <v/>
+      </c>
+      <c r="F9" s="21">
+        <f>-(F7+F8)/Assumptions!$B$134</f>
+        <v/>
+      </c>
+      <c r="G9" s="21">
+        <f>-(G7+G8)/Assumptions!$B$134</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Closing ROU</t>
+        </is>
+      </c>
+      <c r="B10" s="22">
+        <f>Assumptions!$B$133</f>
+        <v/>
+      </c>
+      <c r="C10" s="22">
+        <f>C7+C8+C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="22">
+        <f>D7+D8+D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="22">
+        <f>E7+E8+E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="22">
+        <f>F7+F8+F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="22">
+        <f>G7+G8+G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>LEASE LIABILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening lease liability</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="C13" s="21">
+        <f>Assumptions!$B$50</f>
+        <v/>
+      </c>
+      <c r="D13" s="21">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>D17</f>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>E17</f>
+        <v/>
+      </c>
+      <c r="G13" s="21">
+        <f>F17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + Interest accretion</t>
+        </is>
+      </c>
+      <c r="C14" s="21">
+        <f>C13*Assumptions!$B$135</f>
+        <v/>
+      </c>
+      <c r="D14" s="21">
+        <f>D13*Assumptions!$B$135</f>
+        <v/>
+      </c>
+      <c r="E14" s="21">
+        <f>E13*Assumptions!$B$135</f>
+        <v/>
+      </c>
+      <c r="F14" s="21">
+        <f>F13*Assumptions!$B$135</f>
+        <v/>
+      </c>
+      <c r="G14" s="21">
+        <f>G13*Assumptions!$B$135</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + New lease additions</t>
+        </is>
+      </c>
+      <c r="C15" s="21">
+        <f>C8</f>
+        <v/>
+      </c>
+      <c r="D15" s="21">
+        <f>D8</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>E8</f>
+        <v/>
+      </c>
+      <c r="F15" s="21">
+        <f>F8</f>
+        <v/>
+      </c>
+      <c r="G15" s="21">
+        <f>G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Cash payments</t>
+        </is>
+      </c>
+      <c r="C16" s="21">
+        <f>C9-C14</f>
+        <v/>
+      </c>
+      <c r="D16" s="21">
+        <f>D9-D14</f>
+        <v/>
+      </c>
+      <c r="E16" s="21">
+        <f>E9-E14</f>
+        <v/>
+      </c>
+      <c r="F16" s="21">
+        <f>F9-F14</f>
+        <v/>
+      </c>
+      <c r="G16" s="21">
+        <f>G9-G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Closing lease liability</t>
+        </is>
+      </c>
+      <c r="B17" s="22">
+        <f>Assumptions!$B$50</f>
+        <v/>
+      </c>
+      <c r="C17" s="22">
+        <f>C13+C14+C15+C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="22">
+        <f>D13+D14+D15+D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="22">
+        <f>E13+E14+E15+E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="22">
+        <f>F13+F14+F15+F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="22">
+        <f>G13+G14+G15+G16</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7685,31 +11204,31 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities (IFRS 16)</t>
+          <t>Lease liabilities (from Leases sheet)</t>
         </is>
       </c>
       <c r="B8" s="21">
-        <f>Assumptions!$B$50</f>
+        <f>Leases!$B$17</f>
         <v/>
       </c>
       <c r="C8" s="21">
-        <f>B8</f>
+        <f>Leases!$C$17</f>
         <v/>
       </c>
       <c r="D8" s="21">
-        <f>C8</f>
+        <f>Leases!$D$17</f>
         <v/>
       </c>
       <c r="E8" s="21">
-        <f>D8</f>
+        <f>Leases!$E$17</f>
         <v/>
       </c>
       <c r="F8" s="21">
-        <f>E8</f>
+        <f>Leases!$F$17</f>
         <v/>
       </c>
       <c r="G8" s="21">
-        <f>F8</f>
+        <f>Leases!$G$17</f>
         <v/>
       </c>
     </row>
@@ -7809,27 +11328,27 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Interest expense (= kd × opening gross debt)</t>
+          <t>Interest expense (= kd × opening ST + LT debt)</t>
         </is>
       </c>
       <c r="C16" s="21">
-        <f>Assumptions!$B$23*B10</f>
+        <f>Assumptions!$B$23*(B6+B7)</f>
         <v/>
       </c>
       <c r="D16" s="21">
-        <f>Assumptions!$B$23*C10</f>
+        <f>Assumptions!$B$23*(C6+C7)</f>
         <v/>
       </c>
       <c r="E16" s="21">
-        <f>Assumptions!$B$23*D10</f>
+        <f>Assumptions!$B$23*(D6+D7)</f>
         <v/>
       </c>
       <c r="F16" s="21">
-        <f>Assumptions!$B$23*E10</f>
+        <f>Assumptions!$B$23*(E6+E7)</f>
         <v/>
       </c>
       <c r="G16" s="21">
-        <f>Assumptions!$B$23*F10</f>
+        <f>Assumptions!$B$23*(F6+F7)</f>
         <v/>
       </c>
     </row>
@@ -7838,7 +11357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7965,27 +11484,27 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>− Depreciation &amp; amortisation</t>
+          <t>− Depreciation (PP&amp;E only)</t>
         </is>
       </c>
       <c r="C8" s="21">
-        <f>-Assumptions!$B$8*IS!$C$14</f>
+        <f>-C6*Assumptions!$B$139</f>
         <v/>
       </c>
       <c r="D8" s="21">
-        <f>-Assumptions!$B$8*IS!$D$14</f>
+        <f>-D6*Assumptions!$B$139</f>
         <v/>
       </c>
       <c r="E8" s="21">
-        <f>-Assumptions!$B$8*IS!$E$14</f>
+        <f>-E6*Assumptions!$B$139</f>
         <v/>
       </c>
       <c r="F8" s="21">
-        <f>-Assumptions!$B$8*IS!$F$14</f>
+        <f>-F6*Assumptions!$B$139</f>
         <v/>
       </c>
       <c r="G8" s="21">
-        <f>-Assumptions!$B$8*IS!$G$14</f>
+        <f>-G6*Assumptions!$B$139</f>
         <v/>
       </c>
     </row>
@@ -8025,7 +11544,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8379,7 +11898,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8523,2324 +12042,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>INCOME STATEMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Segment-disclosed revenue + 10-line cost split + finance items + tax + attributable NI + EPS. All figures SAR billion, EPS in SAR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="n"/>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="G4" s="15" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Mobile postpaid</t>
-        </is>
-      </c>
-      <c r="C6" s="21">
-        <f>Drivers!$C$31</f>
-        <v/>
-      </c>
-      <c r="D6" s="21">
-        <f>Drivers!$D$31</f>
-        <v/>
-      </c>
-      <c r="E6" s="21">
-        <f>Drivers!$E$31</f>
-        <v/>
-      </c>
-      <c r="F6" s="21">
-        <f>Drivers!$F$31</f>
-        <v/>
-      </c>
-      <c r="G6" s="21">
-        <f>Drivers!$G$31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Mobile prepaid</t>
-        </is>
-      </c>
-      <c r="C7" s="21">
-        <f>Drivers!$C$32</f>
-        <v/>
-      </c>
-      <c r="D7" s="21">
-        <f>Drivers!$D$32</f>
-        <v/>
-      </c>
-      <c r="E7" s="21">
-        <f>Drivers!$E$32</f>
-        <v/>
-      </c>
-      <c r="F7" s="21">
-        <f>Drivers!$F$32</f>
-        <v/>
-      </c>
-      <c r="G7" s="21">
-        <f>Drivers!$G$32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Fixed broadband</t>
-        </is>
-      </c>
-      <c r="C8" s="21">
-        <f>Drivers!$C$33</f>
-        <v/>
-      </c>
-      <c r="D8" s="21">
-        <f>Drivers!$D$33</f>
-        <v/>
-      </c>
-      <c r="E8" s="21">
-        <f>Drivers!$E$33</f>
-        <v/>
-      </c>
-      <c r="F8" s="21">
-        <f>Drivers!$F$33</f>
-        <v/>
-      </c>
-      <c r="G8" s="21">
-        <f>Drivers!$G$33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B2B connectivity</t>
-        </is>
-      </c>
-      <c r="C9" s="21">
-        <f>Drivers!$C$34</f>
-        <v/>
-      </c>
-      <c r="D9" s="21">
-        <f>Drivers!$D$34</f>
-        <v/>
-      </c>
-      <c r="E9" s="21">
-        <f>Drivers!$E$34</f>
-        <v/>
-      </c>
-      <c r="F9" s="21">
-        <f>Drivers!$F$34</f>
-        <v/>
-      </c>
-      <c r="G9" s="21">
-        <f>Drivers!$G$34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ICT / cloud</t>
-        </is>
-      </c>
-      <c r="C10" s="21">
-        <f>Drivers!$C$35</f>
-        <v/>
-      </c>
-      <c r="D10" s="21">
-        <f>Drivers!$D$35</f>
-        <v/>
-      </c>
-      <c r="E10" s="21">
-        <f>Drivers!$E$35</f>
-        <v/>
-      </c>
-      <c r="F10" s="21">
-        <f>Drivers!$F$35</f>
-        <v/>
-      </c>
-      <c r="G10" s="21">
-        <f>Drivers!$G$35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Wholesale</t>
-        </is>
-      </c>
-      <c r="C11" s="21">
-        <f>Drivers!$C$36</f>
-        <v/>
-      </c>
-      <c r="D11" s="21">
-        <f>Drivers!$D$36</f>
-        <v/>
-      </c>
-      <c r="E11" s="21">
-        <f>Drivers!$E$36</f>
-        <v/>
-      </c>
-      <c r="F11" s="21">
-        <f>Drivers!$F$36</f>
-        <v/>
-      </c>
-      <c r="G11" s="21">
-        <f>Drivers!$G$36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Total service revenue</t>
-        </is>
-      </c>
-      <c r="C12" s="24">
-        <f>C6+C7+C8+C9+C10+C11</f>
-        <v/>
-      </c>
-      <c r="D12" s="24">
-        <f>D6+D7+D8+D9+D10+D11</f>
-        <v/>
-      </c>
-      <c r="E12" s="24">
-        <f>E6+E7+E8+E9+E10+E11</f>
-        <v/>
-      </c>
-      <c r="F12" s="24">
-        <f>F6+F7+F8+F9+F10+F11</f>
-        <v/>
-      </c>
-      <c r="G12" s="24">
-        <f>G6+G7+G8+G9+G10+G11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Equipment / handset revenue</t>
-        </is>
-      </c>
-      <c r="C13" s="21">
-        <f>Drivers!$C$39</f>
-        <v/>
-      </c>
-      <c r="D13" s="21">
-        <f>Drivers!$D$39</f>
-        <v/>
-      </c>
-      <c r="E13" s="21">
-        <f>Drivers!$E$39</f>
-        <v/>
-      </c>
-      <c r="F13" s="21">
-        <f>Drivers!$F$39</f>
-        <v/>
-      </c>
-      <c r="G13" s="21">
-        <f>Drivers!$G$39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL REVENUE</t>
-        </is>
-      </c>
-      <c r="C14" s="22">
-        <f>C12+C13</f>
-        <v/>
-      </c>
-      <c r="D14" s="22">
-        <f>D12+D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="22">
-        <f>E12+E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="22">
-        <f>F12+F13</f>
-        <v/>
-      </c>
-      <c r="G14" s="22">
-        <f>G12+G13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING COSTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Interconnect &amp; roaming</t>
-        </is>
-      </c>
-      <c r="C17" s="21">
-        <f>-Assumptions!$B$109*C14</f>
-        <v/>
-      </c>
-      <c r="D17" s="21">
-        <f>-Assumptions!$B$109*D14</f>
-        <v/>
-      </c>
-      <c r="E17" s="21">
-        <f>-Assumptions!$B$109*E14</f>
-        <v/>
-      </c>
-      <c r="F17" s="21">
-        <f>-Assumptions!$B$109*F14</f>
-        <v/>
-      </c>
-      <c r="G17" s="21">
-        <f>-Assumptions!$B$109*G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Content / OTT licensing</t>
-        </is>
-      </c>
-      <c r="C18" s="21">
-        <f>-Assumptions!$B$110*C14</f>
-        <v/>
-      </c>
-      <c r="D18" s="21">
-        <f>-Assumptions!$B$110*D14</f>
-        <v/>
-      </c>
-      <c r="E18" s="21">
-        <f>-Assumptions!$B$110*E14</f>
-        <v/>
-      </c>
-      <c r="F18" s="21">
-        <f>-Assumptions!$B$110*F14</f>
-        <v/>
-      </c>
-      <c r="G18" s="21">
-        <f>-Assumptions!$B$110*G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Equipment COGS</t>
-        </is>
-      </c>
-      <c r="C19" s="21">
-        <f>-C13*(1-Assumptions!$B$106)</f>
-        <v/>
-      </c>
-      <c r="D19" s="21">
-        <f>-D13*(1-Assumptions!$B$106)</f>
-        <v/>
-      </c>
-      <c r="E19" s="21">
-        <f>-E13*(1-Assumptions!$B$106)</f>
-        <v/>
-      </c>
-      <c r="F19" s="21">
-        <f>-F13*(1-Assumptions!$B$106)</f>
-        <v/>
-      </c>
-      <c r="G19" s="21">
-        <f>-G13*(1-Assumptions!$B$106)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Network energy + site lease</t>
-        </is>
-      </c>
-      <c r="C20" s="21">
-        <f>-Assumptions!$B$111*C14</f>
-        <v/>
-      </c>
-      <c r="D20" s="21">
-        <f>-Assumptions!$B$111*D14</f>
-        <v/>
-      </c>
-      <c r="E20" s="21">
-        <f>-Assumptions!$B$111*E14</f>
-        <v/>
-      </c>
-      <c r="F20" s="21">
-        <f>-Assumptions!$B$111*F14</f>
-        <v/>
-      </c>
-      <c r="G20" s="21">
-        <f>-Assumptions!$B$111*G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Other network opex</t>
-        </is>
-      </c>
-      <c r="C21" s="21">
-        <f>-Assumptions!$B$112*C14</f>
-        <v/>
-      </c>
-      <c r="D21" s="21">
-        <f>-Assumptions!$B$112*D14</f>
-        <v/>
-      </c>
-      <c r="E21" s="21">
-        <f>-Assumptions!$B$112*E14</f>
-        <v/>
-      </c>
-      <c r="F21" s="21">
-        <f>-Assumptions!$B$112*F14</f>
-        <v/>
-      </c>
-      <c r="G21" s="21">
-        <f>-Assumptions!$B$112*G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Employee costs</t>
-        </is>
-      </c>
-      <c r="C22" s="21">
-        <f>-Assumptions!$B$14*C14</f>
-        <v/>
-      </c>
-      <c r="D22" s="21">
-        <f>-Assumptions!$B$14*D14</f>
-        <v/>
-      </c>
-      <c r="E22" s="21">
-        <f>-Assumptions!$B$14*E14</f>
-        <v/>
-      </c>
-      <c r="F22" s="21">
-        <f>-Assumptions!$B$14*F14</f>
-        <v/>
-      </c>
-      <c r="G22" s="21">
-        <f>-Assumptions!$B$14*G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Customer acquisition (commissions, subsidies)</t>
-        </is>
-      </c>
-      <c r="C23" s="21">
-        <f>-Assumptions!$B$15*C14</f>
-        <v/>
-      </c>
-      <c r="D23" s="21">
-        <f>-Assumptions!$B$15*D14</f>
-        <v/>
-      </c>
-      <c r="E23" s="21">
-        <f>-Assumptions!$B$15*E14</f>
-        <v/>
-      </c>
-      <c r="F23" s="21">
-        <f>-Assumptions!$B$15*F14</f>
-        <v/>
-      </c>
-      <c r="G23" s="21">
-        <f>-Assumptions!$B$15*G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Other commercial / marketing</t>
-        </is>
-      </c>
-      <c r="C24" s="21">
-        <f>-Assumptions!$B$113*C14</f>
-        <v/>
-      </c>
-      <c r="D24" s="21">
-        <f>-Assumptions!$B$113*D14</f>
-        <v/>
-      </c>
-      <c r="E24" s="21">
-        <f>-Assumptions!$B$113*E14</f>
-        <v/>
-      </c>
-      <c r="F24" s="21">
-        <f>-Assumptions!$B$113*F14</f>
-        <v/>
-      </c>
-      <c r="G24" s="21">
-        <f>-Assumptions!$B$113*G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  G&amp;A / overhead</t>
-        </is>
-      </c>
-      <c r="C25" s="21">
-        <f>-Assumptions!$B$114*C14</f>
-        <v/>
-      </c>
-      <c r="D25" s="21">
-        <f>-Assumptions!$B$114*D14</f>
-        <v/>
-      </c>
-      <c r="E25" s="21">
-        <f>-Assumptions!$B$114*E14</f>
-        <v/>
-      </c>
-      <c r="F25" s="21">
-        <f>-Assumptions!$B$114*F14</f>
-        <v/>
-      </c>
-      <c r="G25" s="21">
-        <f>-Assumptions!$B$114*G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FX losses (net)</t>
-        </is>
-      </c>
-      <c r="C26" s="21">
-        <f>-Assumptions!$B$115*C14</f>
-        <v/>
-      </c>
-      <c r="D26" s="21">
-        <f>-Assumptions!$B$115*D14</f>
-        <v/>
-      </c>
-      <c r="E26" s="21">
-        <f>-Assumptions!$B$115*E14</f>
-        <v/>
-      </c>
-      <c r="F26" s="21">
-        <f>-Assumptions!$B$115*F14</f>
-        <v/>
-      </c>
-      <c r="G26" s="21">
-        <f>-Assumptions!$B$115*G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Total operating costs</t>
-        </is>
-      </c>
-      <c r="C27" s="24">
-        <f>C17+C18+C19+C20+C21+C22+C23+C24+C25+C26</f>
-        <v/>
-      </c>
-      <c r="D27" s="24">
-        <f>D17+D18+D19+D20+D21+D22+D23+D24+D25+D26</f>
-        <v/>
-      </c>
-      <c r="E27" s="24">
-        <f>E17+E18+E19+E20+E21+E22+E23+E24+E25+E26</f>
-        <v/>
-      </c>
-      <c r="F27" s="24">
-        <f>F17+F18+F19+F20+F21+F22+F23+F24+F25+F26</f>
-        <v/>
-      </c>
-      <c r="G27" s="24">
-        <f>G17+G18+G19+G20+G21+G22+G23+G24+G25+G26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="C28" s="22">
-        <f>C14+C27</f>
-        <v/>
-      </c>
-      <c r="D28" s="22">
-        <f>D14+D27</f>
-        <v/>
-      </c>
-      <c r="E28" s="22">
-        <f>E14+E27</f>
-        <v/>
-      </c>
-      <c r="F28" s="22">
-        <f>F14+F27</f>
-        <v/>
-      </c>
-      <c r="G28" s="22">
-        <f>G14+G27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="C30" s="21">
-        <f>PPE!$C$8</f>
-        <v/>
-      </c>
-      <c r="D30" s="21">
-        <f>PPE!$D$8</f>
-        <v/>
-      </c>
-      <c r="E30" s="21">
-        <f>PPE!$E$8</f>
-        <v/>
-      </c>
-      <c r="F30" s="21">
-        <f>PPE!$F$8</f>
-        <v/>
-      </c>
-      <c r="G30" s="21">
-        <f>PPE!$G$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Amortisation (intangibles ex-spectrum)</t>
-        </is>
-      </c>
-      <c r="C31" s="21">
-        <f>-Assumptions!$B$118*C14</f>
-        <v/>
-      </c>
-      <c r="D31" s="21">
-        <f>-Assumptions!$B$118*D14</f>
-        <v/>
-      </c>
-      <c r="E31" s="21">
-        <f>-Assumptions!$B$118*E14</f>
-        <v/>
-      </c>
-      <c r="F31" s="21">
-        <f>-Assumptions!$B$118*F14</f>
-        <v/>
-      </c>
-      <c r="G31" s="21">
-        <f>-Assumptions!$B$118*G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="C32" s="22">
-        <f>C28+C30+C31</f>
-        <v/>
-      </c>
-      <c r="D32" s="22">
-        <f>D28+D30+D31</f>
-        <v/>
-      </c>
-      <c r="E32" s="22">
-        <f>E28+E30+E31</f>
-        <v/>
-      </c>
-      <c r="F32" s="22">
-        <f>F28+F30+F31</f>
-        <v/>
-      </c>
-      <c r="G32" s="22">
-        <f>G28+G30+G31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Finance income</t>
-        </is>
-      </c>
-      <c r="C34" s="21">
-        <f>Assumptions!$B$17*C14</f>
-        <v/>
-      </c>
-      <c r="D34" s="21">
-        <f>Assumptions!$B$17*D14</f>
-        <v/>
-      </c>
-      <c r="E34" s="21">
-        <f>Assumptions!$B$17*E14</f>
-        <v/>
-      </c>
-      <c r="F34" s="21">
-        <f>Assumptions!$B$17*F14</f>
-        <v/>
-      </c>
-      <c r="G34" s="21">
-        <f>Assumptions!$B$17*G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Finance costs (interest expense)</t>
-        </is>
-      </c>
-      <c r="C35" s="21">
-        <f>-Debt!$C$16</f>
-        <v/>
-      </c>
-      <c r="D35" s="21">
-        <f>-Debt!$D$16</f>
-        <v/>
-      </c>
-      <c r="E35" s="21">
-        <f>-Debt!$E$16</f>
-        <v/>
-      </c>
-      <c r="F35" s="21">
-        <f>-Debt!$F$16</f>
-        <v/>
-      </c>
-      <c r="G35" s="21">
-        <f>-Debt!$G$16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Share of associates / JVs</t>
-        </is>
-      </c>
-      <c r="C36" s="21">
-        <f>Assumptions!$B$119*(1+Assumptions!$B$120)^1</f>
-        <v/>
-      </c>
-      <c r="D36" s="21">
-        <f>Assumptions!$B$119*(1+Assumptions!$B$120)^2</f>
-        <v/>
-      </c>
-      <c r="E36" s="21">
-        <f>Assumptions!$B$119*(1+Assumptions!$B$120)^3</f>
-        <v/>
-      </c>
-      <c r="F36" s="21">
-        <f>Assumptions!$B$119*(1+Assumptions!$B$120)^4</f>
-        <v/>
-      </c>
-      <c r="G36" s="21">
-        <f>Assumptions!$B$119*(1+Assumptions!$B$120)^5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Profit before tax</t>
-        </is>
-      </c>
-      <c r="C37" s="24">
-        <f>C32+C34+C35+C36</f>
-        <v/>
-      </c>
-      <c r="D37" s="24">
-        <f>D32+D34+D35+D36</f>
-        <v/>
-      </c>
-      <c r="E37" s="24">
-        <f>E32+E34+E35+E36</f>
-        <v/>
-      </c>
-      <c r="F37" s="24">
-        <f>F32+F34+F35+F36</f>
-        <v/>
-      </c>
-      <c r="G37" s="24">
-        <f>G32+G34+G35+G36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Current tax expense</t>
-        </is>
-      </c>
-      <c r="C38" s="21">
-        <f>-Tax!$C$8</f>
-        <v/>
-      </c>
-      <c r="D38" s="21">
-        <f>-Tax!$D$8</f>
-        <v/>
-      </c>
-      <c r="E38" s="21">
-        <f>-Tax!$E$8</f>
-        <v/>
-      </c>
-      <c r="F38" s="21">
-        <f>-Tax!$F$8</f>
-        <v/>
-      </c>
-      <c r="G38" s="21">
-        <f>-Tax!$G$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Deferred tax (movement)</t>
-        </is>
-      </c>
-      <c r="C39" s="21">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D39" s="21">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E39" s="21">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F39" s="21">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G39" s="21">
-        <f>0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>NET INCOME</t>
-        </is>
-      </c>
-      <c r="C40" s="22">
-        <f>C37+C38+C39</f>
-        <v/>
-      </c>
-      <c r="D40" s="22">
-        <f>D37+D38+D39</f>
-        <v/>
-      </c>
-      <c r="E40" s="22">
-        <f>E37+E38+E39</f>
-        <v/>
-      </c>
-      <c r="F40" s="22">
-        <f>F37+F38+F39</f>
-        <v/>
-      </c>
-      <c r="G40" s="22">
-        <f>G37+G38+G39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Attributable to equity holders of the parent</t>
-        </is>
-      </c>
-      <c r="C42" s="21">
-        <f>C40*(1-Assumptions!$B$121)</f>
-        <v/>
-      </c>
-      <c r="D42" s="21">
-        <f>D40*(1-Assumptions!$B$121)</f>
-        <v/>
-      </c>
-      <c r="E42" s="21">
-        <f>E40*(1-Assumptions!$B$121)</f>
-        <v/>
-      </c>
-      <c r="F42" s="21">
-        <f>F40*(1-Assumptions!$B$121)</f>
-        <v/>
-      </c>
-      <c r="G42" s="21">
-        <f>G40*(1-Assumptions!$B$121)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Attributable to minority interest</t>
-        </is>
-      </c>
-      <c r="C43" s="21">
-        <f>C40*Assumptions!$B$121</f>
-        <v/>
-      </c>
-      <c r="D43" s="21">
-        <f>D40*Assumptions!$B$121</f>
-        <v/>
-      </c>
-      <c r="E43" s="21">
-        <f>E40*Assumptions!$B$121</f>
-        <v/>
-      </c>
-      <c r="F43" s="21">
-        <f>F40*Assumptions!$B$121</f>
-        <v/>
-      </c>
-      <c r="G43" s="21">
-        <f>G40*Assumptions!$B$121</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Basic EPS (SAR / share)</t>
-        </is>
-      </c>
-      <c r="C45" s="25">
-        <f>C42*1000/Assumptions!$B$32</f>
-        <v/>
-      </c>
-      <c r="D45" s="25">
-        <f>D42*1000/Assumptions!$B$32</f>
-        <v/>
-      </c>
-      <c r="E45" s="25">
-        <f>E42*1000/Assumptions!$B$32</f>
-        <v/>
-      </c>
-      <c r="F45" s="25">
-        <f>F42*1000/Assumptions!$B$32</f>
-        <v/>
-      </c>
-      <c r="G45" s="25">
-        <f>G42*1000/Assumptions!$B$32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>MEMO</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBITDA margin</t>
-        </is>
-      </c>
-      <c r="C48" s="23">
-        <f>C28/C14</f>
-        <v/>
-      </c>
-      <c r="D48" s="23">
-        <f>D28/D14</f>
-        <v/>
-      </c>
-      <c r="E48" s="23">
-        <f>E28/E14</f>
-        <v/>
-      </c>
-      <c r="F48" s="23">
-        <f>F28/F14</f>
-        <v/>
-      </c>
-      <c r="G48" s="23">
-        <f>G28/G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBIT margin</t>
-        </is>
-      </c>
-      <c r="C49" s="23">
-        <f>C32/C14</f>
-        <v/>
-      </c>
-      <c r="D49" s="23">
-        <f>D32/D14</f>
-        <v/>
-      </c>
-      <c r="E49" s="23">
-        <f>E32/E14</f>
-        <v/>
-      </c>
-      <c r="F49" s="23">
-        <f>F32/F14</f>
-        <v/>
-      </c>
-      <c r="G49" s="23">
-        <f>G32/G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Net margin</t>
-        </is>
-      </c>
-      <c r="C50" s="23">
-        <f>C40/C14</f>
-        <v/>
-      </c>
-      <c r="D50" s="23">
-        <f>D40/D14</f>
-        <v/>
-      </c>
-      <c r="E50" s="23">
-        <f>E40/E14</f>
-        <v/>
-      </c>
-      <c r="F50" s="23">
-        <f>F40/F14</f>
-        <v/>
-      </c>
-      <c r="G50" s="23">
-        <f>G40/G14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Effective tax rate</t>
-        </is>
-      </c>
-      <c r="C51" s="23">
-        <f>-(C38+C39)/C37</f>
-        <v/>
-      </c>
-      <c r="D51" s="23">
-        <f>-(D38+D39)/D37</f>
-        <v/>
-      </c>
-      <c r="E51" s="23">
-        <f>-(E38+E39)/E37</f>
-        <v/>
-      </c>
-      <c r="F51" s="23">
-        <f>-(F38+F39)/F37</f>
-        <v/>
-      </c>
-      <c r="G51" s="23">
-        <f>-(G38+G39)/G37</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>SEGMENT P&amp;L  (contribution margin view)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Each segment carries its own contribution margin (segment revenue × CM%). Difference vs. IS EBITDA = unallocated group overhead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="n"/>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Y0 (base)</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="G4" s="15" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Mobile postpaid</t>
-        </is>
-      </c>
-      <c r="B7" s="21">
-        <f>Drivers!$B$31</f>
-        <v/>
-      </c>
-      <c r="C7" s="21">
-        <f>Drivers!$C$31</f>
-        <v/>
-      </c>
-      <c r="D7" s="21">
-        <f>Drivers!$D$31</f>
-        <v/>
-      </c>
-      <c r="E7" s="21">
-        <f>Drivers!$E$31</f>
-        <v/>
-      </c>
-      <c r="F7" s="21">
-        <f>Drivers!$F$31</f>
-        <v/>
-      </c>
-      <c r="G7" s="21">
-        <f>Drivers!$G$31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Mobile prepaid</t>
-        </is>
-      </c>
-      <c r="B8" s="21">
-        <f>Drivers!$B$32</f>
-        <v/>
-      </c>
-      <c r="C8" s="21">
-        <f>Drivers!$C$32</f>
-        <v/>
-      </c>
-      <c r="D8" s="21">
-        <f>Drivers!$D$32</f>
-        <v/>
-      </c>
-      <c r="E8" s="21">
-        <f>Drivers!$E$32</f>
-        <v/>
-      </c>
-      <c r="F8" s="21">
-        <f>Drivers!$F$32</f>
-        <v/>
-      </c>
-      <c r="G8" s="21">
-        <f>Drivers!$G$32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Fixed broadband</t>
-        </is>
-      </c>
-      <c r="B9" s="21">
-        <f>Drivers!$B$33</f>
-        <v/>
-      </c>
-      <c r="C9" s="21">
-        <f>Drivers!$C$33</f>
-        <v/>
-      </c>
-      <c r="D9" s="21">
-        <f>Drivers!$D$33</f>
-        <v/>
-      </c>
-      <c r="E9" s="21">
-        <f>Drivers!$E$33</f>
-        <v/>
-      </c>
-      <c r="F9" s="21">
-        <f>Drivers!$F$33</f>
-        <v/>
-      </c>
-      <c r="G9" s="21">
-        <f>Drivers!$G$33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B2B connectivity</t>
-        </is>
-      </c>
-      <c r="B10" s="21">
-        <f>Drivers!$B$34</f>
-        <v/>
-      </c>
-      <c r="C10" s="21">
-        <f>Drivers!$C$34</f>
-        <v/>
-      </c>
-      <c r="D10" s="21">
-        <f>Drivers!$D$34</f>
-        <v/>
-      </c>
-      <c r="E10" s="21">
-        <f>Drivers!$E$34</f>
-        <v/>
-      </c>
-      <c r="F10" s="21">
-        <f>Drivers!$F$34</f>
-        <v/>
-      </c>
-      <c r="G10" s="21">
-        <f>Drivers!$G$34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ICT / cloud</t>
-        </is>
-      </c>
-      <c r="B11" s="21">
-        <f>Drivers!$B$35</f>
-        <v/>
-      </c>
-      <c r="C11" s="21">
-        <f>Drivers!$C$35</f>
-        <v/>
-      </c>
-      <c r="D11" s="21">
-        <f>Drivers!$D$35</f>
-        <v/>
-      </c>
-      <c r="E11" s="21">
-        <f>Drivers!$E$35</f>
-        <v/>
-      </c>
-      <c r="F11" s="21">
-        <f>Drivers!$F$35</f>
-        <v/>
-      </c>
-      <c r="G11" s="21">
-        <f>Drivers!$G$35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Wholesale</t>
-        </is>
-      </c>
-      <c r="B12" s="21">
-        <f>Drivers!$B$36</f>
-        <v/>
-      </c>
-      <c r="C12" s="21">
-        <f>Drivers!$C$36</f>
-        <v/>
-      </c>
-      <c r="D12" s="21">
-        <f>Drivers!$D$36</f>
-        <v/>
-      </c>
-      <c r="E12" s="21">
-        <f>Drivers!$E$36</f>
-        <v/>
-      </c>
-      <c r="F12" s="21">
-        <f>Drivers!$F$36</f>
-        <v/>
-      </c>
-      <c r="G12" s="21">
-        <f>Drivers!$G$36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Equipment</t>
-        </is>
-      </c>
-      <c r="B13" s="21">
-        <f>Drivers!$B$39</f>
-        <v/>
-      </c>
-      <c r="C13" s="21">
-        <f>Drivers!$C$39</f>
-        <v/>
-      </c>
-      <c r="D13" s="21">
-        <f>Drivers!$D$39</f>
-        <v/>
-      </c>
-      <c r="E13" s="21">
-        <f>Drivers!$E$39</f>
-        <v/>
-      </c>
-      <c r="F13" s="21">
-        <f>Drivers!$F$39</f>
-        <v/>
-      </c>
-      <c r="G13" s="21">
-        <f>Drivers!$G$39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Total service revenue</t>
-        </is>
-      </c>
-      <c r="B14" s="24">
-        <f>B7+B8+B9+B10+B11+B12</f>
-        <v/>
-      </c>
-      <c r="C14" s="24">
-        <f>C7+C8+C9+C10+C11+C12</f>
-        <v/>
-      </c>
-      <c r="D14" s="24">
-        <f>D7+D8+D9+D10+D11+D12</f>
-        <v/>
-      </c>
-      <c r="E14" s="24">
-        <f>E7+E8+E9+E10+E11+E12</f>
-        <v/>
-      </c>
-      <c r="F14" s="24">
-        <f>F7+F8+F9+F10+F11+F12</f>
-        <v/>
-      </c>
-      <c r="G14" s="24">
-        <f>G7+G8+G9+G10+G11+G12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>Total revenue (incl. equipment)</t>
-        </is>
-      </c>
-      <c r="B15" s="22">
-        <f>B7+B8+B9+B10+B11+B12+B13</f>
-        <v/>
-      </c>
-      <c r="C15" s="22">
-        <f>C7+C8+C9+C10+C11+C12+C13</f>
-        <v/>
-      </c>
-      <c r="D15" s="22">
-        <f>D7+D8+D9+D10+D11+D12+D13</f>
-        <v/>
-      </c>
-      <c r="E15" s="22">
-        <f>E7+E8+E9+E10+E11+E12+E13</f>
-        <v/>
-      </c>
-      <c r="F15" s="22">
-        <f>F7+F8+F9+F10+F11+F12+F13</f>
-        <v/>
-      </c>
-      <c r="G15" s="22">
-        <f>G7+G8+G9+G10+G11+G12+G13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>DIRECT COSTS  (= revenue × (1 − CM%))</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Mobile postpaid</t>
-        </is>
-      </c>
-      <c r="B18" s="21">
-        <f>-B7*(1-Assumptions!$B$70)</f>
-        <v/>
-      </c>
-      <c r="C18" s="21">
-        <f>-C7*(1-Assumptions!$B$70)</f>
-        <v/>
-      </c>
-      <c r="D18" s="21">
-        <f>-D7*(1-Assumptions!$B$70)</f>
-        <v/>
-      </c>
-      <c r="E18" s="21">
-        <f>-E7*(1-Assumptions!$B$70)</f>
-        <v/>
-      </c>
-      <c r="F18" s="21">
-        <f>-F7*(1-Assumptions!$B$70)</f>
-        <v/>
-      </c>
-      <c r="G18" s="21">
-        <f>-G7*(1-Assumptions!$B$70)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Mobile prepaid</t>
-        </is>
-      </c>
-      <c r="B19" s="21">
-        <f>-B8*(1-Assumptions!$B$78)</f>
-        <v/>
-      </c>
-      <c r="C19" s="21">
-        <f>-C8*(1-Assumptions!$B$78)</f>
-        <v/>
-      </c>
-      <c r="D19" s="21">
-        <f>-D8*(1-Assumptions!$B$78)</f>
-        <v/>
-      </c>
-      <c r="E19" s="21">
-        <f>-E8*(1-Assumptions!$B$78)</f>
-        <v/>
-      </c>
-      <c r="F19" s="21">
-        <f>-F8*(1-Assumptions!$B$78)</f>
-        <v/>
-      </c>
-      <c r="G19" s="21">
-        <f>-G8*(1-Assumptions!$B$78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Fixed broadband</t>
-        </is>
-      </c>
-      <c r="B20" s="21">
-        <f>-B9*(1-Assumptions!$B$86)</f>
-        <v/>
-      </c>
-      <c r="C20" s="21">
-        <f>-C9*(1-Assumptions!$B$86)</f>
-        <v/>
-      </c>
-      <c r="D20" s="21">
-        <f>-D9*(1-Assumptions!$B$86)</f>
-        <v/>
-      </c>
-      <c r="E20" s="21">
-        <f>-E9*(1-Assumptions!$B$86)</f>
-        <v/>
-      </c>
-      <c r="F20" s="21">
-        <f>-F9*(1-Assumptions!$B$86)</f>
-        <v/>
-      </c>
-      <c r="G20" s="21">
-        <f>-G9*(1-Assumptions!$B$86)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B2B connectivity</t>
-        </is>
-      </c>
-      <c r="B21" s="21">
-        <f>-B10*(1-Assumptions!$B$91)</f>
-        <v/>
-      </c>
-      <c r="C21" s="21">
-        <f>-C10*(1-Assumptions!$B$91)</f>
-        <v/>
-      </c>
-      <c r="D21" s="21">
-        <f>-D10*(1-Assumptions!$B$91)</f>
-        <v/>
-      </c>
-      <c r="E21" s="21">
-        <f>-E10*(1-Assumptions!$B$91)</f>
-        <v/>
-      </c>
-      <c r="F21" s="21">
-        <f>-F10*(1-Assumptions!$B$91)</f>
-        <v/>
-      </c>
-      <c r="G21" s="21">
-        <f>-G10*(1-Assumptions!$B$91)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ICT / cloud</t>
-        </is>
-      </c>
-      <c r="B22" s="21">
-        <f>-B11*(1-Assumptions!$B$96)</f>
-        <v/>
-      </c>
-      <c r="C22" s="21">
-        <f>-C11*(1-Assumptions!$B$96)</f>
-        <v/>
-      </c>
-      <c r="D22" s="21">
-        <f>-D11*(1-Assumptions!$B$96)</f>
-        <v/>
-      </c>
-      <c r="E22" s="21">
-        <f>-E11*(1-Assumptions!$B$96)</f>
-        <v/>
-      </c>
-      <c r="F22" s="21">
-        <f>-F11*(1-Assumptions!$B$96)</f>
-        <v/>
-      </c>
-      <c r="G22" s="21">
-        <f>-G11*(1-Assumptions!$B$96)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Wholesale</t>
-        </is>
-      </c>
-      <c r="B23" s="21">
-        <f>-B12*(1-Assumptions!$B$101)</f>
-        <v/>
-      </c>
-      <c r="C23" s="21">
-        <f>-C12*(1-Assumptions!$B$101)</f>
-        <v/>
-      </c>
-      <c r="D23" s="21">
-        <f>-D12*(1-Assumptions!$B$101)</f>
-        <v/>
-      </c>
-      <c r="E23" s="21">
-        <f>-E12*(1-Assumptions!$B$101)</f>
-        <v/>
-      </c>
-      <c r="F23" s="21">
-        <f>-F12*(1-Assumptions!$B$101)</f>
-        <v/>
-      </c>
-      <c r="G23" s="21">
-        <f>-G12*(1-Assumptions!$B$101)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Equipment</t>
-        </is>
-      </c>
-      <c r="B24" s="21">
-        <f>-B13*(1-Assumptions!$B$106)</f>
-        <v/>
-      </c>
-      <c r="C24" s="21">
-        <f>-C13*(1-Assumptions!$B$106)</f>
-        <v/>
-      </c>
-      <c r="D24" s="21">
-        <f>-D13*(1-Assumptions!$B$106)</f>
-        <v/>
-      </c>
-      <c r="E24" s="21">
-        <f>-E13*(1-Assumptions!$B$106)</f>
-        <v/>
-      </c>
-      <c r="F24" s="21">
-        <f>-F13*(1-Assumptions!$B$106)</f>
-        <v/>
-      </c>
-      <c r="G24" s="21">
-        <f>-G13*(1-Assumptions!$B$106)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Total direct costs</t>
-        </is>
-      </c>
-      <c r="B25" s="24">
-        <f>B18+B19+B20+B21+B22+B23+B24</f>
-        <v/>
-      </c>
-      <c r="C25" s="24">
-        <f>C18+C19+C20+C21+C22+C23+C24</f>
-        <v/>
-      </c>
-      <c r="D25" s="24">
-        <f>D18+D19+D20+D21+D22+D23+D24</f>
-        <v/>
-      </c>
-      <c r="E25" s="24">
-        <f>E18+E19+E20+E21+E22+E23+E24</f>
-        <v/>
-      </c>
-      <c r="F25" s="24">
-        <f>F18+F19+F20+F21+F22+F23+F24</f>
-        <v/>
-      </c>
-      <c r="G25" s="24">
-        <f>G18+G19+G20+G21+G22+G23+G24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>SEGMENT CONTRIBUTION</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Mobile postpaid</t>
-        </is>
-      </c>
-      <c r="B28" s="21">
-        <f>B7+B18</f>
-        <v/>
-      </c>
-      <c r="C28" s="21">
-        <f>C7+C18</f>
-        <v/>
-      </c>
-      <c r="D28" s="21">
-        <f>D7+D18</f>
-        <v/>
-      </c>
-      <c r="E28" s="21">
-        <f>E7+E18</f>
-        <v/>
-      </c>
-      <c r="F28" s="21">
-        <f>F7+F18</f>
-        <v/>
-      </c>
-      <c r="G28" s="21">
-        <f>G7+G18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Mobile prepaid</t>
-        </is>
-      </c>
-      <c r="B29" s="21">
-        <f>B8+B19</f>
-        <v/>
-      </c>
-      <c r="C29" s="21">
-        <f>C8+C19</f>
-        <v/>
-      </c>
-      <c r="D29" s="21">
-        <f>D8+D19</f>
-        <v/>
-      </c>
-      <c r="E29" s="21">
-        <f>E8+E19</f>
-        <v/>
-      </c>
-      <c r="F29" s="21">
-        <f>F8+F19</f>
-        <v/>
-      </c>
-      <c r="G29" s="21">
-        <f>G8+G19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Fixed broadband</t>
-        </is>
-      </c>
-      <c r="B30" s="21">
-        <f>B9+B20</f>
-        <v/>
-      </c>
-      <c r="C30" s="21">
-        <f>C9+C20</f>
-        <v/>
-      </c>
-      <c r="D30" s="21">
-        <f>D9+D20</f>
-        <v/>
-      </c>
-      <c r="E30" s="21">
-        <f>E9+E20</f>
-        <v/>
-      </c>
-      <c r="F30" s="21">
-        <f>F9+F20</f>
-        <v/>
-      </c>
-      <c r="G30" s="21">
-        <f>G9+G20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B2B connectivity</t>
-        </is>
-      </c>
-      <c r="B31" s="21">
-        <f>B10+B21</f>
-        <v/>
-      </c>
-      <c r="C31" s="21">
-        <f>C10+C21</f>
-        <v/>
-      </c>
-      <c r="D31" s="21">
-        <f>D10+D21</f>
-        <v/>
-      </c>
-      <c r="E31" s="21">
-        <f>E10+E21</f>
-        <v/>
-      </c>
-      <c r="F31" s="21">
-        <f>F10+F21</f>
-        <v/>
-      </c>
-      <c r="G31" s="21">
-        <f>G10+G21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ICT / cloud</t>
-        </is>
-      </c>
-      <c r="B32" s="21">
-        <f>B11+B22</f>
-        <v/>
-      </c>
-      <c r="C32" s="21">
-        <f>C11+C22</f>
-        <v/>
-      </c>
-      <c r="D32" s="21">
-        <f>D11+D22</f>
-        <v/>
-      </c>
-      <c r="E32" s="21">
-        <f>E11+E22</f>
-        <v/>
-      </c>
-      <c r="F32" s="21">
-        <f>F11+F22</f>
-        <v/>
-      </c>
-      <c r="G32" s="21">
-        <f>G11+G22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Wholesale</t>
-        </is>
-      </c>
-      <c r="B33" s="21">
-        <f>B12+B23</f>
-        <v/>
-      </c>
-      <c r="C33" s="21">
-        <f>C12+C23</f>
-        <v/>
-      </c>
-      <c r="D33" s="21">
-        <f>D12+D23</f>
-        <v/>
-      </c>
-      <c r="E33" s="21">
-        <f>E12+E23</f>
-        <v/>
-      </c>
-      <c r="F33" s="21">
-        <f>F12+F23</f>
-        <v/>
-      </c>
-      <c r="G33" s="21">
-        <f>G12+G23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Equipment</t>
-        </is>
-      </c>
-      <c r="B34" s="21">
-        <f>B13+B24</f>
-        <v/>
-      </c>
-      <c r="C34" s="21">
-        <f>C13+C24</f>
-        <v/>
-      </c>
-      <c r="D34" s="21">
-        <f>D13+D24</f>
-        <v/>
-      </c>
-      <c r="E34" s="21">
-        <f>E13+E24</f>
-        <v/>
-      </c>
-      <c r="F34" s="21">
-        <f>F13+F24</f>
-        <v/>
-      </c>
-      <c r="G34" s="21">
-        <f>G13+G24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>Aggregate segment contribution</t>
-        </is>
-      </c>
-      <c r="B35" s="22">
-        <f>B28+B29+B30+B31+B32+B33+B34</f>
-        <v/>
-      </c>
-      <c r="C35" s="22">
-        <f>C28+C29+C30+C31+C32+C33+C34</f>
-        <v/>
-      </c>
-      <c r="D35" s="22">
-        <f>D28+D29+D30+D31+D32+D33+D34</f>
-        <v/>
-      </c>
-      <c r="E35" s="22">
-        <f>E28+E29+E30+E31+E32+E33+E34</f>
-        <v/>
-      </c>
-      <c r="F35" s="22">
-        <f>F28+F29+F30+F31+F32+F33+F34</f>
-        <v/>
-      </c>
-      <c r="G35" s="22">
-        <f>G28+G29+G30+G31+G32+G33+G34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>CONTRIBUTION MARGIN %</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Mobile postpaid</t>
-        </is>
-      </c>
-      <c r="B38" s="23">
-        <f>IF(B7=0,0,B28/B7)</f>
-        <v/>
-      </c>
-      <c r="C38" s="23">
-        <f>IF(C7=0,0,C28/C7)</f>
-        <v/>
-      </c>
-      <c r="D38" s="23">
-        <f>IF(D7=0,0,D28/D7)</f>
-        <v/>
-      </c>
-      <c r="E38" s="23">
-        <f>IF(E7=0,0,E28/E7)</f>
-        <v/>
-      </c>
-      <c r="F38" s="23">
-        <f>IF(F7=0,0,F28/F7)</f>
-        <v/>
-      </c>
-      <c r="G38" s="23">
-        <f>IF(G7=0,0,G28/G7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Mobile prepaid</t>
-        </is>
-      </c>
-      <c r="B39" s="23">
-        <f>IF(B8=0,0,B29/B8)</f>
-        <v/>
-      </c>
-      <c r="C39" s="23">
-        <f>IF(C8=0,0,C29/C8)</f>
-        <v/>
-      </c>
-      <c r="D39" s="23">
-        <f>IF(D8=0,0,D29/D8)</f>
-        <v/>
-      </c>
-      <c r="E39" s="23">
-        <f>IF(E8=0,0,E29/E8)</f>
-        <v/>
-      </c>
-      <c r="F39" s="23">
-        <f>IF(F8=0,0,F29/F8)</f>
-        <v/>
-      </c>
-      <c r="G39" s="23">
-        <f>IF(G8=0,0,G29/G8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Fixed broadband</t>
-        </is>
-      </c>
-      <c r="B40" s="23">
-        <f>IF(B9=0,0,B30/B9)</f>
-        <v/>
-      </c>
-      <c r="C40" s="23">
-        <f>IF(C9=0,0,C30/C9)</f>
-        <v/>
-      </c>
-      <c r="D40" s="23">
-        <f>IF(D9=0,0,D30/D9)</f>
-        <v/>
-      </c>
-      <c r="E40" s="23">
-        <f>IF(E9=0,0,E30/E9)</f>
-        <v/>
-      </c>
-      <c r="F40" s="23">
-        <f>IF(F9=0,0,F30/F9)</f>
-        <v/>
-      </c>
-      <c r="G40" s="23">
-        <f>IF(G9=0,0,G30/G9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B2B connectivity</t>
-        </is>
-      </c>
-      <c r="B41" s="23">
-        <f>IF(B10=0,0,B31/B10)</f>
-        <v/>
-      </c>
-      <c r="C41" s="23">
-        <f>IF(C10=0,0,C31/C10)</f>
-        <v/>
-      </c>
-      <c r="D41" s="23">
-        <f>IF(D10=0,0,D31/D10)</f>
-        <v/>
-      </c>
-      <c r="E41" s="23">
-        <f>IF(E10=0,0,E31/E10)</f>
-        <v/>
-      </c>
-      <c r="F41" s="23">
-        <f>IF(F10=0,0,F31/F10)</f>
-        <v/>
-      </c>
-      <c r="G41" s="23">
-        <f>IF(G10=0,0,G31/G10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ICT / cloud</t>
-        </is>
-      </c>
-      <c r="B42" s="23">
-        <f>IF(B11=0,0,B32/B11)</f>
-        <v/>
-      </c>
-      <c r="C42" s="23">
-        <f>IF(C11=0,0,C32/C11)</f>
-        <v/>
-      </c>
-      <c r="D42" s="23">
-        <f>IF(D11=0,0,D32/D11)</f>
-        <v/>
-      </c>
-      <c r="E42" s="23">
-        <f>IF(E11=0,0,E32/E11)</f>
-        <v/>
-      </c>
-      <c r="F42" s="23">
-        <f>IF(F11=0,0,F32/F11)</f>
-        <v/>
-      </c>
-      <c r="G42" s="23">
-        <f>IF(G11=0,0,G32/G11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Wholesale</t>
-        </is>
-      </c>
-      <c r="B43" s="23">
-        <f>IF(B12=0,0,B33/B12)</f>
-        <v/>
-      </c>
-      <c r="C43" s="23">
-        <f>IF(C12=0,0,C33/C12)</f>
-        <v/>
-      </c>
-      <c r="D43" s="23">
-        <f>IF(D12=0,0,D33/D12)</f>
-        <v/>
-      </c>
-      <c r="E43" s="23">
-        <f>IF(E12=0,0,E33/E12)</f>
-        <v/>
-      </c>
-      <c r="F43" s="23">
-        <f>IF(F12=0,0,F33/F12)</f>
-        <v/>
-      </c>
-      <c r="G43" s="23">
-        <f>IF(G12=0,0,G33/G12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Equipment</t>
-        </is>
-      </c>
-      <c r="B44" s="23">
-        <f>IF(B13=0,0,B34/B13)</f>
-        <v/>
-      </c>
-      <c r="C44" s="23">
-        <f>IF(C13=0,0,C34/C13)</f>
-        <v/>
-      </c>
-      <c r="D44" s="23">
-        <f>IF(D13=0,0,D34/D13)</f>
-        <v/>
-      </c>
-      <c r="E44" s="23">
-        <f>IF(E13=0,0,E34/E13)</f>
-        <v/>
-      </c>
-      <c r="F44" s="23">
-        <f>IF(F13=0,0,F34/F13)</f>
-        <v/>
-      </c>
-      <c r="G44" s="23">
-        <f>IF(G13=0,0,G34/G13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Blended CM %</t>
-        </is>
-      </c>
-      <c r="B45" s="26">
-        <f>B35/B15</f>
-        <v/>
-      </c>
-      <c r="C45" s="26">
-        <f>C35/C15</f>
-        <v/>
-      </c>
-      <c r="D45" s="26">
-        <f>D35/D15</f>
-        <v/>
-      </c>
-      <c r="E45" s="26">
-        <f>E35/E15</f>
-        <v/>
-      </c>
-      <c r="F45" s="26">
-        <f>F35/F15</f>
-        <v/>
-      </c>
-      <c r="G45" s="26">
-        <f>G35/G15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>RECONCILIATION TO GROUP EBITDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Aggregate segment contribution</t>
-        </is>
-      </c>
-      <c r="C48" s="21">
-        <f>C35</f>
-        <v/>
-      </c>
-      <c r="D48" s="21">
-        <f>D35</f>
-        <v/>
-      </c>
-      <c r="E48" s="21">
-        <f>E35</f>
-        <v/>
-      </c>
-      <c r="F48" s="21">
-        <f>F35</f>
-        <v/>
-      </c>
-      <c r="G48" s="21">
-        <f>G35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>− IS EBITDA (group)</t>
-        </is>
-      </c>
-      <c r="C49" s="21">
-        <f>-IS!$C$28</f>
-        <v/>
-      </c>
-      <c r="D49" s="21">
-        <f>-IS!$D$28</f>
-        <v/>
-      </c>
-      <c r="E49" s="21">
-        <f>-IS!$E$28</f>
-        <v/>
-      </c>
-      <c r="F49" s="21">
-        <f>-IS!$F$28</f>
-        <v/>
-      </c>
-      <c r="G49" s="21">
-        <f>-IS!$G$28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="18">
-        <f> Unallocated / shared overhead</f>
-        <v/>
-      </c>
-      <c r="C50" s="22">
-        <f>C48+C49</f>
-        <v/>
-      </c>
-      <c r="D50" s="22">
-        <f>D48+D49</f>
-        <v/>
-      </c>
-      <c r="E50" s="22">
-        <f>E48+E49</f>
-        <v/>
-      </c>
-      <c r="F50" s="22">
-        <f>F48+F49</f>
-        <v/>
-      </c>
-      <c r="G50" s="22">
-        <f>G48+G49</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/industries/telecom-it/telecom-model.xlsx
+++ b/industries/telecom-it/telecom-model.xlsx
@@ -1744,23 +1744,23 @@
         </is>
       </c>
       <c r="C35" s="21">
-        <f>-Debt!$C$16-Leases!$C$14</f>
+        <f>-Debt!$C$45-Leases!$C$14</f>
         <v/>
       </c>
       <c r="D35" s="21">
-        <f>-Debt!$D$16-Leases!$D$14</f>
+        <f>-Debt!$D$45-Leases!$D$14</f>
         <v/>
       </c>
       <c r="E35" s="21">
-        <f>-Debt!$E$16-Leases!$E$14</f>
+        <f>-Debt!$E$45-Leases!$E$14</f>
         <v/>
       </c>
       <c r="F35" s="21">
-        <f>-Debt!$F$16-Leases!$F$14</f>
+        <f>-Debt!$F$45-Leases!$F$14</f>
         <v/>
       </c>
       <c r="G35" s="21">
-        <f>-Debt!$G$16-Leases!$G$14</f>
+        <f>-Debt!$G$45-Leases!$G$14</f>
         <v/>
       </c>
     </row>
@@ -1825,23 +1825,23 @@
         </is>
       </c>
       <c r="C38" s="21">
-        <f>-Tax!$C$8</f>
+        <f>-Tax!$C$9</f>
         <v/>
       </c>
       <c r="D38" s="21">
-        <f>-Tax!$D$8</f>
+        <f>-Tax!$D$9</f>
         <v/>
       </c>
       <c r="E38" s="21">
-        <f>-Tax!$E$8</f>
+        <f>-Tax!$E$9</f>
         <v/>
       </c>
       <c r="F38" s="21">
-        <f>-Tax!$F$8</f>
+        <f>-Tax!$F$9</f>
         <v/>
       </c>
       <c r="G38" s="21">
-        <f>-Tax!$G$8</f>
+        <f>-Tax!$G$9</f>
         <v/>
       </c>
     </row>
@@ -1852,23 +1852,23 @@
         </is>
       </c>
       <c r="C39" s="21">
-        <f>0</f>
+        <f>-Tax!$C$15</f>
         <v/>
       </c>
       <c r="D39" s="21">
-        <f>0</f>
+        <f>-Tax!$D$15</f>
         <v/>
       </c>
       <c r="E39" s="21">
-        <f>0</f>
+        <f>-Tax!$E$15</f>
         <v/>
       </c>
       <c r="F39" s="21">
-        <f>0</f>
+        <f>-Tax!$F$15</f>
         <v/>
       </c>
       <c r="G39" s="21">
-        <f>0</f>
+        <f>-Tax!$G$15</f>
         <v/>
       </c>
     </row>
@@ -3712,23 +3712,23 @@
         <v/>
       </c>
       <c r="C7" s="21">
-        <f>B7+CFS!C25</f>
+        <f>B7+CFS!C26</f>
         <v/>
       </c>
       <c r="D7" s="21">
-        <f>C7+CFS!D25</f>
+        <f>C7+CFS!D26</f>
         <v/>
       </c>
       <c r="E7" s="21">
-        <f>D7+CFS!E25</f>
+        <f>D7+CFS!E26</f>
         <v/>
       </c>
       <c r="F7" s="21">
-        <f>E7+CFS!F25</f>
+        <f>E7+CFS!F26</f>
         <v/>
       </c>
       <c r="G7" s="21">
-        <f>F7+CFS!G25</f>
+        <f>F7+CFS!G26</f>
         <v/>
       </c>
     </row>
@@ -4211,27 +4211,27 @@
         </is>
       </c>
       <c r="B27" s="21">
-        <f>Debt!B6</f>
+        <f>Debt!B35</f>
         <v/>
       </c>
       <c r="C27" s="21">
-        <f>Debt!C6</f>
+        <f>Debt!C35</f>
         <v/>
       </c>
       <c r="D27" s="21">
-        <f>Debt!D6</f>
+        <f>Debt!D35</f>
         <v/>
       </c>
       <c r="E27" s="21">
-        <f>Debt!E6</f>
+        <f>Debt!E35</f>
         <v/>
       </c>
       <c r="F27" s="21">
-        <f>Debt!F6</f>
+        <f>Debt!F35</f>
         <v/>
       </c>
       <c r="G27" s="21">
-        <f>Debt!G6</f>
+        <f>Debt!G35</f>
         <v/>
       </c>
     </row>
@@ -4273,27 +4273,27 @@
         </is>
       </c>
       <c r="B30" s="21">
-        <f>Debt!B7</f>
+        <f>Debt!B36</f>
         <v/>
       </c>
       <c r="C30" s="21">
-        <f>Debt!C7</f>
+        <f>Debt!C36</f>
         <v/>
       </c>
       <c r="D30" s="21">
-        <f>Debt!D7</f>
+        <f>Debt!D36</f>
         <v/>
       </c>
       <c r="E30" s="21">
-        <f>Debt!E7</f>
+        <f>Debt!E36</f>
         <v/>
       </c>
       <c r="F30" s="21">
-        <f>Debt!F7</f>
+        <f>Debt!F36</f>
         <v/>
       </c>
       <c r="G30" s="21">
-        <f>Debt!G7</f>
+        <f>Debt!G36</f>
         <v/>
       </c>
     </row>
@@ -4304,27 +4304,27 @@
         </is>
       </c>
       <c r="B31" s="21">
-        <f>Debt!B8</f>
+        <f>Debt!B37</f>
         <v/>
       </c>
       <c r="C31" s="21">
-        <f>Debt!C8</f>
+        <f>Debt!C37</f>
         <v/>
       </c>
       <c r="D31" s="21">
-        <f>Debt!D8</f>
+        <f>Debt!D37</f>
         <v/>
       </c>
       <c r="E31" s="21">
-        <f>Debt!E8</f>
+        <f>Debt!E37</f>
         <v/>
       </c>
       <c r="F31" s="21">
-        <f>Debt!F8</f>
+        <f>Debt!F37</f>
         <v/>
       </c>
       <c r="G31" s="21">
-        <f>Debt!G8</f>
+        <f>Debt!G37</f>
         <v/>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Deferred tax liabilities (flat)</t>
+          <t>Deferred tax liabilities (rollforward)</t>
         </is>
       </c>
       <c r="B33" s="21">
@@ -4370,23 +4370,23 @@
         <v/>
       </c>
       <c r="C33" s="21">
-        <f>B33</f>
+        <f>Tax!$C$16</f>
         <v/>
       </c>
       <c r="D33" s="21">
-        <f>C33</f>
+        <f>Tax!$D$16</f>
         <v/>
       </c>
       <c r="E33" s="21">
-        <f>D33</f>
+        <f>Tax!$E$16</f>
         <v/>
       </c>
       <c r="F33" s="21">
-        <f>E33</f>
+        <f>Tax!$F$16</f>
         <v/>
       </c>
       <c r="G33" s="21">
-        <f>F33</f>
+        <f>Tax!$G$16</f>
         <v/>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4832,365 +4832,392 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
+          <t>+ Deferred tax (non-cash addback)</t>
+        </is>
+      </c>
+      <c r="C10" s="21">
+        <f>Tax!$C$15</f>
+        <v/>
+      </c>
+      <c r="D10" s="21">
+        <f>Tax!$D$15</f>
+        <v/>
+      </c>
+      <c r="E10" s="21">
+        <f>Tax!$E$15</f>
+        <v/>
+      </c>
+      <c r="F10" s="21">
+        <f>Tax!$F$15</f>
+        <v/>
+      </c>
+      <c r="G10" s="21">
+        <f>Tax!$G$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
           <t>+/− Δ working capital</t>
         </is>
       </c>
-      <c r="C10" s="21">
+      <c r="C11" s="21">
         <f>WC!$C$20</f>
         <v/>
       </c>
-      <c r="D10" s="21">
+      <c r="D11" s="21">
         <f>WC!$D$20</f>
         <v/>
       </c>
-      <c r="E10" s="21">
+      <c r="E11" s="21">
         <f>WC!$E$20</f>
         <v/>
       </c>
-      <c r="F10" s="21">
+      <c r="F11" s="21">
         <f>WC!$F$20</f>
         <v/>
       </c>
-      <c r="G10" s="21">
+      <c r="G11" s="21">
         <f>WC!$G$20</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Cash from operations (CFO)</t>
         </is>
       </c>
-      <c r="C11" s="22">
-        <f>C7+C8+C9+C10</f>
-        <v/>
-      </c>
-      <c r="D11" s="22">
-        <f>D7+D8+D9+D10</f>
-        <v/>
-      </c>
-      <c r="E11" s="22">
-        <f>E7+E8+E9+E10</f>
-        <v/>
-      </c>
-      <c r="F11" s="22">
-        <f>F7+F8+F9+F10</f>
-        <v/>
-      </c>
-      <c r="G11" s="22">
-        <f>G7+G8+G9+G10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="C12" s="22">
+        <f>C7+C8+C9+C10+C11</f>
+        <v/>
+      </c>
+      <c r="D12" s="22">
+        <f>D7+D8+D9+D10+D11</f>
+        <v/>
+      </c>
+      <c r="E12" s="22">
+        <f>E7+E8+E9+E10+E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="22">
+        <f>F7+F8+F9+F10+F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="22">
+        <f>G7+G8+G9+G10+G11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>INVESTING</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>− Capex (PP&amp;E)</t>
-        </is>
-      </c>
-      <c r="C14" s="21">
-        <f>-PPE!$C$7</f>
-        <v/>
-      </c>
-      <c r="D14" s="21">
-        <f>-PPE!$D$7</f>
-        <v/>
-      </c>
-      <c r="E14" s="21">
-        <f>-PPE!$E$7</f>
-        <v/>
-      </c>
-      <c r="F14" s="21">
-        <f>-PPE!$F$7</f>
-        <v/>
-      </c>
-      <c r="G14" s="21">
-        <f>-PPE!$G$7</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>− Spectrum cash payments</t>
+          <t>− Capex (PP&amp;E)</t>
         </is>
       </c>
       <c r="C15" s="21">
-        <f>-Spectrum!$C$25</f>
+        <f>-PPE!$C$7</f>
         <v/>
       </c>
       <c r="D15" s="21">
-        <f>-Spectrum!$D$25</f>
+        <f>-PPE!$D$7</f>
         <v/>
       </c>
       <c r="E15" s="21">
-        <f>-Spectrum!$E$25</f>
+        <f>-PPE!$E$7</f>
         <v/>
       </c>
       <c r="F15" s="21">
-        <f>-Spectrum!$F$25</f>
+        <f>-PPE!$F$7</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>-Spectrum!$G$25</f>
+        <f>-PPE!$G$7</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
+          <t>− Spectrum cash payments</t>
+        </is>
+      </c>
+      <c r="C16" s="21">
+        <f>-Spectrum!$C$25</f>
+        <v/>
+      </c>
+      <c r="D16" s="21">
+        <f>-Spectrum!$D$25</f>
+        <v/>
+      </c>
+      <c r="E16" s="21">
+        <f>-Spectrum!$E$25</f>
+        <v/>
+      </c>
+      <c r="F16" s="21">
+        <f>-Spectrum!$F$25</f>
+        <v/>
+      </c>
+      <c r="G16" s="21">
+        <f>-Spectrum!$G$25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
           <t>Other investing (flat / nil)</t>
         </is>
       </c>
-      <c r="C16" s="21">
+      <c r="C17" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="D16" s="21">
+      <c r="D17" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="E16" s="21">
+      <c r="E17" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="F16" s="21">
+      <c r="F17" s="21">
         <f>0</f>
         <v/>
       </c>
-      <c r="G16" s="21">
+      <c r="G17" s="21">
         <f>0</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Cash from investing (CFI)</t>
         </is>
       </c>
-      <c r="C17" s="22">
-        <f>C14+C15+C16</f>
-        <v/>
-      </c>
-      <c r="D17" s="22">
-        <f>D14+D15+D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="22">
-        <f>E14+E15+E16</f>
-        <v/>
-      </c>
-      <c r="F17" s="22">
-        <f>F14+F15+F16</f>
-        <v/>
-      </c>
-      <c r="G17" s="22">
-        <f>G14+G15+G16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="C18" s="22">
+        <f>C15+C16+C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="22">
+        <f>D15+D16+D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="22">
+        <f>E15+E16+E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="22">
+        <f>F15+F16+F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="22">
+        <f>G15+G16+G17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>FINANCING</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>+/− Net debt issuance (flat assumption)</t>
-        </is>
-      </c>
-      <c r="C20" s="21">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D20" s="21">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E20" s="21">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F20" s="21">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G20" s="21">
-        <f>0</f>
-        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>− Lease cash payments</t>
+          <t>+/− Net debt issuance (from Debt schedule)</t>
         </is>
       </c>
       <c r="C21" s="21">
-        <f>Leases!$C$16</f>
+        <f>Debt!$C$46</f>
         <v/>
       </c>
       <c r="D21" s="21">
-        <f>Leases!$D$16</f>
+        <f>Debt!$D$46</f>
         <v/>
       </c>
       <c r="E21" s="21">
-        <f>Leases!$E$16</f>
+        <f>Debt!$E$46</f>
         <v/>
       </c>
       <c r="F21" s="21">
-        <f>Leases!$F$16</f>
+        <f>Debt!$F$46</f>
         <v/>
       </c>
       <c r="G21" s="21">
-        <f>Leases!$G$16</f>
+        <f>Debt!$G$46</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
+          <t>− Lease cash payments</t>
+        </is>
+      </c>
+      <c r="C22" s="21">
+        <f>Leases!$C$16</f>
+        <v/>
+      </c>
+      <c r="D22" s="21">
+        <f>Leases!$D$16</f>
+        <v/>
+      </c>
+      <c r="E22" s="21">
+        <f>Leases!$E$16</f>
+        <v/>
+      </c>
+      <c r="F22" s="21">
+        <f>Leases!$F$16</f>
+        <v/>
+      </c>
+      <c r="G22" s="21">
+        <f>Leases!$G$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
           <t>− Dividends paid</t>
         </is>
       </c>
-      <c r="C22" s="21">
+      <c r="C23" s="21">
         <f>Equity!$C$9</f>
         <v/>
       </c>
-      <c r="D22" s="21">
+      <c r="D23" s="21">
         <f>Equity!$D$9</f>
         <v/>
       </c>
-      <c r="E22" s="21">
+      <c r="E23" s="21">
         <f>Equity!$E$9</f>
         <v/>
       </c>
-      <c r="F22" s="21">
+      <c r="F23" s="21">
         <f>Equity!$F$9</f>
         <v/>
       </c>
-      <c r="G22" s="21">
+      <c r="G23" s="21">
         <f>Equity!$G$9</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Cash from financing (CFF)</t>
         </is>
       </c>
-      <c r="C23" s="22">
-        <f>C20+C21+C22</f>
-        <v/>
-      </c>
-      <c r="D23" s="22">
-        <f>D20+D21+D22</f>
-        <v/>
-      </c>
-      <c r="E23" s="22">
-        <f>E20+E21+E22</f>
-        <v/>
-      </c>
-      <c r="F23" s="22">
-        <f>F20+F21+F22</f>
-        <v/>
-      </c>
-      <c r="G23" s="22">
-        <f>G20+G21+G22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="C24" s="22">
+        <f>C21+C22+C23</f>
+        <v/>
+      </c>
+      <c r="D24" s="22">
+        <f>D21+D22+D23</f>
+        <v/>
+      </c>
+      <c r="E24" s="22">
+        <f>E21+E22+E23</f>
+        <v/>
+      </c>
+      <c r="F24" s="22">
+        <f>F21+F22+F23</f>
+        <v/>
+      </c>
+      <c r="G24" s="22">
+        <f>G21+G22+G23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="C25" s="22">
-        <f>C11+C17+C23</f>
-        <v/>
-      </c>
-      <c r="D25" s="22">
-        <f>D11+D17+D23</f>
-        <v/>
-      </c>
-      <c r="E25" s="22">
-        <f>E11+E17+E23</f>
-        <v/>
-      </c>
-      <c r="F25" s="22">
-        <f>F11+F17+F23</f>
-        <v/>
-      </c>
-      <c r="G25" s="22">
-        <f>G11+G17+G23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="C26" s="22">
+        <f>C12+C18+C24</f>
+        <v/>
+      </c>
+      <c r="D26" s="22">
+        <f>D12+D18+D24</f>
+        <v/>
+      </c>
+      <c r="E26" s="22">
+        <f>E12+E18+E24</f>
+        <v/>
+      </c>
+      <c r="F26" s="22">
+        <f>F12+F18+F24</f>
+        <v/>
+      </c>
+      <c r="G26" s="22">
+        <f>G12+G18+G24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Opening cash</t>
         </is>
       </c>
-      <c r="C26" s="21">
+      <c r="C27" s="21">
         <f>Assumptions!$B$35</f>
         <v/>
       </c>
-      <c r="D26" s="21">
-        <f>C27</f>
-        <v/>
-      </c>
-      <c r="E26" s="21">
-        <f>D27</f>
-        <v/>
-      </c>
-      <c r="F26" s="21">
-        <f>E27</f>
-        <v/>
-      </c>
-      <c r="G26" s="21">
-        <f>F27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="D27" s="21">
+        <f>C28</f>
+        <v/>
+      </c>
+      <c r="E27" s="21">
+        <f>D28</f>
+        <v/>
+      </c>
+      <c r="F27" s="21">
+        <f>E28</f>
+        <v/>
+      </c>
+      <c r="G27" s="21">
+        <f>F28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Closing cash</t>
         </is>
       </c>
-      <c r="C27" s="22">
-        <f>C26+C25</f>
-        <v/>
-      </c>
-      <c r="D27" s="22">
-        <f>D26+D25</f>
-        <v/>
-      </c>
-      <c r="E27" s="22">
-        <f>E26+E25</f>
-        <v/>
-      </c>
-      <c r="F27" s="22">
-        <f>F26+F25</f>
-        <v/>
-      </c>
-      <c r="G27" s="22">
-        <f>G26+G25</f>
+      <c r="C28" s="22">
+        <f>C27+C26</f>
+        <v/>
+      </c>
+      <c r="D28" s="22">
+        <f>D27+D26</f>
+        <v/>
+      </c>
+      <c r="E28" s="22">
+        <f>E27+E26</f>
+        <v/>
+      </c>
+      <c r="F28" s="22">
+        <f>F27+F26</f>
+        <v/>
+      </c>
+      <c r="G28" s="22">
+        <f>G27+G26</f>
         <v/>
       </c>
     </row>
@@ -6805,23 +6832,23 @@
         <v>0.01</v>
       </c>
       <c r="B6" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A6)/(B5-A6))/(1+B5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A6)/(B5-A6))/(1+B5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="C6" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A6)/(C5-A6))/(1+C5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A6)/(C5-A6))/(1+C5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="D6" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A6)/(D5-A6))/(1+D5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A6)/(D5-A6))/(1+D5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="E6" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A6)/(E5-A6))/(1+E5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A6)/(E5-A6))/(1+E5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A6)/(F5-A6))/(1+F5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A6)/(F5-A6))/(1+F5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
     </row>
@@ -6830,23 +6857,23 @@
         <v>0.02</v>
       </c>
       <c r="B7" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A7)/(B5-A7))/(1+B5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A7)/(B5-A7))/(1+B5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="C7" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A7)/(C5-A7))/(1+C5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A7)/(C5-A7))/(1+C5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="D7" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A7)/(D5-A7))/(1+D5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A7)/(D5-A7))/(1+D5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="E7" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A7)/(E5-A7))/(1+E5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A7)/(E5-A7))/(1+E5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A7)/(F5-A7))/(1+F5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A7)/(F5-A7))/(1+F5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
     </row>
@@ -6855,23 +6882,23 @@
         <v>0.03</v>
       </c>
       <c r="B8" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A8)/(B5-A8))/(1+B5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A8)/(B5-A8))/(1+B5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A8)/(C5-A8))/(1+C5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A8)/(C5-A8))/(1+C5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A8)/(D5-A8))/(1+D5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A8)/(D5-A8))/(1+D5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A8)/(E5-A8))/(1+E5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A8)/(E5-A8))/(1+E5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A8)/(F5-A8))/(1+F5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A8)/(F5-A8))/(1+F5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
     </row>
@@ -6880,23 +6907,23 @@
         <v>0.04</v>
       </c>
       <c r="B9" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A9)/(B5-A9))/(1+B5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A9)/(B5-A9))/(1+B5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="C9" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A9)/(C5-A9))/(1+C5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A9)/(C5-A9))/(1+C5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="D9" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A9)/(D5-A9))/(1+D5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A9)/(D5-A9))/(1+D5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A9)/(E5-A9))/(1+E5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A9)/(E5-A9))/(1+E5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A9)/(F5-A9))/(1+F5)^5))-Debt!$B$14)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A9)/(F5-A9))/(1+F5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
     </row>
@@ -7440,7 +7467,7 @@
         </is>
       </c>
       <c r="B23" s="21">
-        <f>-Debt!$B$14</f>
+        <f>-Debt!$B$43</f>
         <v/>
       </c>
     </row>
@@ -7616,23 +7643,23 @@
         </is>
       </c>
       <c r="C7" s="32">
-        <f>IF(ABS(BS!C7-CFS!C27)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(BS!C7-CFS!C28)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="D7" s="32">
-        <f>IF(ABS(BS!D7-CFS!D27)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(BS!D7-CFS!D28)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="E7" s="32">
-        <f>IF(ABS(BS!E7-CFS!E27)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(BS!E7-CFS!E28)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="F7" s="32">
-        <f>IF(ABS(BS!F7-CFS!F27)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(BS!F7-CFS!F28)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="G7" s="32">
-        <f>IF(ABS(BS!G7-CFS!G27)&lt;0.01,"PASS","FAIL")</f>
+        <f>IF(ABS(BS!G7-CFS!G28)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -7744,7 +7771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C142"/>
+  <dimension ref="A1:C164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -9230,6 +9257,193 @@
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>Brand, software, customer lists (ex-spectrum).</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>PHASE 3 — Debt tranches</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>Tranche 1 — Sukuk 1 (bullet, refi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Notional (SAR bn)</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Bullet maturity in year t1_maturity_y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Coupon</t>
+        </is>
+      </c>
+      <c r="B147" s="10" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Maturity year</t>
+        </is>
+      </c>
+      <c r="B148" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Refinanced at par at maturity (net debt change = 0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>Tranche 2 — Sukuk 2 (matures Y8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Notional (SAR bn)</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Out of 5-year horizon; held flat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Coupon</t>
+        </is>
+      </c>
+      <c r="B152" s="10" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>Tranche 3 — Term loan (amortising)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Notional Y0 (SAR bn)</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Amortises annually.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Coupon</t>
+        </is>
+      </c>
+      <c r="B156" s="10" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Repayment per year</t>
+        </is>
+      </c>
+      <c r="B157" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Fully paid off by Y5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>Tranche 4 — RCF (drawn portion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Drawn balance Y0 (SAR bn)</t>
+        </is>
+      </c>
+      <c r="B160" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Held flat at drawn level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Coupon (floating)</t>
+        </is>
+      </c>
+      <c r="B161" s="10" t="n">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>PHASE 3 — Deferred tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>Tax depreciation rate</t>
+        </is>
+      </c>
+      <c r="B164" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Accelerated vs book 10% → creates DTL.</t>
         </is>
       </c>
     </row>
@@ -11080,10 +11294,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -11095,14 +11309,14 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>DEBT SCHEDULE</t>
+          <t>DEBT SCHEDULE — TRANCHE WATERFALL</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total debt = ST + LT + lease liabilities. Held flat unless overridden (simplification).</t>
+          <t>Four debt instruments. Per-tranche opening + issuance − repayment = closing. Lease liabilities live on the Leases sheet; pulled in below for total leverage view.</t>
         </is>
       </c>
     </row>
@@ -11140,215 +11354,1000 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Short-term debt</t>
-        </is>
-      </c>
-      <c r="B6" s="21">
-        <f>Assumptions!$B$48</f>
-        <v/>
-      </c>
-      <c r="C6" s="21">
-        <f>B6</f>
-        <v/>
-      </c>
-      <c r="D6" s="21">
-        <f>C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="21">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="F6" s="21">
-        <f>E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="21">
-        <f>F6</f>
-        <v/>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>TRANCHE 1 — Sukuk 1 (bullet, refinanced)</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Long-term debt</t>
-        </is>
-      </c>
-      <c r="B7" s="21">
-        <f>Assumptions!$B$49</f>
-        <v/>
+          <t xml:space="preserve">  Opening balance</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
       </c>
       <c r="C7" s="21">
-        <f>B7</f>
+        <f>Assumptions!$B$146</f>
         <v/>
       </c>
       <c r="D7" s="21">
-        <f>C7</f>
+        <f>C10</f>
         <v/>
       </c>
       <c r="E7" s="21">
-        <f>D7</f>
+        <f>D10</f>
         <v/>
       </c>
       <c r="F7" s="21">
-        <f>E7</f>
+        <f>E10</f>
         <v/>
       </c>
       <c r="G7" s="21">
-        <f>F7</f>
+        <f>F10</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities (from Leases sheet)</t>
-        </is>
-      </c>
-      <c r="B8" s="21">
-        <f>Leases!$B$17</f>
-        <v/>
+          <t xml:space="preserve">  + Issuance</t>
+        </is>
       </c>
       <c r="C8" s="21">
-        <f>Leases!$C$17</f>
+        <f>IF(1=Assumptions!$B$148,Assumptions!$B$146,0)</f>
         <v/>
       </c>
       <c r="D8" s="21">
-        <f>Leases!$D$17</f>
+        <f>IF(2=Assumptions!$B$148,Assumptions!$B$146,0)</f>
         <v/>
       </c>
       <c r="E8" s="21">
-        <f>Leases!$E$17</f>
+        <f>IF(3=Assumptions!$B$148,Assumptions!$B$146,0)</f>
         <v/>
       </c>
       <c r="F8" s="21">
-        <f>Leases!$F$17</f>
+        <f>IF(4=Assumptions!$B$148,Assumptions!$B$146,0)</f>
         <v/>
       </c>
       <c r="G8" s="21">
-        <f>Leases!$G$17</f>
+        <f>IF(5=Assumptions!$B$148,Assumptions!$B$146,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Repayment</t>
+        </is>
+      </c>
+      <c r="C9" s="21">
+        <f>-IF(1=Assumptions!$B$148,Assumptions!$B$146,0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
+        <f>-IF(2=Assumptions!$B$148,Assumptions!$B$146,0)</f>
+        <v/>
+      </c>
+      <c r="E9" s="21">
+        <f>-IF(3=Assumptions!$B$148,Assumptions!$B$146,0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="21">
+        <f>-IF(4=Assumptions!$B$148,Assumptions!$B$146,0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="21">
+        <f>-IF(5=Assumptions!$B$148,Assumptions!$B$146,0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Gross debt (total)</t>
+          <t xml:space="preserve">  Closing balance</t>
         </is>
       </c>
       <c r="B10" s="22">
-        <f>B6+B7+B8</f>
+        <f>Assumptions!$B$146</f>
         <v/>
       </c>
       <c r="C10" s="22">
-        <f>C6+C7+C8</f>
+        <f>C7+C8+C9</f>
         <v/>
       </c>
       <c r="D10" s="22">
-        <f>D6+D7+D8</f>
+        <f>D7+D8+D9</f>
         <v/>
       </c>
       <c r="E10" s="22">
-        <f>E6+E7+E8</f>
+        <f>E7+E8+E9</f>
         <v/>
       </c>
       <c r="F10" s="22">
-        <f>F6+F7+F8</f>
+        <f>F7+F8+F9</f>
         <v/>
       </c>
       <c r="G10" s="22">
-        <f>G6+G7+G8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Less: cash (from BS)</t>
-        </is>
-      </c>
-      <c r="B12" s="21">
-        <f>-Assumptions!$B$35</f>
-        <v/>
-      </c>
-      <c r="C12" s="21">
-        <f>-BS!C7</f>
-        <v/>
-      </c>
-      <c r="D12" s="21">
-        <f>-BS!D7</f>
-        <v/>
-      </c>
-      <c r="E12" s="21">
-        <f>-BS!E7</f>
-        <v/>
-      </c>
-      <c r="F12" s="21">
-        <f>-BS!F7</f>
-        <v/>
-      </c>
-      <c r="G12" s="21">
-        <f>-BS!G7</f>
-        <v/>
+        <f>G7+G8+G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Interest expense (coupon × opening)</t>
+        </is>
+      </c>
+      <c r="C11" s="21">
+        <f>C7*Assumptions!$B$147</f>
+        <v/>
+      </c>
+      <c r="D11" s="21">
+        <f>D7*Assumptions!$B$147</f>
+        <v/>
+      </c>
+      <c r="E11" s="21">
+        <f>E7*Assumptions!$B$147</f>
+        <v/>
+      </c>
+      <c r="F11" s="21">
+        <f>F7*Assumptions!$B$147</f>
+        <v/>
+      </c>
+      <c r="G11" s="21">
+        <f>G7*Assumptions!$B$147</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>TRANCHE 2 — Sukuk 2 (matures Y8)</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>Net debt</t>
-        </is>
-      </c>
-      <c r="B14" s="22">
-        <f>B10+B12</f>
-        <v/>
-      </c>
-      <c r="C14" s="22">
-        <f>C10+C12</f>
-        <v/>
-      </c>
-      <c r="D14" s="22">
-        <f>D10+D12</f>
-        <v/>
-      </c>
-      <c r="E14" s="22">
-        <f>E10+E12</f>
-        <v/>
-      </c>
-      <c r="F14" s="22">
-        <f>F10+F12</f>
-        <v/>
-      </c>
-      <c r="G14" s="22">
-        <f>G10+G12</f>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening balance</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="C14" s="21">
+        <f>Assumptions!$B$151</f>
+        <v/>
+      </c>
+      <c r="D14" s="21">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="E14" s="21">
+        <f>D17</f>
+        <v/>
+      </c>
+      <c r="F14" s="21">
+        <f>E17</f>
+        <v/>
+      </c>
+      <c r="G14" s="21">
+        <f>F17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + Issuance</t>
+        </is>
+      </c>
+      <c r="C15" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D15" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F15" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G15" s="21">
+        <f>0</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Interest expense (= kd × opening ST + LT debt)</t>
+          <t xml:space="preserve">  − Repayment</t>
         </is>
       </c>
       <c r="C16" s="21">
-        <f>Assumptions!$B$23*(B6+B7)</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="D16" s="21">
-        <f>Assumptions!$B$23*(C6+C7)</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E16" s="21">
-        <f>Assumptions!$B$23*(D6+D7)</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="F16" s="21">
-        <f>Assumptions!$B$23*(E6+E7)</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="G16" s="21">
-        <f>Assumptions!$B$23*(F6+F7)</f>
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Closing balance</t>
+        </is>
+      </c>
+      <c r="B17" s="22">
+        <f>Assumptions!$B$151</f>
+        <v/>
+      </c>
+      <c r="C17" s="22">
+        <f>C14+C15+C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="22">
+        <f>D14+D15+D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="22">
+        <f>E14+E15+E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="22">
+        <f>F14+F15+F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="22">
+        <f>G14+G15+G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Interest expense</t>
+        </is>
+      </c>
+      <c r="C18" s="21">
+        <f>C14*Assumptions!$B$152</f>
+        <v/>
+      </c>
+      <c r="D18" s="21">
+        <f>D14*Assumptions!$B$152</f>
+        <v/>
+      </c>
+      <c r="E18" s="21">
+        <f>E14*Assumptions!$B$152</f>
+        <v/>
+      </c>
+      <c r="F18" s="21">
+        <f>F14*Assumptions!$B$152</f>
+        <v/>
+      </c>
+      <c r="G18" s="21">
+        <f>G14*Assumptions!$B$152</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>TRANCHE 3 — Term loan (amortising)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening balance</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="C21" s="21">
+        <f>Assumptions!$B$155</f>
+        <v/>
+      </c>
+      <c r="D21" s="21">
+        <f>C24</f>
+        <v/>
+      </c>
+      <c r="E21" s="21">
+        <f>D24</f>
+        <v/>
+      </c>
+      <c r="F21" s="21">
+        <f>E24</f>
+        <v/>
+      </c>
+      <c r="G21" s="21">
+        <f>F24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + Issuance</t>
+        </is>
+      </c>
+      <c r="C22" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D22" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E22" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F22" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G22" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Repayment</t>
+        </is>
+      </c>
+      <c r="C23" s="21">
+        <f>-MIN(Assumptions!$B$157,C21)</f>
+        <v/>
+      </c>
+      <c r="D23" s="21">
+        <f>-MIN(Assumptions!$B$157,D21)</f>
+        <v/>
+      </c>
+      <c r="E23" s="21">
+        <f>-MIN(Assumptions!$B$157,E21)</f>
+        <v/>
+      </c>
+      <c r="F23" s="21">
+        <f>-MIN(Assumptions!$B$157,F21)</f>
+        <v/>
+      </c>
+      <c r="G23" s="21">
+        <f>-MIN(Assumptions!$B$157,G21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Closing balance</t>
+        </is>
+      </c>
+      <c r="B24" s="22">
+        <f>Assumptions!$B$155</f>
+        <v/>
+      </c>
+      <c r="C24" s="22">
+        <f>C21+C22+C23</f>
+        <v/>
+      </c>
+      <c r="D24" s="22">
+        <f>D21+D22+D23</f>
+        <v/>
+      </c>
+      <c r="E24" s="22">
+        <f>E21+E22+E23</f>
+        <v/>
+      </c>
+      <c r="F24" s="22">
+        <f>F21+F22+F23</f>
+        <v/>
+      </c>
+      <c r="G24" s="22">
+        <f>G21+G22+G23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Interest expense</t>
+        </is>
+      </c>
+      <c r="C25" s="21">
+        <f>C21*Assumptions!$B$156</f>
+        <v/>
+      </c>
+      <c r="D25" s="21">
+        <f>D21*Assumptions!$B$156</f>
+        <v/>
+      </c>
+      <c r="E25" s="21">
+        <f>E21*Assumptions!$B$156</f>
+        <v/>
+      </c>
+      <c r="F25" s="21">
+        <f>F21*Assumptions!$B$156</f>
+        <v/>
+      </c>
+      <c r="G25" s="21">
+        <f>G21*Assumptions!$B$156</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>TRANCHE 4 — RCF (drawn portion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening balance</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="C28" s="21">
+        <f>Assumptions!$B$160</f>
+        <v/>
+      </c>
+      <c r="D28" s="21">
+        <f>C31</f>
+        <v/>
+      </c>
+      <c r="E28" s="21">
+        <f>D31</f>
+        <v/>
+      </c>
+      <c r="F28" s="21">
+        <f>E31</f>
+        <v/>
+      </c>
+      <c r="G28" s="21">
+        <f>F31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + Issuance</t>
+        </is>
+      </c>
+      <c r="C29" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D29" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E29" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F29" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G29" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Repayment</t>
+        </is>
+      </c>
+      <c r="C30" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D30" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E30" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F30" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G30" s="21">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Closing balance</t>
+        </is>
+      </c>
+      <c r="B31" s="22">
+        <f>Assumptions!$B$160</f>
+        <v/>
+      </c>
+      <c r="C31" s="22">
+        <f>C28+C29+C30</f>
+        <v/>
+      </c>
+      <c r="D31" s="22">
+        <f>D28+D29+D30</f>
+        <v/>
+      </c>
+      <c r="E31" s="22">
+        <f>E28+E29+E30</f>
+        <v/>
+      </c>
+      <c r="F31" s="22">
+        <f>F28+F29+F30</f>
+        <v/>
+      </c>
+      <c r="G31" s="22">
+        <f>G28+G29+G30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Interest expense</t>
+        </is>
+      </c>
+      <c r="C32" s="21">
+        <f>C28*Assumptions!$B$161</f>
+        <v/>
+      </c>
+      <c r="D32" s="21">
+        <f>D28*Assumptions!$B$161</f>
+        <v/>
+      </c>
+      <c r="E32" s="21">
+        <f>E28*Assumptions!$B$161</f>
+        <v/>
+      </c>
+      <c r="F32" s="21">
+        <f>F28*Assumptions!$B$161</f>
+        <v/>
+      </c>
+      <c r="G32" s="21">
+        <f>G28*Assumptions!$B$161</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL FINANCIAL DEBT (excl. leases)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Short-term debt (Term Loan + RCF)</t>
+        </is>
+      </c>
+      <c r="B35" s="24">
+        <f>Assumptions!$B$48</f>
+        <v/>
+      </c>
+      <c r="C35" s="24">
+        <f>C24+C31</f>
+        <v/>
+      </c>
+      <c r="D35" s="24">
+        <f>D24+D31</f>
+        <v/>
+      </c>
+      <c r="E35" s="24">
+        <f>E24+E31</f>
+        <v/>
+      </c>
+      <c r="F35" s="24">
+        <f>F24+F31</f>
+        <v/>
+      </c>
+      <c r="G35" s="24">
+        <f>G24+G31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Long-term debt (Sukuk 1 + Sukuk 2)</t>
+        </is>
+      </c>
+      <c r="B36" s="24">
+        <f>Assumptions!$B$49</f>
+        <v/>
+      </c>
+      <c r="C36" s="24">
+        <f>C10+C17</f>
+        <v/>
+      </c>
+      <c r="D36" s="24">
+        <f>D10+D17</f>
+        <v/>
+      </c>
+      <c r="E36" s="24">
+        <f>E10+E17</f>
+        <v/>
+      </c>
+      <c r="F36" s="24">
+        <f>F10+F17</f>
+        <v/>
+      </c>
+      <c r="G36" s="24">
+        <f>G10+G17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Lease liabilities (from Leases sheet)</t>
+        </is>
+      </c>
+      <c r="B37" s="21">
+        <f>Leases!$B$17</f>
+        <v/>
+      </c>
+      <c r="C37" s="21">
+        <f>Leases!$C$17</f>
+        <v/>
+      </c>
+      <c r="D37" s="21">
+        <f>Leases!$D$17</f>
+        <v/>
+      </c>
+      <c r="E37" s="21">
+        <f>Leases!$E$17</f>
+        <v/>
+      </c>
+      <c r="F37" s="21">
+        <f>Leases!$F$17</f>
+        <v/>
+      </c>
+      <c r="G37" s="21">
+        <f>Leases!$G$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>Gross debt (total, incl. leases)</t>
+        </is>
+      </c>
+      <c r="B39" s="22">
+        <f>B35+B36+B37</f>
+        <v/>
+      </c>
+      <c r="C39" s="22">
+        <f>C35+C36+C37</f>
+        <v/>
+      </c>
+      <c r="D39" s="22">
+        <f>D35+D36+D37</f>
+        <v/>
+      </c>
+      <c r="E39" s="22">
+        <f>E35+E36+E37</f>
+        <v/>
+      </c>
+      <c r="F39" s="22">
+        <f>F35+F36+F37</f>
+        <v/>
+      </c>
+      <c r="G39" s="22">
+        <f>G35+G36+G37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Less: cash (from BS)</t>
+        </is>
+      </c>
+      <c r="B41" s="21">
+        <f>-Assumptions!$B$35</f>
+        <v/>
+      </c>
+      <c r="C41" s="21">
+        <f>-BS!C7</f>
+        <v/>
+      </c>
+      <c r="D41" s="21">
+        <f>-BS!D7</f>
+        <v/>
+      </c>
+      <c r="E41" s="21">
+        <f>-BS!E7</f>
+        <v/>
+      </c>
+      <c r="F41" s="21">
+        <f>-BS!F7</f>
+        <v/>
+      </c>
+      <c r="G41" s="21">
+        <f>-BS!G7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B43" s="22">
+        <f>B39+B41</f>
+        <v/>
+      </c>
+      <c r="C43" s="22">
+        <f>C39+C41</f>
+        <v/>
+      </c>
+      <c r="D43" s="22">
+        <f>D39+D41</f>
+        <v/>
+      </c>
+      <c r="E43" s="22">
+        <f>E39+E41</f>
+        <v/>
+      </c>
+      <c r="F43" s="22">
+        <f>F39+F41</f>
+        <v/>
+      </c>
+      <c r="G43" s="22">
+        <f>G39+G41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>Total financial interest (sum of tranches)</t>
+        </is>
+      </c>
+      <c r="C45" s="22">
+        <f>C11+C18+C25+C32</f>
+        <v/>
+      </c>
+      <c r="D45" s="22">
+        <f>D11+D18+D25+D32</f>
+        <v/>
+      </c>
+      <c r="E45" s="22">
+        <f>E11+E18+E25+E32</f>
+        <v/>
+      </c>
+      <c r="F45" s="22">
+        <f>F11+F18+F25+F32</f>
+        <v/>
+      </c>
+      <c r="G45" s="22">
+        <f>G11+G18+G25+G32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Net debt issuance (to CFS)</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="C46" s="24">
+        <f>C8+C9+C15+C16+C22+C23+C29+C30</f>
+        <v/>
+      </c>
+      <c r="D46" s="24">
+        <f>D8+D9+D15+D16+D22+D23+D29+D30</f>
+        <v/>
+      </c>
+      <c r="E46" s="24">
+        <f>E8+E9+E15+E16+E22+E23+E29+E30</f>
+        <v/>
+      </c>
+      <c r="F46" s="24">
+        <f>F8+F9+F15+F16+F22+F23+F29+F30</f>
+        <v/>
+      </c>
+      <c r="G46" s="24">
+        <f>G8+G9+G15+G16+G22+G23+G29+G30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>MATURITY PROFILE — principal payments by year</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>Principal due</t>
+        </is>
+      </c>
+      <c r="C49" s="22">
+        <f>-C9+-C16+-C23+-C30</f>
+        <v/>
+      </c>
+      <c r="D49" s="22">
+        <f>-D9+-D16+-D23+-D30</f>
+        <v/>
+      </c>
+      <c r="E49" s="22">
+        <f>-E9+-E16+-E23+-E30</f>
+        <v/>
+      </c>
+      <c r="F49" s="22">
+        <f>-F9+-F16+-F23+-F30</f>
+        <v/>
+      </c>
+      <c r="G49" s="22">
+        <f>-G9+-G16+-G23+-G30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sukuk 1</t>
+        </is>
+      </c>
+      <c r="C50" s="21">
+        <f>-C9</f>
+        <v/>
+      </c>
+      <c r="D50" s="21">
+        <f>-D9</f>
+        <v/>
+      </c>
+      <c r="E50" s="21">
+        <f>-E9</f>
+        <v/>
+      </c>
+      <c r="F50" s="21">
+        <f>-F9</f>
+        <v/>
+      </c>
+      <c r="G50" s="21">
+        <f>-G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sukuk 2</t>
+        </is>
+      </c>
+      <c r="C51" s="21">
+        <f>-C16</f>
+        <v/>
+      </c>
+      <c r="D51" s="21">
+        <f>-D16</f>
+        <v/>
+      </c>
+      <c r="E51" s="21">
+        <f>-E16</f>
+        <v/>
+      </c>
+      <c r="F51" s="21">
+        <f>-F16</f>
+        <v/>
+      </c>
+      <c r="G51" s="21">
+        <f>-G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Term loan</t>
+        </is>
+      </c>
+      <c r="C52" s="21">
+        <f>-C23</f>
+        <v/>
+      </c>
+      <c r="D52" s="21">
+        <f>-D23</f>
+        <v/>
+      </c>
+      <c r="E52" s="21">
+        <f>-E23</f>
+        <v/>
+      </c>
+      <c r="F52" s="21">
+        <f>-F23</f>
+        <v/>
+      </c>
+      <c r="G52" s="21">
+        <f>-G23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RCF</t>
+        </is>
+      </c>
+      <c r="C53" s="21">
+        <f>-C30</f>
+        <v/>
+      </c>
+      <c r="D53" s="21">
+        <f>-D30</f>
+        <v/>
+      </c>
+      <c r="E53" s="21">
+        <f>-E30</f>
+        <v/>
+      </c>
+      <c r="F53" s="21">
+        <f>-F30</f>
+        <v/>
+      </c>
+      <c r="G53" s="21">
+        <f>-G30</f>
         <v/>
       </c>
     </row>
@@ -11904,10 +12903,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -11919,14 +12918,14 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>TAX SCHEDULE</t>
+          <t>TAX SCHEDULE — current + deferred</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Simplified: current tax = max(0, pretax × effective rate). Deferred tax held flat.</t>
+          <t>Current tax = effective rate × pre-tax income. Deferred tax driven by PP&amp;E book-vs-tax depreciation timing.</t>
         </is>
       </c>
     </row>
@@ -11959,83 +12958,286 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Pre-tax income (from IS)</t>
-        </is>
-      </c>
-      <c r="C6" s="21">
-        <f>IS!$C$37</f>
-        <v/>
-      </c>
-      <c r="D6" s="21">
-        <f>IS!$D$37</f>
-        <v/>
-      </c>
-      <c r="E6" s="21">
-        <f>IS!$E$37</f>
-        <v/>
-      </c>
-      <c r="F6" s="21">
-        <f>IS!$F$37</f>
-        <v/>
-      </c>
-      <c r="G6" s="21">
-        <f>IS!$G$37</f>
-        <v/>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CURRENT TAX</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
+          <t>Pre-tax income (from IS)</t>
+        </is>
+      </c>
+      <c r="C7" s="21">
+        <f>IS!$C$37</f>
+        <v/>
+      </c>
+      <c r="D7" s="21">
+        <f>IS!$D$37</f>
+        <v/>
+      </c>
+      <c r="E7" s="21">
+        <f>IS!$E$37</f>
+        <v/>
+      </c>
+      <c r="F7" s="21">
+        <f>IS!$F$37</f>
+        <v/>
+      </c>
+      <c r="G7" s="21">
+        <f>IS!$G$37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
           <t>Effective tax rate</t>
         </is>
       </c>
-      <c r="C7" s="23">
+      <c r="C8" s="23">
         <f>Assumptions!$B$20</f>
         <v/>
       </c>
-      <c r="D7" s="23">
+      <c r="D8" s="23">
         <f>Assumptions!$B$20</f>
         <v/>
       </c>
-      <c r="E7" s="23">
+      <c r="E8" s="23">
         <f>Assumptions!$B$20</f>
         <v/>
       </c>
-      <c r="F7" s="23">
+      <c r="F8" s="23">
         <f>Assumptions!$B$20</f>
         <v/>
       </c>
-      <c r="G7" s="23">
+      <c r="G8" s="23">
         <f>Assumptions!$B$20</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Current tax expense</t>
         </is>
       </c>
-      <c r="C8" s="22">
-        <f>MAX(0,C6*C7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="22">
-        <f>MAX(0,D6*D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="22">
-        <f>MAX(0,E6*E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="22">
-        <f>MAX(0,F6*F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="22">
-        <f>MAX(0,G6*G7)</f>
+      <c r="C9" s="22">
+        <f>MAX(0,C7*C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="22">
+        <f>MAX(0,D7*D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="22">
+        <f>MAX(0,E7*E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="22">
+        <f>MAX(0,F7*F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="22">
+        <f>MAX(0,G7*G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>DEFERRED TAX  (PP&amp;E book vs tax depreciation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Book depreciation (PP&amp;E)</t>
+        </is>
+      </c>
+      <c r="C12" s="21">
+        <f>-PPE!$C$8</f>
+        <v/>
+      </c>
+      <c r="D12" s="21">
+        <f>-PPE!$D$8</f>
+        <v/>
+      </c>
+      <c r="E12" s="21">
+        <f>-PPE!$E$8</f>
+        <v/>
+      </c>
+      <c r="F12" s="21">
+        <f>-PPE!$F$8</f>
+        <v/>
+      </c>
+      <c r="G12" s="21">
+        <f>-PPE!$G$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Tax depreciation (accelerated)</t>
+        </is>
+      </c>
+      <c r="C13" s="21">
+        <f>Assumptions!$B$164*PPE!$B$9</f>
+        <v/>
+      </c>
+      <c r="D13" s="21">
+        <f>Assumptions!$B$164*PPE!$C$9</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>Assumptions!$B$164*PPE!$D$9</f>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>Assumptions!$B$164*PPE!$E$9</f>
+        <v/>
+      </c>
+      <c r="G13" s="21">
+        <f>Assumptions!$B$164*PPE!$F$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Timing difference (tax &gt; book)</t>
+        </is>
+      </c>
+      <c r="C14" s="21">
+        <f>C13-C12</f>
+        <v/>
+      </c>
+      <c r="D14" s="21">
+        <f>D13-D12</f>
+        <v/>
+      </c>
+      <c r="E14" s="21">
+        <f>E13-E12</f>
+        <v/>
+      </c>
+      <c r="F14" s="21">
+        <f>F13-F12</f>
+        <v/>
+      </c>
+      <c r="G14" s="21">
+        <f>G13-G12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Deferred tax expense (= timing × rate)</t>
+        </is>
+      </c>
+      <c r="C15" s="22">
+        <f>C14*C8</f>
+        <v/>
+      </c>
+      <c r="D15" s="22">
+        <f>D14*D8</f>
+        <v/>
+      </c>
+      <c r="E15" s="22">
+        <f>E14*E8</f>
+        <v/>
+      </c>
+      <c r="F15" s="22">
+        <f>F14*F8</f>
+        <v/>
+      </c>
+      <c r="G15" s="22">
+        <f>G14*G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Closing DTL (rollforward)</t>
+        </is>
+      </c>
+      <c r="C16" s="21">
+        <f>Assumptions!$B$52+C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="21">
+        <f>C16+D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="21">
+        <f>D16+E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="21">
+        <f>E16+F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="21">
+        <f>F16+G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL TAX EXPENSE (current + deferred)</t>
+        </is>
+      </c>
+      <c r="C18" s="22">
+        <f>C9+C15</f>
+        <v/>
+      </c>
+      <c r="D18" s="22">
+        <f>D9+D15</f>
+        <v/>
+      </c>
+      <c r="E18" s="22">
+        <f>E9+E15</f>
+        <v/>
+      </c>
+      <c r="F18" s="22">
+        <f>F9+F15</f>
+        <v/>
+      </c>
+      <c r="G18" s="22">
+        <f>G9+G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Effective tax rate (incl. deferred)</t>
+        </is>
+      </c>
+      <c r="C19" s="23">
+        <f>C18/C7</f>
+        <v/>
+      </c>
+      <c r="D19" s="23">
+        <f>D18/D7</f>
+        <v/>
+      </c>
+      <c r="E19" s="23">
+        <f>E18/E7</f>
+        <v/>
+      </c>
+      <c r="F19" s="23">
+        <f>F18/F7</f>
+        <v/>
+      </c>
+      <c r="G19" s="23">
+        <f>G18/G7</f>
         <v/>
       </c>
     </row>

--- a/industries/telecom-it/telecom-model.xlsx
+++ b/industries/telecom-it/telecom-model.xlsx
@@ -1636,23 +1636,23 @@
         </is>
       </c>
       <c r="C30" s="21">
-        <f>PPE!$C$8+Leases!$C$9</f>
+        <f>PPE!$C$39+Leases!$C$9</f>
         <v/>
       </c>
       <c r="D30" s="21">
-        <f>PPE!$D$8+Leases!$D$9</f>
+        <f>PPE!$D$39+Leases!$D$9</f>
         <v/>
       </c>
       <c r="E30" s="21">
-        <f>PPE!$E$8+Leases!$E$9</f>
+        <f>PPE!$E$39+Leases!$E$9</f>
         <v/>
       </c>
       <c r="F30" s="21">
-        <f>PPE!$F$8+Leases!$F$9</f>
+        <f>PPE!$F$39+Leases!$F$9</f>
         <v/>
       </c>
       <c r="G30" s="21">
-        <f>PPE!$G$8+Leases!$G$9</f>
+        <f>PPE!$G$39+Leases!$G$9</f>
         <v/>
       </c>
     </row>
@@ -3867,23 +3867,23 @@
         <v/>
       </c>
       <c r="C13" s="21">
-        <f>PPE!$C$9</f>
+        <f>PPE!$C$40</f>
         <v/>
       </c>
       <c r="D13" s="21">
-        <f>PPE!$D$9</f>
+        <f>PPE!$D$40</f>
         <v/>
       </c>
       <c r="E13" s="21">
-        <f>PPE!$E$9</f>
+        <f>PPE!$E$40</f>
         <v/>
       </c>
       <c r="F13" s="21">
-        <f>PPE!$F$9</f>
+        <f>PPE!$F$40</f>
         <v/>
       </c>
       <c r="G13" s="21">
-        <f>PPE!$G$9</f>
+        <f>PPE!$G$40</f>
         <v/>
       </c>
     </row>
@@ -4924,23 +4924,23 @@
         </is>
       </c>
       <c r="C15" s="21">
-        <f>-PPE!$C$7</f>
+        <f>-PPE!$C$38</f>
         <v/>
       </c>
       <c r="D15" s="21">
-        <f>-PPE!$D$7</f>
+        <f>-PPE!$D$38</f>
         <v/>
       </c>
       <c r="E15" s="21">
-        <f>-PPE!$E$7</f>
+        <f>-PPE!$E$38</f>
         <v/>
       </c>
       <c r="F15" s="21">
-        <f>-PPE!$F$7</f>
+        <f>-PPE!$F$38</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>-PPE!$G$7</f>
+        <f>-PPE!$G$38</f>
         <v/>
       </c>
     </row>
@@ -6832,23 +6832,23 @@
         <v>0.01</v>
       </c>
       <c r="B6" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A6)/(B5-A6))/(1+B5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A6)/(B5-A6))/(1+B5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="C6" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A6)/(C5-A6))/(1+C5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A6)/(C5-A6))/(1+C5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="D6" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A6)/(D5-A6))/(1+D5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A6)/(D5-A6))/(1+D5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="E6" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A6)/(E5-A6))/(1+E5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A6)/(E5-A6))/(1+E5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A6)/(F5-A6))/(1+F5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A6)/(F5-A6))/(1+F5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
     </row>
@@ -6857,23 +6857,23 @@
         <v>0.02</v>
       </c>
       <c r="B7" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A7)/(B5-A7))/(1+B5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A7)/(B5-A7))/(1+B5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="C7" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A7)/(C5-A7))/(1+C5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A7)/(C5-A7))/(1+C5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="D7" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A7)/(D5-A7))/(1+D5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A7)/(D5-A7))/(1+D5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="E7" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A7)/(E5-A7))/(1+E5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A7)/(E5-A7))/(1+E5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A7)/(F5-A7))/(1+F5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A7)/(F5-A7))/(1+F5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
     </row>
@@ -6882,23 +6882,23 @@
         <v>0.03</v>
       </c>
       <c r="B8" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A8)/(B5-A8))/(1+B5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A8)/(B5-A8))/(1+B5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A8)/(C5-A8))/(1+C5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A8)/(C5-A8))/(1+C5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A8)/(D5-A8))/(1+D5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A8)/(D5-A8))/(1+D5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A8)/(E5-A8))/(1+E5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A8)/(E5-A8))/(1+E5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A8)/(F5-A8))/(1+F5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A8)/(F5-A8))/(1+F5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
     </row>
@@ -6907,23 +6907,23 @@
         <v>0.04</v>
       </c>
       <c r="B9" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A9)/(B5-A9))/(1+B5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+B5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+B5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+B5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+B5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+B5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A9)/(B5-A9))/(1+B5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="C9" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A9)/(C5-A9))/(1+C5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+C5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+C5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+C5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+C5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+C5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A9)/(C5-A9))/(1+C5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="D9" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A9)/(D5-A9))/(1+D5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+D5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+D5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+D5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+D5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+D5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A9)/(D5-A9))/(1+D5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A9)/(E5-A9))/(1+E5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+E5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+E5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+E5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+E5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+E5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A9)/(E5-A9))/(1+E5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$7+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$7+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$7+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$7+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$7+WC!$G$20)*(1+A9)/(F5-A9))/(1+F5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
+        <f>((((IS!$C$32*(1-Assumptions!$B$20)+(-IS!$C$30)-PPE!$C$38+WC!$C$20)/(1+F5)^1)+((IS!$D$32*(1-Assumptions!$B$20)+(-IS!$D$30)-PPE!$D$38+WC!$D$20)/(1+F5)^2)+((IS!$E$32*(1-Assumptions!$B$20)+(-IS!$E$30)-PPE!$E$38+WC!$E$20)/(1+F5)^3)+((IS!$F$32*(1-Assumptions!$B$20)+(-IS!$F$30)-PPE!$F$38+WC!$F$20)/(1+F5)^4)+((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)/(1+F5)^5)+(((IS!$G$32*(1-Assumptions!$B$20)+(-IS!$G$30)-PPE!$G$38+WC!$G$20)*(1+A9)/(F5-A9))/(1+F5)^5))-Debt!$B$43)*1000/Assumptions!$B$32</f>
         <v/>
       </c>
     </row>
@@ -7261,23 +7261,23 @@
         </is>
       </c>
       <c r="C10" s="21">
-        <f>-PPE!$C$7</f>
+        <f>-PPE!$C$38</f>
         <v/>
       </c>
       <c r="D10" s="21">
-        <f>-PPE!$D$7</f>
+        <f>-PPE!$D$38</f>
         <v/>
       </c>
       <c r="E10" s="21">
-        <f>-PPE!$E$7</f>
+        <f>-PPE!$E$38</f>
         <v/>
       </c>
       <c r="F10" s="21">
-        <f>-PPE!$F$7</f>
+        <f>-PPE!$F$38</f>
         <v/>
       </c>
       <c r="G10" s="21">
-        <f>-PPE!$G$7</f>
+        <f>-PPE!$G$38</f>
         <v/>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -9445,6 +9445,213 @@
         <is>
           <t>Accelerated vs book 10% → creates DTL.</t>
         </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>PHASE 3+ — PP&amp;E by asset class</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>Class 1 — Network &amp; infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NBV Y0 (SAR bn)</t>
+        </is>
+      </c>
+      <c r="B168" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Largest asset class — radio, transmission, core.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Useful life (years)</t>
+        </is>
+      </c>
+      <c r="B169" s="12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capex allocation</t>
+        </is>
+      </c>
+      <c r="B170" s="10" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>Class 2 — Towers &amp; sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NBV Y0</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Long-life, low capex share.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Useful life</t>
+        </is>
+      </c>
+      <c r="B174" s="12" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capex allocation</t>
+        </is>
+      </c>
+      <c r="B175" s="10" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>Class 3 — Buildings &amp; land</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NBV Y0</t>
+        </is>
+      </c>
+      <c r="B178" s="9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Useful life</t>
+        </is>
+      </c>
+      <c r="B179" s="12" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capex allocation</t>
+        </is>
+      </c>
+      <c r="B180" s="10" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>Class 4 — IT &amp; equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NBV Y0</t>
+        </is>
+      </c>
+      <c r="B183" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Short life, frequent refresh cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Useful life</t>
+        </is>
+      </c>
+      <c r="B184" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capex allocation</t>
+        </is>
+      </c>
+      <c r="B185" s="10" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>Class 5 — Vehicles &amp; other</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NBV Y0</t>
+        </is>
+      </c>
+      <c r="B188" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Useful life</t>
+        </is>
+      </c>
+      <c r="B189" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capex allocation</t>
+        </is>
+      </c>
+      <c r="B190" s="10" t="n">
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>
@@ -12362,10 +12569,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -12377,14 +12584,14 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>PP&amp;E ROLLFORWARD</t>
+          <t>PP&amp;E ROLLFORWARD — by asset class</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Opening PP&amp;E + capex − depreciation = closing PP&amp;E. Net basis (no gross / accumulated split).</t>
+          <t>Five classes: network/infrastructure, towers/sites, buildings/land, IT/equipment, vehicles/other. Each has its own useful life and capex share. Class capex = capex_share × total capex (where total = capex_pct × revenue).</t>
         </is>
       </c>
     </row>
@@ -12422,119 +12629,829 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Opening PP&amp;E</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="C6" s="21">
-        <f>Assumptions!$B$39</f>
-        <v/>
-      </c>
-      <c r="D6" s="21">
-        <f>C9</f>
-        <v/>
-      </c>
-      <c r="E6" s="21">
-        <f>D9</f>
-        <v/>
-      </c>
-      <c r="F6" s="21">
-        <f>E9</f>
-        <v/>
-      </c>
-      <c r="G6" s="21">
-        <f>F9</f>
-        <v/>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Class 1 — Network &amp; infrastructure</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>+ Capex</t>
+          <t xml:space="preserve">  Opening NBV</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
         </is>
       </c>
       <c r="C7" s="21">
-        <f>Assumptions!$B$9*IS!$C$14</f>
+        <f>Assumptions!$B$168</f>
         <v/>
       </c>
       <c r="D7" s="21">
-        <f>Assumptions!$B$9*IS!$D$14</f>
+        <f>C10</f>
         <v/>
       </c>
       <c r="E7" s="21">
-        <f>Assumptions!$B$9*IS!$E$14</f>
+        <f>D10</f>
         <v/>
       </c>
       <c r="F7" s="21">
-        <f>Assumptions!$B$9*IS!$F$14</f>
+        <f>E10</f>
         <v/>
       </c>
       <c r="G7" s="21">
-        <f>Assumptions!$B$9*IS!$G$14</f>
+        <f>F10</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>− Depreciation (PP&amp;E only)</t>
+          <t xml:space="preserve">  + Capex (share × total)</t>
         </is>
       </c>
       <c r="C8" s="21">
-        <f>-C6*Assumptions!$B$139</f>
+        <f>Assumptions!$B$170*Assumptions!$B$9*IS!$C$14</f>
         <v/>
       </c>
       <c r="D8" s="21">
-        <f>-D6*Assumptions!$B$139</f>
+        <f>Assumptions!$B$170*Assumptions!$B$9*IS!$D$14</f>
         <v/>
       </c>
       <c r="E8" s="21">
-        <f>-E6*Assumptions!$B$139</f>
+        <f>Assumptions!$B$170*Assumptions!$B$9*IS!$E$14</f>
         <v/>
       </c>
       <c r="F8" s="21">
-        <f>-F6*Assumptions!$B$139</f>
+        <f>Assumptions!$B$170*Assumptions!$B$9*IS!$F$14</f>
         <v/>
       </c>
       <c r="G8" s="21">
-        <f>-G6*Assumptions!$B$139</f>
+        <f>Assumptions!$B$170*Assumptions!$B$9*IS!$G$14</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>Closing PP&amp;E</t>
-        </is>
-      </c>
-      <c r="B9" s="22">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Depreciation (NBV / life)</t>
+        </is>
+      </c>
+      <c r="C9" s="21">
+        <f>-C7/Assumptions!$B$169</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
+        <f>-D7/Assumptions!$B$169</f>
+        <v/>
+      </c>
+      <c r="E9" s="21">
+        <f>-E7/Assumptions!$B$169</f>
+        <v/>
+      </c>
+      <c r="F9" s="21">
+        <f>-F7/Assumptions!$B$169</f>
+        <v/>
+      </c>
+      <c r="G9" s="21">
+        <f>-G7/Assumptions!$B$169</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Closing NBV</t>
+        </is>
+      </c>
+      <c r="B10" s="22">
+        <f>Assumptions!$B$168</f>
+        <v/>
+      </c>
+      <c r="C10" s="22">
+        <f>C7+C8+C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="22">
+        <f>D7+D8+D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="22">
+        <f>E7+E8+E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="22">
+        <f>F7+F8+F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="22">
+        <f>G7+G8+G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Class 2 — Towers &amp; sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening NBV</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="C13" s="21">
+        <f>Assumptions!$B$173</f>
+        <v/>
+      </c>
+      <c r="D13" s="21">
+        <f>C16</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>D16</f>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>E16</f>
+        <v/>
+      </c>
+      <c r="G13" s="21">
+        <f>F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + Capex (share × total)</t>
+        </is>
+      </c>
+      <c r="C14" s="21">
+        <f>Assumptions!$B$175*Assumptions!$B$9*IS!$C$14</f>
+        <v/>
+      </c>
+      <c r="D14" s="21">
+        <f>Assumptions!$B$175*Assumptions!$B$9*IS!$D$14</f>
+        <v/>
+      </c>
+      <c r="E14" s="21">
+        <f>Assumptions!$B$175*Assumptions!$B$9*IS!$E$14</f>
+        <v/>
+      </c>
+      <c r="F14" s="21">
+        <f>Assumptions!$B$175*Assumptions!$B$9*IS!$F$14</f>
+        <v/>
+      </c>
+      <c r="G14" s="21">
+        <f>Assumptions!$B$175*Assumptions!$B$9*IS!$G$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Depreciation (NBV / life)</t>
+        </is>
+      </c>
+      <c r="C15" s="21">
+        <f>-C13/Assumptions!$B$174</f>
+        <v/>
+      </c>
+      <c r="D15" s="21">
+        <f>-D13/Assumptions!$B$174</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>-E13/Assumptions!$B$174</f>
+        <v/>
+      </c>
+      <c r="F15" s="21">
+        <f>-F13/Assumptions!$B$174</f>
+        <v/>
+      </c>
+      <c r="G15" s="21">
+        <f>-G13/Assumptions!$B$174</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Closing NBV</t>
+        </is>
+      </c>
+      <c r="B16" s="22">
+        <f>Assumptions!$B$173</f>
+        <v/>
+      </c>
+      <c r="C16" s="22">
+        <f>C13+C14+C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="22">
+        <f>D13+D14+D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="22">
+        <f>E13+E14+E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="22">
+        <f>F13+F14+F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="22">
+        <f>G13+G14+G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Class 3 — Buildings &amp; land</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening NBV</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="C19" s="21">
+        <f>Assumptions!$B$178</f>
+        <v/>
+      </c>
+      <c r="D19" s="21">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="E19" s="21">
+        <f>D22</f>
+        <v/>
+      </c>
+      <c r="F19" s="21">
+        <f>E22</f>
+        <v/>
+      </c>
+      <c r="G19" s="21">
+        <f>F22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + Capex (share × total)</t>
+        </is>
+      </c>
+      <c r="C20" s="21">
+        <f>Assumptions!$B$180*Assumptions!$B$9*IS!$C$14</f>
+        <v/>
+      </c>
+      <c r="D20" s="21">
+        <f>Assumptions!$B$180*Assumptions!$B$9*IS!$D$14</f>
+        <v/>
+      </c>
+      <c r="E20" s="21">
+        <f>Assumptions!$B$180*Assumptions!$B$9*IS!$E$14</f>
+        <v/>
+      </c>
+      <c r="F20" s="21">
+        <f>Assumptions!$B$180*Assumptions!$B$9*IS!$F$14</f>
+        <v/>
+      </c>
+      <c r="G20" s="21">
+        <f>Assumptions!$B$180*Assumptions!$B$9*IS!$G$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Depreciation (NBV / life)</t>
+        </is>
+      </c>
+      <c r="C21" s="21">
+        <f>-C19/Assumptions!$B$179</f>
+        <v/>
+      </c>
+      <c r="D21" s="21">
+        <f>-D19/Assumptions!$B$179</f>
+        <v/>
+      </c>
+      <c r="E21" s="21">
+        <f>-E19/Assumptions!$B$179</f>
+        <v/>
+      </c>
+      <c r="F21" s="21">
+        <f>-F19/Assumptions!$B$179</f>
+        <v/>
+      </c>
+      <c r="G21" s="21">
+        <f>-G19/Assumptions!$B$179</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Closing NBV</t>
+        </is>
+      </c>
+      <c r="B22" s="22">
+        <f>Assumptions!$B$178</f>
+        <v/>
+      </c>
+      <c r="C22" s="22">
+        <f>C19+C20+C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="22">
+        <f>D19+D20+D21</f>
+        <v/>
+      </c>
+      <c r="E22" s="22">
+        <f>E19+E20+E21</f>
+        <v/>
+      </c>
+      <c r="F22" s="22">
+        <f>F19+F20+F21</f>
+        <v/>
+      </c>
+      <c r="G22" s="22">
+        <f>G19+G20+G21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Class 4 — IT &amp; equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening NBV</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="C25" s="21">
+        <f>Assumptions!$B$183</f>
+        <v/>
+      </c>
+      <c r="D25" s="21">
+        <f>C28</f>
+        <v/>
+      </c>
+      <c r="E25" s="21">
+        <f>D28</f>
+        <v/>
+      </c>
+      <c r="F25" s="21">
+        <f>E28</f>
+        <v/>
+      </c>
+      <c r="G25" s="21">
+        <f>F28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + Capex (share × total)</t>
+        </is>
+      </c>
+      <c r="C26" s="21">
+        <f>Assumptions!$B$185*Assumptions!$B$9*IS!$C$14</f>
+        <v/>
+      </c>
+      <c r="D26" s="21">
+        <f>Assumptions!$B$185*Assumptions!$B$9*IS!$D$14</f>
+        <v/>
+      </c>
+      <c r="E26" s="21">
+        <f>Assumptions!$B$185*Assumptions!$B$9*IS!$E$14</f>
+        <v/>
+      </c>
+      <c r="F26" s="21">
+        <f>Assumptions!$B$185*Assumptions!$B$9*IS!$F$14</f>
+        <v/>
+      </c>
+      <c r="G26" s="21">
+        <f>Assumptions!$B$185*Assumptions!$B$9*IS!$G$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Depreciation (NBV / life)</t>
+        </is>
+      </c>
+      <c r="C27" s="21">
+        <f>-C25/Assumptions!$B$184</f>
+        <v/>
+      </c>
+      <c r="D27" s="21">
+        <f>-D25/Assumptions!$B$184</f>
+        <v/>
+      </c>
+      <c r="E27" s="21">
+        <f>-E25/Assumptions!$B$184</f>
+        <v/>
+      </c>
+      <c r="F27" s="21">
+        <f>-F25/Assumptions!$B$184</f>
+        <v/>
+      </c>
+      <c r="G27" s="21">
+        <f>-G25/Assumptions!$B$184</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Closing NBV</t>
+        </is>
+      </c>
+      <c r="B28" s="22">
+        <f>Assumptions!$B$183</f>
+        <v/>
+      </c>
+      <c r="C28" s="22">
+        <f>C25+C26+C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="22">
+        <f>D25+D26+D27</f>
+        <v/>
+      </c>
+      <c r="E28" s="22">
+        <f>E25+E26+E27</f>
+        <v/>
+      </c>
+      <c r="F28" s="22">
+        <f>F25+F26+F27</f>
+        <v/>
+      </c>
+      <c r="G28" s="22">
+        <f>G25+G26+G27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Class 5 — Vehicles &amp; other</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening NBV</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="C31" s="21">
+        <f>Assumptions!$B$188</f>
+        <v/>
+      </c>
+      <c r="D31" s="21">
+        <f>C34</f>
+        <v/>
+      </c>
+      <c r="E31" s="21">
+        <f>D34</f>
+        <v/>
+      </c>
+      <c r="F31" s="21">
+        <f>E34</f>
+        <v/>
+      </c>
+      <c r="G31" s="21">
+        <f>F34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + Capex (share × total)</t>
+        </is>
+      </c>
+      <c r="C32" s="21">
+        <f>Assumptions!$B$190*Assumptions!$B$9*IS!$C$14</f>
+        <v/>
+      </c>
+      <c r="D32" s="21">
+        <f>Assumptions!$B$190*Assumptions!$B$9*IS!$D$14</f>
+        <v/>
+      </c>
+      <c r="E32" s="21">
+        <f>Assumptions!$B$190*Assumptions!$B$9*IS!$E$14</f>
+        <v/>
+      </c>
+      <c r="F32" s="21">
+        <f>Assumptions!$B$190*Assumptions!$B$9*IS!$F$14</f>
+        <v/>
+      </c>
+      <c r="G32" s="21">
+        <f>Assumptions!$B$190*Assumptions!$B$9*IS!$G$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Depreciation (NBV / life)</t>
+        </is>
+      </c>
+      <c r="C33" s="21">
+        <f>-C31/Assumptions!$B$189</f>
+        <v/>
+      </c>
+      <c r="D33" s="21">
+        <f>-D31/Assumptions!$B$189</f>
+        <v/>
+      </c>
+      <c r="E33" s="21">
+        <f>-E31/Assumptions!$B$189</f>
+        <v/>
+      </c>
+      <c r="F33" s="21">
+        <f>-F31/Assumptions!$B$189</f>
+        <v/>
+      </c>
+      <c r="G33" s="21">
+        <f>-G31/Assumptions!$B$189</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Closing NBV</t>
+        </is>
+      </c>
+      <c r="B34" s="22">
+        <f>Assumptions!$B$188</f>
+        <v/>
+      </c>
+      <c r="C34" s="22">
+        <f>C31+C32+C33</f>
+        <v/>
+      </c>
+      <c r="D34" s="22">
+        <f>D31+D32+D33</f>
+        <v/>
+      </c>
+      <c r="E34" s="22">
+        <f>E31+E32+E33</f>
+        <v/>
+      </c>
+      <c r="F34" s="22">
+        <f>F31+F32+F33</f>
+        <v/>
+      </c>
+      <c r="G34" s="22">
+        <f>G31+G32+G33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL PP&amp;E</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Total opening NBV</t>
+        </is>
+      </c>
+      <c r="C37" s="24">
+        <f>C7+C13+C19+C25+C31</f>
+        <v/>
+      </c>
+      <c r="D37" s="24">
+        <f>D7+D13+D19+D25+D31</f>
+        <v/>
+      </c>
+      <c r="E37" s="24">
+        <f>E7+E13+E19+E25+E31</f>
+        <v/>
+      </c>
+      <c r="F37" s="24">
+        <f>F7+F13+F19+F25+F31</f>
+        <v/>
+      </c>
+      <c r="G37" s="24">
+        <f>G7+G13+G19+G25+G31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>+ Total capex</t>
+        </is>
+      </c>
+      <c r="C38" s="24">
+        <f>C8+C14+C20+C26+C32</f>
+        <v/>
+      </c>
+      <c r="D38" s="24">
+        <f>D8+D14+D20+D26+D32</f>
+        <v/>
+      </c>
+      <c r="E38" s="24">
+        <f>E8+E14+E20+E26+E32</f>
+        <v/>
+      </c>
+      <c r="F38" s="24">
+        <f>F8+F14+F20+F26+F32</f>
+        <v/>
+      </c>
+      <c r="G38" s="24">
+        <f>G8+G14+G20+G26+G32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>− Total depreciation</t>
+        </is>
+      </c>
+      <c r="C39" s="24">
+        <f>C9+C15+C21+C27+C33</f>
+        <v/>
+      </c>
+      <c r="D39" s="24">
+        <f>D9+D15+D21+D27+D33</f>
+        <v/>
+      </c>
+      <c r="E39" s="24">
+        <f>E9+E15+E21+E27+E33</f>
+        <v/>
+      </c>
+      <c r="F39" s="24">
+        <f>F9+F15+F21+F27+F33</f>
+        <v/>
+      </c>
+      <c r="G39" s="24">
+        <f>G9+G15+G21+G27+G33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>Total closing PP&amp;E</t>
+        </is>
+      </c>
+      <c r="B40" s="22">
         <f>Assumptions!$B$39</f>
         <v/>
       </c>
-      <c r="C9" s="22">
-        <f>C6+C7+C8</f>
-        <v/>
-      </c>
-      <c r="D9" s="22">
-        <f>D6+D7+D8</f>
-        <v/>
-      </c>
-      <c r="E9" s="22">
-        <f>E6+E7+E8</f>
-        <v/>
-      </c>
-      <c r="F9" s="22">
-        <f>F6+F7+F8</f>
-        <v/>
-      </c>
-      <c r="G9" s="22">
-        <f>G6+G7+G8</f>
+      <c r="C40" s="22">
+        <f>C10+C16+C22+C28+C34</f>
+        <v/>
+      </c>
+      <c r="D40" s="22">
+        <f>D10+D16+D22+D28+D34</f>
+        <v/>
+      </c>
+      <c r="E40" s="22">
+        <f>E10+E16+E22+E28+E34</f>
+        <v/>
+      </c>
+      <c r="F40" s="22">
+        <f>F10+F16+F22+F28+F34</f>
+        <v/>
+      </c>
+      <c r="G40" s="22">
+        <f>G10+G16+G22+G28+G34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>CAPEX SPLIT — maintenance vs growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Maintenance capex</t>
+        </is>
+      </c>
+      <c r="C43" s="21">
+        <f>C38*Assumptions!$B$140</f>
+        <v/>
+      </c>
+      <c r="D43" s="21">
+        <f>D38*Assumptions!$B$140</f>
+        <v/>
+      </c>
+      <c r="E43" s="21">
+        <f>E38*Assumptions!$B$140</f>
+        <v/>
+      </c>
+      <c r="F43" s="21">
+        <f>F38*Assumptions!$B$140</f>
+        <v/>
+      </c>
+      <c r="G43" s="21">
+        <f>G38*Assumptions!$B$140</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Growth capex</t>
+        </is>
+      </c>
+      <c r="C44" s="21">
+        <f>C38*(1-Assumptions!$B$140)</f>
+        <v/>
+      </c>
+      <c r="D44" s="21">
+        <f>D38*(1-Assumptions!$B$140)</f>
+        <v/>
+      </c>
+      <c r="E44" s="21">
+        <f>E38*(1-Assumptions!$B$140)</f>
+        <v/>
+      </c>
+      <c r="F44" s="21">
+        <f>F38*(1-Assumptions!$B$140)</f>
+        <v/>
+      </c>
+      <c r="G44" s="21">
+        <f>G38*(1-Assumptions!$B$140)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Implied blended dep rate (memo)</t>
+        </is>
+      </c>
+      <c r="C45" s="23">
+        <f>-C39/C37</f>
+        <v/>
+      </c>
+      <c r="D45" s="23">
+        <f>-D39/D37</f>
+        <v/>
+      </c>
+      <c r="E45" s="23">
+        <f>-E39/E37</f>
+        <v/>
+      </c>
+      <c r="F45" s="23">
+        <f>-F39/F37</f>
+        <v/>
+      </c>
+      <c r="G45" s="23">
+        <f>-G39/G37</f>
         <v/>
       </c>
     </row>
@@ -13059,23 +13976,23 @@
         </is>
       </c>
       <c r="C12" s="21">
-        <f>-PPE!$C$8</f>
+        <f>-PPE!$C$39</f>
         <v/>
       </c>
       <c r="D12" s="21">
-        <f>-PPE!$D$8</f>
+        <f>-PPE!$D$39</f>
         <v/>
       </c>
       <c r="E12" s="21">
-        <f>-PPE!$E$8</f>
+        <f>-PPE!$E$39</f>
         <v/>
       </c>
       <c r="F12" s="21">
-        <f>-PPE!$F$8</f>
+        <f>-PPE!$F$39</f>
         <v/>
       </c>
       <c r="G12" s="21">
-        <f>-PPE!$G$8</f>
+        <f>-PPE!$G$39</f>
         <v/>
       </c>
     </row>
@@ -13086,23 +14003,23 @@
         </is>
       </c>
       <c r="C13" s="21">
-        <f>Assumptions!$B$164*PPE!$B$9</f>
+        <f>Assumptions!$B$164*PPE!$B$40</f>
         <v/>
       </c>
       <c r="D13" s="21">
-        <f>Assumptions!$B$164*PPE!$C$9</f>
+        <f>Assumptions!$B$164*PPE!$C$40</f>
         <v/>
       </c>
       <c r="E13" s="21">
-        <f>Assumptions!$B$164*PPE!$D$9</f>
+        <f>Assumptions!$B$164*PPE!$D$40</f>
         <v/>
       </c>
       <c r="F13" s="21">
-        <f>Assumptions!$B$164*PPE!$E$9</f>
+        <f>Assumptions!$B$164*PPE!$E$40</f>
         <v/>
       </c>
       <c r="G13" s="21">
-        <f>Assumptions!$B$164*PPE!$F$9</f>
+        <f>Assumptions!$B$164*PPE!$F$40</f>
         <v/>
       </c>
     </row>

--- a/industries/telecom-it/telecom-model.xlsx
+++ b/industries/telecom-it/telecom-model.xlsx
@@ -886,14 +886,14 @@
     <row r="33">
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>DATA DISCLAIMER</t>
+          <t>DATA SOURCES</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Default values are calibrated to roughly approximate STC (Tadawul: 7010) at the consolidated level, but starting balance-sheet line items are illustrative — they are NOT extracted from actual STC filings. The model demonstrates structure and methodology. For a publication-grade analysis, replace all blue input cells with figures verified against STC's audited financial statements.</t>
+          <t>Y0 inputs calibrated to STC's FY2024 actuals. Revenue (SAR 75.9 bn) and balance-sheet items (cash 13.4, AR 35.0, PP&amp;E 43.3, intangibles 17.3, investments 34.3, AP 7.5, ST debt 3.0, LT debt 14.0, lease liab 1.7, share capital 50.0, equity 86.4) are drawn from STC's FY2024 consolidated balance sheet (per IR release dated 25-Feb-2025 and the FY2024 annual report). Segment splits (postpaid / prepaid / fixed / B2B / ICT / wholesale), debt tranche structure, spectrum cohort assumptions, working-capital ratios and growth/margin forecast inputs are analytical estimates — STC discloses by business unit (consumer / business / wholesale), not by the analytical segments modelled here. The tranche structure (Sukuk 1/Sukuk 2/Term Loan/RCF) is an illustrative breakdown of STC's actual SAR 17 bn financial debt; STC does not publicly disclose each tranche's coupon and maturity in granular form.</t>
         </is>
       </c>
     </row>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>75</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>0.36</v>
+        <v>0.345</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         </is>
       </c>
       <c r="B27" s="11" t="n">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         </is>
       </c>
       <c r="B28" s="11" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         </is>
       </c>
       <c r="B35" s="9" t="n">
-        <v>10</v>
+        <v>13.4</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         </is>
       </c>
       <c r="B36" s="9" t="n">
-        <v>15.4</v>
+        <v>35</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="B37" s="9" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="38">
@@ -8182,7 +8182,7 @@
         </is>
       </c>
       <c r="B38" s="9" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         </is>
       </c>
       <c r="B39" s="9" t="n">
-        <v>62</v>
+        <v>43.3</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         </is>
       </c>
       <c r="B40" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B41" s="9" t="n">
-        <v>15</v>
+        <v>17.3</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>8</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="43">
@@ -8252,7 +8252,7 @@
         </is>
       </c>
       <c r="B43" s="9" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="B47" s="9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="B48" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="B49" s="9" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50">
@@ -8319,7 +8319,7 @@
         </is>
       </c>
       <c r="B50" s="9" t="n">
-        <v>18</v>
+        <v>1.7</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="B53" s="9" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="55">
@@ -8376,7 +8376,7 @@
         </is>
       </c>
       <c r="B56" s="9" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="B57" s="9" t="n">
-        <v>79.5</v>
+        <v>32.4</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="B59" s="9" t="n">
-        <v>7.9</v>
+        <v>4.1</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="B65" s="13" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         </is>
       </c>
       <c r="B66" s="12" t="n">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         </is>
       </c>
       <c r="B73" s="13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74">
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75">
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="B81" s="13" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="B89" s="9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="B99" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         </is>
       </c>
       <c r="B104" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="B133" s="9" t="n">
-        <v>18</v>
+        <v>1.7</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="B136" s="9" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="B142" s="9" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="B146" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="B151" s="9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         </is>
       </c>
       <c r="B155" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="B157" s="9" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="B168" s="9" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="B170" s="10" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="172">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="B173" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="B175" s="10" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="177">
@@ -9552,7 +9552,7 @@
         </is>
       </c>
       <c r="B178" s="9" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="179">
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="B180" s="10" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="182">
@@ -9589,7 +9589,7 @@
         </is>
       </c>
       <c r="B183" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         </is>
       </c>
       <c r="B185" s="10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="187">
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="B188" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -9651,7 +9651,7 @@
         </is>
       </c>
       <c r="B190" s="10" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
